--- a/google-ads-skills-index.xlsx
+++ b/google-ads-skills-index.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S91"/>
+  <dimension ref="A1:S114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -8468,42 +8468,1675 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="15" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="16" t="inlineStr">
+        <is>
+          <t>Full account audit — multi-module diagnostic</t>
+        </is>
+      </c>
+      <c r="C92" s="15" t="inlineStr">
+        <is>
+          <t>Testing &amp; measurement</t>
+        </is>
+      </c>
+      <c r="D92" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E92" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F92" s="15" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="G92" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H92" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I92" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J92" s="16" t="inlineStr">
+        <is>
+          <t>Taking over an account, quarterly review, or pre-pitch; need a ranked list of critical issues across tracking, structure, settings, keywords/search terms, bids/budgets, ads, landing pages</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L92" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M92" s="15" t="n"/>
+      <c r="N92" s="17" t="n"/>
+      <c r="O92" s="15" t="inlineStr">
+        <is>
+          <t>why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+        </is>
+      </c>
+      <c r="P92" s="15" t="n"/>
+      <c r="Q92" s="16" t="n"/>
+      <c r="R92" s="15" t="n"/>
+      <c r="S92" s="15" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="15" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="16" t="inlineStr">
+        <is>
+          <t>Conversion tracking audit</t>
+        </is>
+      </c>
+      <c r="C93" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D93" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E93" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F93" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G93" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H93" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I93" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J93" s="16" t="inlineStr">
+        <is>
+          <t>Before trusting Smart Bidding on any account: verify tags, primary/secondary actions, duplicates, attribution, Enhanced Conversions, Consent Mode v2, OCI, counting method</t>
+        </is>
+      </c>
+      <c r="K93" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L93" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M93" s="15" t="n"/>
+      <c r="N93" s="17" t="n"/>
+      <c r="O93" s="15" t="inlineStr">
+        <is>
+          <t>why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
+        </is>
+      </c>
+      <c r="P93" s="15" t="n"/>
+      <c r="Q93" s="16" t="n"/>
+      <c r="R93" s="15" t="n"/>
+      <c r="S93" s="15" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="15" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>Weekly account review routine</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr">
+        <is>
+          <t>Testing &amp; measurement</t>
+        </is>
+      </c>
+      <c r="D94" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F94" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G94" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H94" s="15" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+      <c r="I94" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J94" s="16" t="inlineStr">
+        <is>
+          <t>Running the standing weekly check: what to look at, in what order, over which lookbacks, and what triggers an action vs a watch</t>
+        </is>
+      </c>
+      <c r="K94" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L94" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M94" s="15" t="n"/>
+      <c r="N94" s="17" t="n"/>
+      <c r="O94" s="15" t="inlineStr">
+        <is>
+          <t>why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
+        </is>
+      </c>
+      <c r="P94" s="15" t="n"/>
+      <c r="Q94" s="16" t="n"/>
+      <c r="R94" s="15" t="n"/>
+      <c r="S94" s="15" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="15" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="16" t="inlineStr">
+        <is>
+          <t>Performance change root-cause diagnosis</t>
+        </is>
+      </c>
+      <c r="C95" s="15" t="inlineStr">
+        <is>
+          <t>Testing &amp; measurement</t>
+        </is>
+      </c>
+      <c r="D95" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E95" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F95" s="15" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="G95" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H95" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I95" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J95" s="16" t="inlineStr">
+        <is>
+          <t>CPC, CTR, clicks, conversions or CPA moved and nobody knows why; need a decomposition tree before touching anything</t>
+        </is>
+      </c>
+      <c r="K95" s="15" t="inlineStr">
+        <is>
+          <t>Adalysis KPI monitoring series</t>
+        </is>
+      </c>
+      <c r="L95" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M95" s="15" t="n"/>
+      <c r="N95" s="17" t="n"/>
+      <c r="O95" s="15" t="inlineStr">
+        <is>
+          <t>why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
+        </is>
+      </c>
+      <c r="P95" s="15" t="n"/>
+      <c r="Q95" s="16" t="n"/>
+      <c r="R95" s="15" t="n"/>
+      <c r="S95" s="15" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>Bid strategy selection — Smart Bidding vs manual, target vs maximise</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D96" s="15" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F96" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G96" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H96" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I96" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J96" s="16" t="inlineStr">
+        <is>
+          <t>Choosing or changing a bid strategy per campaign; deciding whether volume, signal quality and spend-control needs justify Smart Bidding at all</t>
+        </is>
+      </c>
+      <c r="K96" s="15" t="inlineStr">
+        <is>
+          <t>Optmyzr / Adalysis / PPC Mastery</t>
+        </is>
+      </c>
+      <c r="L96" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M96" s="15" t="n"/>
+      <c r="N96" s="17" t="n"/>
+      <c r="O96" s="15" t="inlineStr">
+        <is>
+          <t>why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
+        </is>
+      </c>
+      <c r="P96" s="15" t="n"/>
+      <c r="Q96" s="16" t="n"/>
+      <c r="R96" s="15" t="n"/>
+      <c r="S96" s="15" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>Targets from unit economics — break-even ROAS, profit curve, growth vs efficiency</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D97" s="15" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F97" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G97" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H97" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I97" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J97" s="16" t="inlineStr">
+        <is>
+          <t>Setting or renegotiating tCPA/tROAS with a client; need margin, LTV, payback and a primary-goal/guardrail pair before touching the target</t>
+        </is>
+      </c>
+      <c r="K97" s="15" t="inlineStr">
+        <is>
+          <t>Mike Rhodes / PPC Mastery</t>
+        </is>
+      </c>
+      <c r="L97" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M97" s="15" t="n"/>
+      <c r="N97" s="17" t="n"/>
+      <c r="O97" s="15" t="inlineStr">
+        <is>
+          <t>why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
+        </is>
+      </c>
+      <c r="P97" s="15" t="n"/>
+      <c r="Q97" s="16" t="n"/>
+      <c r="R97" s="15" t="n"/>
+      <c r="S97" s="15" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
+        <is>
+          <t>Smart Bidding learning period — what resets it and change-size rules</t>
+        </is>
+      </c>
+      <c r="C98" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D98" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E98" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F98" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G98" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H98" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I98" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J98" s="16" t="inlineStr">
+        <is>
+          <t>Planning any target, budget, structure or conversion-action change on a Smart Bidding campaign; deciding step size and spacing to avoid relearning</t>
+        </is>
+      </c>
+      <c r="K98" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L98" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M98" s="15" t="n"/>
+      <c r="N98" s="17" t="n"/>
+      <c r="O98" s="15" t="inlineStr">
+        <is>
+          <t>why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
+        </is>
+      </c>
+      <c r="P98" s="15" t="n"/>
+      <c r="Q98" s="16" t="n"/>
+      <c r="R98" s="15" t="n"/>
+      <c r="S98" s="15" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="15" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" s="16" t="inlineStr">
+        <is>
+          <t>AI Max for Search — test design and evaluation</t>
+        </is>
+      </c>
+      <c r="C99" s="15" t="inlineStr">
+        <is>
+          <t>Keyword &amp; query</t>
+        </is>
+      </c>
+      <c r="D99" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E99" s="15" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="F99" s="15" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="G99" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H99" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I99" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J99" s="16" t="inlineStr">
+        <is>
+          <t>Google is pushing AI Max; need prerequisites, a limited test, and how to read search terms, asset source and URL expansion before keeping it on</t>
+        </is>
+      </c>
+      <c r="K99" s="15" t="inlineStr">
+        <is>
+          <t>Adalysis / ZATO</t>
+        </is>
+      </c>
+      <c r="L99" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M99" s="15" t="n"/>
+      <c r="N99" s="17" t="n"/>
+      <c r="O99" s="15" t="inlineStr">
+        <is>
+          <t>why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
+        </is>
+      </c>
+      <c r="P99" s="15" t="n"/>
+      <c r="Q99" s="16" t="n"/>
+      <c r="R99" s="15" t="n"/>
+      <c r="S99" s="15" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" s="16" t="inlineStr">
+        <is>
+          <t>Product performance bucketing for Shopping and PMax</t>
+        </is>
+      </c>
+      <c r="C100" s="15" t="inlineStr">
+        <is>
+          <t>Shopping &amp; feeds</t>
+        </is>
+      </c>
+      <c r="D100" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E100" s="15" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="F100" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G100" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H100" s="15" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I100" s="15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="J100" s="16" t="inlineStr">
+        <is>
+          <t>Spend concentrated on a few SKUs while most products get no impressions; want zombies/heroes/sidekicks split into campaigns or asset groups</t>
+        </is>
+      </c>
+      <c r="K100" s="15" t="inlineStr">
+        <is>
+          <t>Mike Rhodes / Optmyzr</t>
+        </is>
+      </c>
+      <c r="L100" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M100" s="15" t="n"/>
+      <c r="N100" s="17" t="n"/>
+      <c r="O100" s="15" t="inlineStr">
+        <is>
+          <t>why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
+        </is>
+      </c>
+      <c r="P100" s="15" t="n"/>
+      <c r="Q100" s="16" t="n"/>
+      <c r="R100" s="15" t="n"/>
+      <c r="S100" s="15" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" s="16" t="inlineStr">
+        <is>
+          <t>Bid adjustments under Smart Bidding — what still applies</t>
+        </is>
+      </c>
+      <c r="C101" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D101" s="15" t="inlineStr">
+        <is>
+          <t>Setting</t>
+        </is>
+      </c>
+      <c r="E101" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F101" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G101" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H101" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I101" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J101" s="16" t="inlineStr">
+        <is>
+          <t>Inherited account full of device/location/schedule/audience adjustments on tCPA/tROAS; deciding what to strip, what -100% exclusions remain valid</t>
+        </is>
+      </c>
+      <c r="K101" s="15" t="inlineStr">
+        <is>
+          <t>PPC Mastery / Adalysis</t>
+        </is>
+      </c>
+      <c r="L101" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M101" s="15" t="n"/>
+      <c r="N101" s="17" t="n"/>
+      <c r="O101" s="15" t="inlineStr">
+        <is>
+          <t>why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
+        </is>
+      </c>
+      <c r="P101" s="15" t="n"/>
+      <c r="Q101" s="16" t="n"/>
+      <c r="R101" s="15" t="n"/>
+      <c r="S101" s="15" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>Budget reallocation across campaigns by marginal return</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D102" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F102" s="15" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="G102" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I102" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J102" s="16" t="inlineStr">
+        <is>
+          <t>Fixed account budget; some campaigns limited by budget, others underspending; deciding where the next euro goes and whether shared budgets help</t>
+        </is>
+      </c>
+      <c r="K102" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L102" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M102" s="15" t="n"/>
+      <c r="N102" s="17" t="n"/>
+      <c r="O102" s="15" t="inlineStr">
+        <is>
+          <t>why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
+        </is>
+      </c>
+      <c r="P102" s="15" t="n"/>
+      <c r="Q102" s="16" t="n"/>
+      <c r="R102" s="15" t="n"/>
+      <c r="S102" s="15" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="15" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" s="16" t="inlineStr">
+        <is>
+          <t>Scaling without breaking efficiency — budget and target step rules</t>
+        </is>
+      </c>
+      <c r="C103" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D103" s="15" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E103" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F103" s="15" t="inlineStr">
+        <is>
+          <t>Scale</t>
+        </is>
+      </c>
+      <c r="G103" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I103" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J103" s="16" t="inlineStr">
+        <is>
+          <t>Client wants 2x volume; deciding the order of levers (budget, target, match type, campaign type) and step sizes without CPA blowing up</t>
+        </is>
+      </c>
+      <c r="K103" s="15" t="inlineStr">
+        <is>
+          <t>ZATO / PPC Mastery</t>
+        </is>
+      </c>
+      <c r="L103" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M103" s="15" t="n"/>
+      <c r="N103" s="17" t="n"/>
+      <c r="O103" s="15" t="inlineStr">
+        <is>
+          <t>why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
+        </is>
+      </c>
+      <c r="P103" s="15" t="n"/>
+      <c r="Q103" s="16" t="n"/>
+      <c r="R103" s="15" t="n"/>
+      <c r="S103" s="15" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" s="15" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" s="16" t="inlineStr">
+        <is>
+          <t>Campaign not serving / zero impressions troubleshooting</t>
+        </is>
+      </c>
+      <c r="C104" s="15" t="inlineStr">
+        <is>
+          <t>Testing &amp; measurement</t>
+        </is>
+      </c>
+      <c r="D104" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E104" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F104" s="15" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="G104" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I104" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J104" s="16" t="inlineStr">
+        <is>
+          <t>Live campaign with no or near-zero impressions; need the ordered checklist (billing, policy, status, targeting, bids/targets, negatives, eligibility) before escalating</t>
+        </is>
+      </c>
+      <c r="K104" s="15" t="inlineStr">
+        <is>
+          <t>ZATO / Navah Hopkins</t>
+        </is>
+      </c>
+      <c r="L104" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M104" s="15" t="n"/>
+      <c r="N104" s="17" t="n"/>
+      <c r="O104" s="15" t="inlineStr">
+        <is>
+          <t>why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
+        </is>
+      </c>
+      <c r="P104" s="15" t="n"/>
+      <c r="Q104" s="16" t="n"/>
+      <c r="R104" s="15" t="n"/>
+      <c r="S104" s="15" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" s="15" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" s="16" t="inlineStr">
+        <is>
+          <t>New Search campaign launch checklist and first-30-days watch</t>
+        </is>
+      </c>
+      <c r="C105" s="15" t="inlineStr">
+        <is>
+          <t>Account structure</t>
+        </is>
+      </c>
+      <c r="D105" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E105" s="15" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="F105" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G105" s="15" t="inlineStr">
+        <is>
+          <t>New</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I105" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J105" s="16" t="inlineStr">
+        <is>
+          <t>Launching a new Search campaign; pre-launch settings check and what to review in weeks 1–2 (relevance, net-new impressions, IS) vs weeks 3–4 (conversion quality, serving, match type, bid method switch)</t>
+        </is>
+      </c>
+      <c r="K105" s="15" t="inlineStr">
+        <is>
+          <t>Adalysis / PPC Mastery</t>
+        </is>
+      </c>
+      <c r="L105" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M105" s="15" t="n"/>
+      <c r="N105" s="17" t="n"/>
+      <c r="O105" s="15" t="inlineStr">
+        <is>
+          <t>why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
+        </is>
+      </c>
+      <c r="P105" s="15" t="n"/>
+      <c r="Q105" s="16" t="n"/>
+      <c r="R105" s="15" t="n"/>
+      <c r="S105" s="15" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="15" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" s="16" t="inlineStr">
+        <is>
+          <t>Ad assets (sitelinks, callouts, snippets, images) — build and evaluate</t>
+        </is>
+      </c>
+      <c r="C106" s="15" t="inlineStr">
+        <is>
+          <t>RSA &amp; ad copy</t>
+        </is>
+      </c>
+      <c r="D106" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E106" s="15" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="F106" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G106" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I106" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J106" s="16" t="inlineStr">
+        <is>
+          <t>Setting up or auditing assets; reading asset-level performance and the asset-vs-ad report; which assets to pin to campaign vs account level</t>
+        </is>
+      </c>
+      <c r="K106" s="15" t="inlineStr">
+        <is>
+          <t>Adalysis</t>
+        </is>
+      </c>
+      <c r="L106" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M106" s="15" t="n"/>
+      <c r="N106" s="17" t="n"/>
+      <c r="O106" s="15" t="inlineStr">
+        <is>
+          <t>why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
+        </is>
+      </c>
+      <c r="P106" s="15" t="n"/>
+      <c r="Q106" s="16" t="n"/>
+      <c r="R106" s="15" t="n"/>
+      <c r="S106" s="15" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="15" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" s="16" t="inlineStr">
+        <is>
+          <t>Feed attribute optimisation beyond titles (product_type, google_product_category, id, description)</t>
+        </is>
+      </c>
+      <c r="C107" s="15" t="inlineStr">
+        <is>
+          <t>Shopping &amp; feeds</t>
+        </is>
+      </c>
+      <c r="D107" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E107" s="15" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="F107" s="15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="G107" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J107" s="16" t="inlineStr">
+        <is>
+          <t>Titles done; want the secondary attributes that drive matching and segmentation right, and stable product IDs before any feed-provider change</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
+          <t>ZATO Merchant Center Mastery</t>
+        </is>
+      </c>
+      <c r="L107" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M107" s="15" t="n"/>
+      <c r="N107" s="17" t="n"/>
+      <c r="O107" s="15" t="inlineStr">
+        <is>
+          <t>why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
+        </is>
+      </c>
+      <c r="P107" s="15" t="n"/>
+      <c r="Q107" s="16" t="n"/>
+      <c r="R107" s="15" t="n"/>
+      <c r="S107" s="15" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="15" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" s="16" t="inlineStr">
+        <is>
+          <t>Merchant Center account suspension recovery</t>
+        </is>
+      </c>
+      <c r="C108" s="15" t="inlineStr">
+        <is>
+          <t>Shopping &amp; feeds</t>
+        </is>
+      </c>
+      <c r="D108" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E108" s="15" t="inlineStr">
+        <is>
+          <t>Shopping</t>
+        </is>
+      </c>
+      <c r="F108" s="15" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="G108" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I108" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>Account-level suspension (misrepresentation, unacceptable business practices, tax/shipping) rather than item disapprovals; need the compliance checklist and appeal sequence</t>
+        </is>
+      </c>
+      <c r="K108" s="15" t="inlineStr">
+        <is>
+          <t>ZATO</t>
+        </is>
+      </c>
+      <c r="L108" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M108" s="15" t="n"/>
+      <c r="N108" s="17" t="n"/>
+      <c r="O108" s="15" t="inlineStr">
+        <is>
+          <t>why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
+        </is>
+      </c>
+      <c r="P108" s="15" t="n"/>
+      <c r="Q108" s="16" t="n"/>
+      <c r="R108" s="15" t="n"/>
+      <c r="S108" s="15" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="15" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" s="16" t="inlineStr">
+        <is>
+          <t>PMax asset group and asset performance review</t>
+        </is>
+      </c>
+      <c r="C109" s="15" t="inlineStr">
+        <is>
+          <t>Performance Max</t>
+        </is>
+      </c>
+      <c r="D109" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E109" s="15" t="inlineStr">
+        <is>
+          <t>PMax</t>
+        </is>
+      </c>
+      <c r="F109" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G109" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H109" s="15" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I109" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J109" s="16" t="inlineStr">
+        <is>
+          <t>Deciding which assets and asset groups to replace; reading asset ratings, asset-group spend and conversion split, and auto-generated vs supplied assets</t>
+        </is>
+      </c>
+      <c r="K109" s="15" t="inlineStr">
+        <is>
+          <t>Mike Rhodes</t>
+        </is>
+      </c>
+      <c r="L109" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M109" s="15" t="n"/>
+      <c r="N109" s="17" t="n"/>
+      <c r="O109" s="15" t="inlineStr">
+        <is>
+          <t>why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
+        </is>
+      </c>
+      <c r="P109" s="15" t="n"/>
+      <c r="Q109" s="16" t="n"/>
+      <c r="R109" s="15" t="n"/>
+      <c r="S109" s="15" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="15" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" s="16" t="inlineStr">
+        <is>
+          <t>Spam conversions and invalid traffic polluting Smart Bidding</t>
+        </is>
+      </c>
+      <c r="C110" s="15" t="inlineStr">
+        <is>
+          <t>Bidding</t>
+        </is>
+      </c>
+      <c r="D110" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E110" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F110" s="15" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="G110" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H110" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J110" s="16" t="inlineStr">
+        <is>
+          <t>Sudden conversion spike with no revenue, bot form fills, or suspected click fraud; detect, confirm, negate/exclude, and clean the bidding signal</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="inlineStr">
+        <is>
+          <t>Practitioner method</t>
+        </is>
+      </c>
+      <c r="L110" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M110" s="15" t="n"/>
+      <c r="N110" s="17" t="n"/>
+      <c r="O110" s="15" t="inlineStr">
+        <is>
+          <t>why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
+        </is>
+      </c>
+      <c r="P110" s="15" t="n"/>
+      <c r="Q110" s="16" t="n"/>
+      <c r="R110" s="15" t="n"/>
+      <c r="S110" s="15" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="15" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" s="16" t="inlineStr">
+        <is>
+          <t>Landing page audit for paid search</t>
+        </is>
+      </c>
+      <c r="C111" s="15" t="inlineStr">
+        <is>
+          <t>Quality Score</t>
+        </is>
+      </c>
+      <c r="D111" s="15" t="inlineStr">
+        <is>
+          <t>Technique</t>
+        </is>
+      </c>
+      <c r="E111" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F111" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G111" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="inlineStr">
+        <is>
+          <t>As needed</t>
+        </is>
+      </c>
+      <c r="I111" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J111" s="16" t="inlineStr">
+        <is>
+          <t>CVR low despite relevant traffic; structured LP audit (message match, hero, proof, speed, form/CTA, guarantee) and how to test LP with ad together</t>
+        </is>
+      </c>
+      <c r="K111" s="15" t="inlineStr">
+        <is>
+          <t>PPC Mastery / Adalysis</t>
+        </is>
+      </c>
+      <c r="L111" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M111" s="15" t="n"/>
+      <c r="N111" s="17" t="n"/>
+      <c r="O111" s="15" t="inlineStr">
+        <is>
+          <t>why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
+        </is>
+      </c>
+      <c r="P111" s="15" t="n"/>
+      <c r="Q111" s="16" t="n"/>
+      <c r="R111" s="15" t="n"/>
+      <c r="S111" s="15" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="15" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" s="16" t="inlineStr">
+        <is>
+          <t>Automation layering — guardrail automations over Google's automation</t>
+        </is>
+      </c>
+      <c r="C112" s="15" t="inlineStr">
+        <is>
+          <t>Scripts &amp; automation</t>
+        </is>
+      </c>
+      <c r="D112" s="15" t="inlineStr">
+        <is>
+          <t>Strategy</t>
+        </is>
+      </c>
+      <c r="E112" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F112" s="15" t="inlineStr">
+        <is>
+          <t>Optimise</t>
+        </is>
+      </c>
+      <c r="G112" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H112" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I112" s="15" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="J112" s="16" t="inlineStr">
+        <is>
+          <t>Deciding which Google automations to adopt and which monitors (alerts, rules, scripts) must sit on top of each before go-live</t>
+        </is>
+      </c>
+      <c r="K112" s="15" t="inlineStr">
+        <is>
+          <t>Fred Vallaeys</t>
+        </is>
+      </c>
+      <c r="L112" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M112" s="15" t="n"/>
+      <c r="N112" s="17" t="n"/>
+      <c r="O112" s="15" t="inlineStr">
+        <is>
+          <t>why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
+        </is>
+      </c>
+      <c r="P112" s="15" t="n"/>
+      <c r="Q112" s="16" t="n"/>
+      <c r="R112" s="15" t="n"/>
+      <c r="S112" s="15" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="15" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" s="16" t="inlineStr">
+        <is>
+          <t>Change history monitoring</t>
+        </is>
+      </c>
+      <c r="C113" s="15" t="inlineStr">
+        <is>
+          <t>Scripts &amp; automation</t>
+        </is>
+      </c>
+      <c r="D113" s="15" t="inlineStr">
+        <is>
+          <t>Script</t>
+        </is>
+      </c>
+      <c r="E113" s="15" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="F113" s="15" t="inlineStr">
+        <is>
+          <t>Protect</t>
+        </is>
+      </c>
+      <c r="G113" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="H113" s="15" t="inlineStr">
+        <is>
+          <t>One-off</t>
+        </is>
+      </c>
+      <c r="I113" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J113" s="16" t="inlineStr">
+        <is>
+          <t>Multiple users, Google reps or auto-apply touching the account; want daily alerts on unexpected changes with who/what</t>
+        </is>
+      </c>
+      <c r="K113" s="15" t="inlineStr">
+        <is>
+          <t>Nils Rooijmans</t>
+        </is>
+      </c>
+      <c r="L113" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M113" s="15" t="n"/>
+      <c r="N113" s="17" t="n"/>
+      <c r="O113" s="15" t="inlineStr">
+        <is>
+          <t>why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
+        </is>
+      </c>
+      <c r="P113" s="15" t="n"/>
+      <c r="Q113" s="16" t="n"/>
+      <c r="R113" s="15" t="n"/>
+      <c r="S113" s="15" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="15" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" s="16" t="inlineStr">
+        <is>
+          <t>Lin-Rodnitzky ratio as a search-term health metric</t>
+        </is>
+      </c>
+      <c r="C114" s="15" t="inlineStr">
+        <is>
+          <t>Keyword &amp; query</t>
+        </is>
+      </c>
+      <c r="D114" s="15" t="inlineStr">
+        <is>
+          <t>Diagnostic</t>
+        </is>
+      </c>
+      <c r="E114" s="15" t="inlineStr">
+        <is>
+          <t>Search</t>
+        </is>
+      </c>
+      <c r="F114" s="15" t="inlineStr">
+        <is>
+          <t>Diagnose</t>
+        </is>
+      </c>
+      <c r="G114" s="15" t="inlineStr">
+        <is>
+          <t>Established</t>
+        </is>
+      </c>
+      <c r="H114" s="15" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="I114" s="15" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="J114" s="16" t="inlineStr">
+        <is>
+          <t>Need one account-level number for whether query mining is too conservative or too loose (all-query CPA ÷ converting-query CPA, bands 1.0–1.5 / 1.5–2.0 / 2.0–2.5 / 2.5+)</t>
+        </is>
+      </c>
+      <c r="K114" s="15" t="inlineStr">
+        <is>
+          <t>Nils Rooijmans script</t>
+        </is>
+      </c>
+      <c r="L114" s="15" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="M114" s="15" t="n"/>
+      <c r="N114" s="17" t="n"/>
+      <c r="O114" s="15" t="inlineStr">
+        <is>
+          <t>why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
+        </is>
+      </c>
+      <c r="P114" s="15" t="n"/>
+      <c r="Q114" s="16" t="n"/>
+      <c r="R114" s="15" t="n"/>
+      <c r="S114" s="15" t="n"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:S91"/>
   <dataValidations count="9">
-    <dataValidation sqref="D2:D91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D2:D114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Structure,Strategy,Technique,Script,Research,Diagnostic,Setting"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E2:E114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Search,Shopping,PMax,All"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F2:F91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F2:F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Setup,Scale,Optimise,Diagnose,Protect"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G2:G114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"New,Established,Any"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H2:H114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"One-off,Weekly,Monthly,As needed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="I2:I91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="I2:I114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
-      <formula1>"Not started,Drafting,Review,Done"</formula1>
+    <dataValidation sqref="L2:L114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+      <formula1>"Not started,Drafting,Review,Done,Proposed,Re-check"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="R2:R91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R2:R114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Strong,Adequate,Thin"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S91" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="S2:S114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"PASS,FAIL,NEEDS ELIAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -9112,11 +10745,11 @@
         </is>
       </c>
       <c r="B2" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A2)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A2)</f>
         <v/>
       </c>
       <c r="C2" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A2,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A2,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D2" s="22" t="n"/>
@@ -9126,7 +10759,7 @@
         </is>
       </c>
       <c r="F2" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$91,E2)</f>
+        <f>COUNTIF(Skills!$I$2:$I$114,E2)</f>
         <v/>
       </c>
       <c r="G2" s="22" t="n"/>
@@ -9136,7 +10769,7 @@
         </is>
       </c>
       <c r="I2" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$91,H2)</f>
+        <f>COUNTIF(Skills!$F$2:$F$114,H2)</f>
         <v/>
       </c>
     </row>
@@ -9147,11 +10780,11 @@
         </is>
       </c>
       <c r="B3" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A3)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A3)</f>
         <v/>
       </c>
       <c r="C3" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A3,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A3,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D3" s="22" t="n"/>
@@ -9161,7 +10794,7 @@
         </is>
       </c>
       <c r="F3" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$91,E3)</f>
+        <f>COUNTIF(Skills!$I$2:$I$114,E3)</f>
         <v/>
       </c>
       <c r="G3" s="22" t="n"/>
@@ -9171,7 +10804,7 @@
         </is>
       </c>
       <c r="I3" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$91,H3)</f>
+        <f>COUNTIF(Skills!$F$2:$F$114,H3)</f>
         <v/>
       </c>
     </row>
@@ -9182,11 +10815,11 @@
         </is>
       </c>
       <c r="B4" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A4)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A4)</f>
         <v/>
       </c>
       <c r="C4" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A4,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A4,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D4" s="22" t="n"/>
@@ -9196,7 +10829,7 @@
         </is>
       </c>
       <c r="F4" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$91,E4)</f>
+        <f>COUNTIF(Skills!$I$2:$I$114,E4)</f>
         <v/>
       </c>
       <c r="G4" s="22" t="n"/>
@@ -9206,7 +10839,7 @@
         </is>
       </c>
       <c r="I4" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$91,H4)</f>
+        <f>COUNTIF(Skills!$F$2:$F$114,H4)</f>
         <v/>
       </c>
     </row>
@@ -9217,11 +10850,11 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A5)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A5)</f>
         <v/>
       </c>
       <c r="C5" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A5,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A5,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D5" s="22" t="n"/>
@@ -9234,7 +10867,7 @@
         </is>
       </c>
       <c r="I5" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$91,H5)</f>
+        <f>COUNTIF(Skills!$F$2:$F$114,H5)</f>
         <v/>
       </c>
     </row>
@@ -9245,11 +10878,11 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A6)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A6)</f>
         <v/>
       </c>
       <c r="C6" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A6,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A6,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D6" s="22" t="n"/>
@@ -9262,7 +10895,7 @@
         </is>
       </c>
       <c r="I6" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$91,H6)</f>
+        <f>COUNTIF(Skills!$F$2:$F$114,H6)</f>
         <v/>
       </c>
     </row>
@@ -9273,11 +10906,11 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A7)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A7)</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A7,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A7,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D7" s="22" t="n"/>
@@ -9294,11 +10927,11 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A8)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A8)</f>
         <v/>
       </c>
       <c r="C8" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A8,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A8,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D8" s="22" t="n"/>
@@ -9315,11 +10948,11 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A9)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A9)</f>
         <v/>
       </c>
       <c r="C9" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A9,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A9,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -9336,11 +10969,11 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A10)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A10)</f>
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A10,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A10,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -9357,11 +10990,11 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A11)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A11)</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A11,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A11,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -9378,11 +11011,11 @@
         </is>
       </c>
       <c r="B12" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$91,A12)</f>
+        <f>COUNTIF(Skills!$C$2:$C$114,A12)</f>
         <v/>
       </c>
       <c r="C12" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$91,A12,Skills!$L$2:$L$91,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$114,A12,Skills!$L$2:$L$114,"Done")</f>
         <v/>
       </c>
       <c r="D12" s="22" t="n"/>

--- a/google-ads-skills-index.xlsx
+++ b/google-ads-skills-index.xlsx
@@ -8531,13 +8531,17 @@
       <c r="N92" s="17" t="n"/>
       <c r="O92" s="15" t="inlineStr">
         <is>
-          <t>why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
         </is>
       </c>
       <c r="P92" s="15" t="n"/>
       <c r="Q92" s="16" t="n"/>
       <c r="R92" s="15" t="n"/>
-      <c r="S92" s="15" t="n"/>
+      <c r="S92" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
@@ -8602,13 +8606,17 @@
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="15" t="inlineStr">
         <is>
-          <t>why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
         </is>
       </c>
       <c r="P93" s="15" t="n"/>
       <c r="Q93" s="16" t="n"/>
       <c r="R93" s="15" t="n"/>
-      <c r="S93" s="15" t="n"/>
+      <c r="S93" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
@@ -8673,13 +8681,17 @@
       <c r="N94" s="17" t="n"/>
       <c r="O94" s="15" t="inlineStr">
         <is>
-          <t>why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
         </is>
       </c>
       <c r="P94" s="15" t="n"/>
       <c r="Q94" s="16" t="n"/>
       <c r="R94" s="15" t="n"/>
-      <c r="S94" s="15" t="n"/>
+      <c r="S94" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
@@ -8744,13 +8756,17 @@
       <c r="N95" s="17" t="n"/>
       <c r="O95" s="15" t="inlineStr">
         <is>
-          <t>why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
         </is>
       </c>
       <c r="P95" s="15" t="n"/>
       <c r="Q95" s="16" t="n"/>
       <c r="R95" s="15" t="n"/>
-      <c r="S95" s="15" t="n"/>
+      <c r="S95" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
@@ -8815,13 +8831,17 @@
       <c r="N96" s="17" t="n"/>
       <c r="O96" s="15" t="inlineStr">
         <is>
-          <t>why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
         </is>
       </c>
       <c r="P96" s="15" t="n"/>
       <c r="Q96" s="16" t="n"/>
       <c r="R96" s="15" t="n"/>
-      <c r="S96" s="15" t="n"/>
+      <c r="S96" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
@@ -8886,13 +8906,17 @@
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="15" t="inlineStr">
         <is>
-          <t>why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
         </is>
       </c>
       <c r="P97" s="15" t="n"/>
       <c r="Q97" s="16" t="n"/>
       <c r="R97" s="15" t="n"/>
-      <c r="S97" s="15" t="n"/>
+      <c r="S97" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
@@ -8957,13 +8981,17 @@
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
         </is>
       </c>
       <c r="P98" s="15" t="n"/>
       <c r="Q98" s="16" t="n"/>
       <c r="R98" s="15" t="n"/>
-      <c r="S98" s="15" t="n"/>
+      <c r="S98" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
@@ -9028,13 +9056,17 @@
       <c r="N99" s="17" t="n"/>
       <c r="O99" s="15" t="inlineStr">
         <is>
-          <t>why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
         </is>
       </c>
       <c r="P99" s="15" t="n"/>
       <c r="Q99" s="16" t="n"/>
       <c r="R99" s="15" t="n"/>
-      <c r="S99" s="15" t="n"/>
+      <c r="S99" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
@@ -9099,13 +9131,17 @@
       <c r="N100" s="17" t="n"/>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
         </is>
       </c>
       <c r="P100" s="15" t="n"/>
       <c r="Q100" s="16" t="n"/>
       <c r="R100" s="15" t="n"/>
-      <c r="S100" s="15" t="n"/>
+      <c r="S100" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
@@ -9170,13 +9206,17 @@
       <c r="N101" s="17" t="n"/>
       <c r="O101" s="15" t="inlineStr">
         <is>
-          <t>why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
         </is>
       </c>
       <c r="P101" s="15" t="n"/>
       <c r="Q101" s="16" t="n"/>
       <c r="R101" s="15" t="n"/>
-      <c r="S101" s="15" t="n"/>
+      <c r="S101" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
@@ -9241,13 +9281,17 @@
       <c r="N102" s="17" t="n"/>
       <c r="O102" s="15" t="inlineStr">
         <is>
-          <t>why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
         </is>
       </c>
       <c r="P102" s="15" t="n"/>
       <c r="Q102" s="16" t="n"/>
       <c r="R102" s="15" t="n"/>
-      <c r="S102" s="15" t="n"/>
+      <c r="S102" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
@@ -9312,13 +9356,17 @@
       <c r="N103" s="17" t="n"/>
       <c r="O103" s="15" t="inlineStr">
         <is>
-          <t>why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
         </is>
       </c>
       <c r="P103" s="15" t="n"/>
       <c r="Q103" s="16" t="n"/>
       <c r="R103" s="15" t="n"/>
-      <c r="S103" s="15" t="n"/>
+      <c r="S103" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
@@ -9383,13 +9431,17 @@
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="15" t="inlineStr">
         <is>
-          <t>why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
         </is>
       </c>
       <c r="P104" s="15" t="n"/>
       <c r="Q104" s="16" t="n"/>
       <c r="R104" s="15" t="n"/>
-      <c r="S104" s="15" t="n"/>
+      <c r="S104" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
@@ -9454,13 +9506,17 @@
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="15" t="inlineStr">
         <is>
-          <t>why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
         </is>
       </c>
       <c r="P105" s="15" t="n"/>
       <c r="Q105" s="16" t="n"/>
       <c r="R105" s="15" t="n"/>
-      <c r="S105" s="15" t="n"/>
+      <c r="S105" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
@@ -9525,13 +9581,17 @@
       <c r="N106" s="17" t="n"/>
       <c r="O106" s="15" t="inlineStr">
         <is>
-          <t>why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
         </is>
       </c>
       <c r="P106" s="15" t="n"/>
       <c r="Q106" s="16" t="n"/>
       <c r="R106" s="15" t="n"/>
-      <c r="S106" s="15" t="n"/>
+      <c r="S106" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
@@ -9596,13 +9656,17 @@
       <c r="N107" s="17" t="n"/>
       <c r="O107" s="15" t="inlineStr">
         <is>
-          <t>why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
         </is>
       </c>
       <c r="P107" s="15" t="n"/>
       <c r="Q107" s="16" t="n"/>
       <c r="R107" s="15" t="n"/>
-      <c r="S107" s="15" t="n"/>
+      <c r="S107" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
@@ -9667,13 +9731,17 @@
       <c r="N108" s="17" t="n"/>
       <c r="O108" s="15" t="inlineStr">
         <is>
-          <t>why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
         </is>
       </c>
       <c r="P108" s="15" t="n"/>
       <c r="Q108" s="16" t="n"/>
       <c r="R108" s="15" t="n"/>
-      <c r="S108" s="15" t="n"/>
+      <c r="S108" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
@@ -9738,13 +9806,17 @@
       <c r="N109" s="17" t="n"/>
       <c r="O109" s="15" t="inlineStr">
         <is>
-          <t>why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
         </is>
       </c>
       <c r="P109" s="15" t="n"/>
       <c r="Q109" s="16" t="n"/>
       <c r="R109" s="15" t="n"/>
-      <c r="S109" s="15" t="n"/>
+      <c r="S109" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
@@ -9809,13 +9881,17 @@
       <c r="N110" s="17" t="n"/>
       <c r="O110" s="15" t="inlineStr">
         <is>
-          <t>why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
         </is>
       </c>
       <c r="P110" s="15" t="n"/>
       <c r="Q110" s="16" t="n"/>
       <c r="R110" s="15" t="n"/>
-      <c r="S110" s="15" t="n"/>
+      <c r="S110" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
@@ -9880,13 +9956,17 @@
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="15" t="inlineStr">
         <is>
-          <t>why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
         </is>
       </c>
       <c r="P111" s="15" t="n"/>
       <c r="Q111" s="16" t="n"/>
       <c r="R111" s="15" t="n"/>
-      <c r="S111" s="15" t="n"/>
+      <c r="S111" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
@@ -9951,13 +10031,17 @@
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="15" t="inlineStr">
         <is>
-          <t>why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
         </is>
       </c>
       <c r="P112" s="15" t="n"/>
       <c r="Q112" s="16" t="n"/>
       <c r="R112" s="15" t="n"/>
-      <c r="S112" s="15" t="n"/>
+      <c r="S112" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
@@ -10022,13 +10106,17 @@
       <c r="N113" s="17" t="n"/>
       <c r="O113" s="15" t="inlineStr">
         <is>
-          <t>why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
         </is>
       </c>
       <c r="P113" s="15" t="n"/>
       <c r="Q113" s="16" t="n"/>
       <c r="R113" s="15" t="n"/>
-      <c r="S113" s="15" t="n"/>
+      <c r="S113" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="15" t="n">
@@ -10093,13 +10181,17 @@
       <c r="N114" s="17" t="n"/>
       <c r="O114" s="15" t="inlineStr">
         <is>
-          <t>why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
         </is>
       </c>
       <c r="P114" s="15" t="n"/>
       <c r="Q114" s="16" t="n"/>
       <c r="R114" s="15" t="n"/>
-      <c r="S114" s="15" t="n"/>
+      <c r="S114" s="15" t="inlineStr">
+        <is>
+          <t>NEEDS ELIAS</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:S91"/>

--- a/google-ads-skills-index.xlsx
+++ b/google-ads-skills-index.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S114"/>
+  <dimension ref="A1:S113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -3416,16 +3416,16 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="13">
       <c r="A34" s="15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Ad copy localisation vs. translation (Nordic patterns)</t>
+          <t>Improve Expected CTR</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D34" s="15" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="E34" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>Expanding to SE/NO/DK/FI or localising English-first copy</t>
+          <t>Expected CTR below average on spend-heavy keywords</t>
         </is>
       </c>
       <c r="K34" s="15" t="inlineStr">
@@ -3470,20 +3470,16 @@
       </c>
       <c r="L34" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M34" s="15" t="n"/>
       <c r="N34" s="17" t="inlineStr">
         <is>
-          <t>skills/33-nordic-localisation/</t>
-        </is>
-      </c>
-      <c r="O34" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/34-improve-expected-ctr/</t>
+        </is>
+      </c>
+      <c r="O34" s="15" t="n"/>
       <c r="P34" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3491,27 +3487,27 @@
       </c>
       <c r="Q34" s="16" t="inlineStr">
         <is>
-          <t>Not applicable until a method exists; adjacent findings depend on the 30/90 character limits.</t>
+          <t>Google changing the expected-CTR comparison set (currently exact-same-keyword, trailing 90 days) or folding assets into QS; retirement of keyword-level QS reporting.</t>
         </is>
       </c>
       <c r="R34" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S34" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="35" ht="15" customHeight="1" s="13">
       <c r="A35" s="15" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Improve Expected CTR</t>
+          <t>Improve Ad Relevance</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -3551,7 +3547,7 @@
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>Expected CTR below average on spend-heavy keywords</t>
+          <t>Ad relevance below average; keyword-to-ad mismatch</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
@@ -3567,7 +3563,7 @@
       <c r="M35" s="15" t="n"/>
       <c r="N35" s="17" t="inlineStr">
         <is>
-          <t>skills/34-improve-expected-ctr/</t>
+          <t>skills/35-improve-ad-relevance/</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -3578,12 +3574,12 @@
       </c>
       <c r="Q35" s="16" t="inlineStr">
         <is>
-          <t>Google changing the expected-CTR comparison set (currently exact-same-keyword, trailing 90 days) or folding assets into QS; retirement of keyword-level QS reporting.</t>
+          <t>Google merging ad relevance into an asset-level signal, changing the exact-same-keyword comparison set, or removing keyword-level component reporting.</t>
         </is>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S35" s="15" t="inlineStr">
@@ -3594,11 +3590,11 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="13">
       <c r="A36" s="15" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>Improve Ad Relevance</t>
+          <t>Improve Landing Page Experience</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -3638,7 +3634,7 @@
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>Ad relevance below average; keyword-to-ad mismatch</t>
+          <t>LPE below average; CPCs high relative to competitors</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
@@ -3654,7 +3650,7 @@
       <c r="M36" s="15" t="n"/>
       <c r="N36" s="17" t="inlineStr">
         <is>
-          <t>skills/35-improve-ad-relevance/</t>
+          <t>skills/36-improve-landing-page-experience/</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -3665,7 +3661,7 @@
       </c>
       <c r="Q36" s="16" t="inlineStr">
         <is>
-          <t>Google merging ad relevance into an asset-level signal, changing the exact-same-keyword comparison set, or removing keyword-level component reporting.</t>
+          <t>Google replacing crawler-based LPE with a separately reported Core Web Vitals or engagement signal, removing LPE from the keyword report, or changing the exact-same-keyword comparison set.</t>
         </is>
       </c>
       <c r="R36" s="15" t="inlineStr">
@@ -3681,11 +3677,11 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="13">
       <c r="A37" s="15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>Improve Landing Page Experience</t>
+          <t>QS tracker script (daily snapshot)</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
@@ -3695,7 +3691,7 @@
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -3705,7 +3701,7 @@
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
@@ -3715,22 +3711,22 @@
       </c>
       <c r="H37" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>LPE below average; CPCs high relative to competitors</t>
+          <t>Need QS history, which Google doesn't keep</t>
         </is>
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Brainlabs / Optmyzr</t>
         </is>
       </c>
       <c r="L37" s="15" t="inlineStr">
@@ -3741,7 +3737,7 @@
       <c r="M37" s="15" t="n"/>
       <c r="N37" s="17" t="inlineStr">
         <is>
-          <t>skills/36-improve-landing-page-experience/</t>
+          <t>skills/37-qs-tracker-script/</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -3752,12 +3748,12 @@
       </c>
       <c r="Q37" s="16" t="inlineStr">
         <is>
-          <t>Google replacing crawler-based LPE with a separately reported Core Web Vitals or engagement signal, removing LPE from the keyword report, or changing the exact-same-keyword comparison set.</t>
+          <t>Removal of quality_info from the Google Ads API/Scripts reports, a change to the Scripts 30-minute execution limit, or Google shipping native impression-weighted QS trend charts.</t>
         </is>
       </c>
       <c r="R37" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S37" s="15" t="inlineStr">
@@ -3768,11 +3764,11 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="13">
       <c r="A38" s="15" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>QS tracker script (daily snapshot)</t>
+          <t>Impression-weighted QS as the account metric</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
@@ -3782,7 +3778,7 @@
       </c>
       <c r="D38" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E38" s="15" t="inlineStr">
@@ -3792,7 +3788,7 @@
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
@@ -3802,7 +3798,7 @@
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
@@ -3812,12 +3808,12 @@
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>Need QS history, which Google doesn't keep</t>
+          <t>Reporting QS; average QS is misleading</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>Brainlabs / Optmyzr</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L38" s="15" t="inlineStr">
@@ -3828,7 +3824,7 @@
       <c r="M38" s="15" t="n"/>
       <c r="N38" s="17" t="inlineStr">
         <is>
-          <t>skills/37-qs-tracker-script/</t>
+          <t>skills/38-impression-weighted-qs/</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -3839,7 +3835,7 @@
       </c>
       <c r="Q38" s="16" t="inlineStr">
         <is>
-          <t>Removal of quality_info from the Google Ads API/Scripts reports, a change to the Scripts 30-minute execution limit, or Google shipping native impression-weighted QS trend charts.</t>
+          <t>Google publishing a native weighted account-level quality metric, removing keyword-level QS, or changing the null-QS rule.</t>
         </is>
       </c>
       <c r="R38" s="15" t="inlineStr">
@@ -3855,11 +3851,11 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="13">
       <c r="A39" s="15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Impression-weighted QS as the account metric</t>
+          <t>Does QS matter under Smart Bidding — the evidence</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
@@ -3869,7 +3865,7 @@
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
@@ -3879,7 +3875,7 @@
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
@@ -3889,22 +3885,22 @@
       </c>
       <c r="H39" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>Reporting QS; average QS is misleading</t>
+          <t>Deciding how much effort to put into QS work</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Practitioner debate</t>
         </is>
       </c>
       <c r="L39" s="15" t="inlineStr">
@@ -3915,7 +3911,7 @@
       <c r="M39" s="15" t="n"/>
       <c r="N39" s="17" t="inlineStr">
         <is>
-          <t>skills/38-impression-weighted-qs/</t>
+          <t>skills/39-qs-under-smart-bidding/</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -3926,12 +3922,12 @@
       </c>
       <c r="Q39" s="16" t="inlineStr">
         <is>
-          <t>Google publishing a native weighted account-level quality metric, removing keyword-level QS, or changing the null-QS rule.</t>
+          <t>Google publishing how Smart Bidding treats quality components, a canon cross-account study of QS work under Smart Bidding, or removal of keyword-level QS.</t>
         </is>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S39" s="15" t="inlineStr">
@@ -3942,21 +3938,21 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="13">
       <c r="A40" s="15" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>Does QS matter under Smart Bidding — the evidence</t>
+          <t>Portfolio bid strategies with max CPC caps</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
         <is>
-          <t>Quality Score</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
@@ -3971,7 +3967,7 @@
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -3981,17 +3977,17 @@
       </c>
       <c r="I40" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>Deciding how much effort to put into QS work</t>
+          <t>Smart Bidding overpaying on clicks; need a ceiling</t>
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Practitioner debate</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L40" s="15" t="inlineStr">
@@ -4002,7 +3998,7 @@
       <c r="M40" s="15" t="n"/>
       <c r="N40" s="17" t="inlineStr">
         <is>
-          <t>skills/39-qs-under-smart-bidding/</t>
+          <t>skills/40-portfolio-max-cpc-caps/</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -4013,12 +4009,12 @@
       </c>
       <c r="Q40" s="16" t="inlineStr">
         <is>
-          <t>Google publishing how Smart Bidding treats quality components, a canon cross-account study of QS work under Smart Bidding, or removal of keyword-level QS.</t>
+          <t>Google adding bid limits to standard (non-portfolio) strategies, removing them from portfolios, extending them beyond Search auctions, or reversing the 17 Aug 2026 budget-limited bidding change.</t>
         </is>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S40" s="15" t="inlineStr">
@@ -4029,11 +4025,11 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="13">
       <c r="A41" s="15" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Portfolio bid strategies with max CPC caps</t>
+          <t>Conversion value rules</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -4048,7 +4044,7 @@
       </c>
       <c r="E41" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F41" s="15" t="inlineStr">
@@ -4068,12 +4064,12 @@
       </c>
       <c r="I41" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>Smart Bidding overpaying on clicks; need a ceiling</t>
+          <t>Want tROAS to favour an audience/location/device without splitting campaigns</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
@@ -4089,7 +4085,7 @@
       <c r="M41" s="15" t="n"/>
       <c r="N41" s="17" t="inlineStr">
         <is>
-          <t>skills/40-portfolio-max-cpc-caps/</t>
+          <t>skills/41-conversion-value-rules/</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -4100,12 +4096,12 @@
       </c>
       <c r="Q41" s="16" t="inlineStr">
         <is>
-          <t>Google adding bid limits to standard (non-portfolio) strategies, removing them from portfolios, extending them beyond Search auctions, or reversing the 17 Aug 2026 budget-limited bidding change.</t>
+          <t>Google changing the multiplier range (0.5–10×), the two-dimension limit, the one-rule-per-conversion precedence, or extending rules to non-value bid strategies.</t>
         </is>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S41" s="15" t="inlineStr">
@@ -4116,11 +4112,11 @@
     </row>
     <row r="42" ht="23.25" customHeight="1" s="13">
       <c r="A42" s="15" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>Conversion value rules</t>
+          <t>Value-based bidding for lead gen (proxy values)</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -4130,7 +4126,7 @@
       </c>
       <c r="D42" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E42" s="15" t="inlineStr">
@@ -4140,7 +4136,7 @@
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
@@ -4155,17 +4151,17 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>Want tROAS to favour an audience/location/device without splitting campaigns</t>
+          <t>Lead-gen client; leads differ in quality; moving from tCPA to tROAS</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L42" s="15" t="inlineStr">
@@ -4176,7 +4172,7 @@
       <c r="M42" s="15" t="n"/>
       <c r="N42" s="17" t="inlineStr">
         <is>
-          <t>skills/41-conversion-value-rules/</t>
+          <t>skills/42-value-based-bidding-lead-gen/</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -4187,12 +4183,12 @@
       </c>
       <c r="Q42" s="16" t="inlineStr">
         <is>
-          <t>Google changing the multiplier range (0.5–10×), the two-dimension limit, the one-rule-per-conversion precedence, or extending rules to non-value bid strategies.</t>
+          <t>Google changing conversion value rules, removing Max Conversion Value without a target, changing tROAS eligibility floors, or the Data Manager API changing offline value upload.</t>
         </is>
       </c>
       <c r="R42" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S42" s="15" t="inlineStr">
@@ -4203,11 +4199,11 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="13">
       <c r="A43" s="15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Value-based bidding for lead gen (proxy values)</t>
+          <t>Micro-conversion ladder for new accounts</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -4227,12 +4223,12 @@
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
@@ -4247,7 +4243,7 @@
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>Lead-gen client; leads differ in quality; moving from tCPA to tROAS</t>
+          <t>Too few macro conversions for Smart Bidding to learn</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr">
@@ -4263,7 +4259,7 @@
       <c r="M43" s="15" t="n"/>
       <c r="N43" s="17" t="inlineStr">
         <is>
-          <t>skills/42-value-based-bidding-lead-gen/</t>
+          <t>skills/43-micro-conversion-ladder/</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -4274,12 +4270,12 @@
       </c>
       <c r="Q43" s="16" t="inlineStr">
         <is>
-          <t>Google changing conversion value rules, removing Max Conversion Value without a target, changing tROAS eligibility floors, or the Data Manager API changing offline value upload.</t>
+          <t>Google removing the primary/secondary conversion distinction, changing the Smart Bidding data floors, or retiring Maximize Clicks.</t>
         </is>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S43" s="15" t="inlineStr">
@@ -4290,11 +4286,11 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="13">
       <c r="A44" s="15" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Micro-conversion ladder for new accounts</t>
+          <t>Seasonality adjustments vs. data exclusions</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -4304,7 +4300,7 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
@@ -4314,32 +4310,32 @@
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>Too few macro conversions for Smart Bidding to learn</t>
+          <t>Short sale coming, or a tracking outage happened</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L44" s="15" t="inlineStr">
@@ -4350,7 +4346,7 @@
       <c r="M44" s="15" t="n"/>
       <c r="N44" s="17" t="inlineStr">
         <is>
-          <t>skills/43-micro-conversion-ladder/</t>
+          <t>skills/44-seasonality-adjustments-vs-data-exclusions/</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -4361,12 +4357,12 @@
       </c>
       <c r="Q44" s="16" t="inlineStr">
         <is>
-          <t>Google removing the primary/secondary conversion distinction, changing the Smart Bidding data floors, or retiring Maximize Clicks.</t>
+          <t>Google changing seasonality-adjustment duration guidance or the 0.1–10 modifier range, changing data exclusions to conversion-based rather than click-based, or new cross-account evidence that adjustments on mainstream events stopped inflating CPCs.</t>
         </is>
       </c>
       <c r="R44" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S44" s="15" t="inlineStr">
@@ -4377,11 +4373,11 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="13">
       <c r="A45" s="15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Seasonality adjustments vs. data exclusions</t>
+          <t>Target impression share for brand defence</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -4391,27 +4387,27 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I45" s="15" t="inlineStr">
@@ -4421,12 +4417,12 @@
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>Short sale coming, or a tracking outage happened</t>
+          <t>Competitors bidding on brand; deciding how to defend</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L45" s="15" t="inlineStr">
@@ -4437,7 +4433,7 @@
       <c r="M45" s="15" t="n"/>
       <c r="N45" s="17" t="inlineStr">
         <is>
-          <t>skills/44-seasonality-adjustments-vs-data-exclusions/</t>
+          <t>skills/45-target-impression-share-brand-defence/</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -4448,7 +4444,7 @@
       </c>
       <c r="Q45" s="16" t="inlineStr">
         <is>
-          <t>Google changing seasonality-adjustment duration guidance or the 0.1–10 modifier range, changing data exclusions to conversion-based rather than click-based, or new cross-account evidence that adjustments on mainstream events stopped inflating CPCs.</t>
+          <t>Google removing the bid limit from Target Impression Share, changing Ad Rank reserve pricing on uncontested auctions, or restricting competitor brand bidding by policy.</t>
         </is>
       </c>
       <c r="R45" s="15" t="inlineStr">
@@ -4464,11 +4460,11 @@
     </row>
     <row r="46" ht="15" customHeight="1" s="13">
       <c r="A46" s="15" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>Target impression share for brand defence</t>
+          <t>Bid simulator &amp; 'target too aggressive' diagnosis</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -4478,27 +4474,27 @@
       </c>
       <c r="D46" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E46" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F46" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G46" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -4508,7 +4504,7 @@
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>Competitors bidding on brand; deciding how to defend</t>
+          <t>Spend dropped after a target change; campaign underdelivering</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr">
@@ -4524,7 +4520,7 @@
       <c r="M46" s="15" t="n"/>
       <c r="N46" s="17" t="inlineStr">
         <is>
-          <t>skills/45-target-impression-share-brand-defence/</t>
+          <t>skills/46-bid-simulator-target-too-aggressive/</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -4535,7 +4531,7 @@
       </c>
       <c r="Q46" s="16" t="inlineStr">
         <is>
-          <t>Google removing the bid limit from Target Impression Share, changing Ad Rank reserve pricing on uncontested auctions, or restricting competitor brand bidding by policy.</t>
+          <t>Google changing the simulator data window or availability rules, reversing the 17 Aug 2026 budget-limited bidding change, or changing the bid strategy report's average-target reporting.</t>
         </is>
       </c>
       <c r="R46" s="15" t="inlineStr">
@@ -4551,11 +4547,11 @@
     </row>
     <row r="47" ht="15" customHeight="1" s="13">
       <c r="A47" s="15" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Bid simulator &amp; 'target too aggressive' diagnosis</t>
+          <t>Enhanced conversions — measurement uplift &amp; when it pays</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
@@ -4565,7 +4561,7 @@
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
@@ -4575,17 +4571,17 @@
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
@@ -4595,12 +4591,12 @@
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>Spend dropped after a target change; campaign underdelivering</t>
+          <t>Deciding whether the setup effort is worth it for a client</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
@@ -4611,7 +4607,7 @@
       <c r="M47" s="15" t="n"/>
       <c r="N47" s="17" t="inlineStr">
         <is>
-          <t>skills/46-bid-simulator-target-too-aggressive/</t>
+          <t>skills/47-enhanced-conversions-uplift/</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -4622,12 +4618,12 @@
       </c>
       <c r="Q47" s="16" t="inlineStr">
         <is>
-          <t>Google changing the simulator data window or availability rules, reversing the 17 Aug 2026 budget-limited bidding change, or changing the bid strategy report's average-target reporting.</t>
+          <t>Google changing the matching mechanism, removing the GCLID requirement/recommendation, changing the single on/off setting introduced April 2026, or publishing per-account uplift reporting that makes the verification protocol redundant.</t>
         </is>
       </c>
       <c r="R47" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S47" s="15" t="inlineStr">
@@ -4638,11 +4634,11 @@
     </row>
     <row r="48" ht="15" customHeight="1" s="13">
       <c r="A48" s="15" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Enhanced conversions — measurement uplift &amp; when it pays</t>
+          <t>Offline conversion import with lead stages</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
@@ -4652,7 +4648,7 @@
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
@@ -4662,12 +4658,12 @@
       </c>
       <c r="F48" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G48" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H48" s="15" t="inlineStr">
@@ -4677,12 +4673,12 @@
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>Deciding whether the setup effort is worth it for a client</t>
+          <t>B2B/long sales cycle; want Smart Bidding on SQL/closed-won</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr">
@@ -4698,7 +4694,7 @@
       <c r="M48" s="15" t="n"/>
       <c r="N48" s="17" t="inlineStr">
         <is>
-          <t>skills/47-enhanced-conversions-uplift/</t>
+          <t>skills/48-offline-conversion-import-lead-stages/</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -4709,12 +4705,12 @@
       </c>
       <c r="Q48" s="16" t="inlineStr">
         <is>
-          <t>Google changing the matching mechanism, removing the GCLID requirement/recommendation, changing the single on/off setting introduced April 2026, or publishing per-account uplift reporting that makes the verification protocol redundant.</t>
+          <t>Google changing the GCLID upload/restatement windows, the 90-day click window, Data Manager source cadences, or deprecating classic offline conversion import in favour of enhanced conversions for leads only.</t>
         </is>
       </c>
       <c r="R48" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S48" s="15" t="inlineStr">
@@ -4725,11 +4721,11 @@
     </row>
     <row r="49" ht="15" customHeight="1" s="13">
       <c r="A49" s="15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>Offline conversion import with lead stages</t>
+          <t>Conversion lag modelling</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
@@ -4739,7 +4735,7 @@
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -4749,7 +4745,7 @@
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
@@ -4759,22 +4755,22 @@
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>B2B/long sales cycle; want Smart Bidding on SQL/closed-won</t>
+          <t>Recent performance looks bad; need to adjust for lag before acting</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L49" s="15" t="inlineStr">
@@ -4785,7 +4781,7 @@
       <c r="M49" s="15" t="n"/>
       <c r="N49" s="17" t="inlineStr">
         <is>
-          <t>skills/48-offline-conversion-import-lead-stages/</t>
+          <t>skills/49-conversion-lag-modelling/</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -4796,12 +4792,12 @@
       </c>
       <c r="Q49" s="16" t="inlineStr">
         <is>
-          <t>Google changing the GCLID upload/restatement windows, the 90-day click window, Data Manager source cadences, or deprecating classic offline conversion import in favour of enhanced conversions for leads only.</t>
+          <t>Google changing conversion-time reporting or the lag-bucket segments, the 90-day click window, or how late conversions are weighted in Smart Bidding.</t>
         </is>
       </c>
       <c r="R49" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S49" s="15" t="inlineStr">
@@ -4812,31 +4808,31 @@
     </row>
     <row r="50" ht="15" customHeight="1" s="13">
       <c r="A50" s="15" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>Conversion lag modelling</t>
+          <t>RLSA layering under Smart Bidding</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Audiences</t>
         </is>
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
@@ -4846,17 +4842,17 @@
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>Recent performance looks bad; need to adjust for lag before acting</t>
+          <t>Have remarketing lists; deciding observation vs. target vs. bid adj</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
@@ -4872,7 +4868,7 @@
       <c r="M50" s="15" t="n"/>
       <c r="N50" s="17" t="inlineStr">
         <is>
-          <t>skills/49-conversion-lag-modelling/</t>
+          <t>skills/50-rlsa-layering-smart-bidding/</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -4883,7 +4879,7 @@
       </c>
       <c r="Q50" s="16" t="inlineStr">
         <is>
-          <t>Google changing conversion-time reporting or the lag-bucket segments, the 90-day click window, or how late conversions are weighted in Smart Bidding.</t>
+          <t>Google documenting that Smart Bidding honours audience bid adjustments other than -100%; removal of observation mode from Search; conversion value rules extended to tCPA/Max Conversions; Google ending automatic use of first-party lists as Search signals.</t>
         </is>
       </c>
       <c r="R50" s="15" t="inlineStr">
@@ -4899,11 +4895,11 @@
     </row>
     <row r="51" ht="15" customHeight="1" s="13">
       <c r="A51" s="15" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>RLSA layering under Smart Bidding</t>
+          <t>Customer Match as signal vs. target</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
@@ -4918,12 +4914,12 @@
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
@@ -4933,22 +4929,22 @@
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>Have remarketing lists; deciding observation vs. target vs. bid adj</t>
+          <t>Have first-party lists; deciding how to use them and refresh cadence</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L51" s="15" t="inlineStr">
@@ -4959,7 +4955,7 @@
       <c r="M51" s="15" t="n"/>
       <c r="N51" s="17" t="inlineStr">
         <is>
-          <t>skills/50-rlsa-layering-smart-bidding/</t>
+          <t>skills/51-customer-match-signal-vs-target/</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -4970,7 +4966,7 @@
       </c>
       <c r="Q51" s="16" t="inlineStr">
         <is>
-          <t>Google documenting that Smart Bidding honours audience bid adjustments other than -100%; removal of observation mode from Search; conversion value rules extended to tCPA/Max Conversions; Google ending automatic use of first-party lists as Search signals.</t>
+          <t>Google removing the account-level "Use all Customer Match lists in Smart Bidding or Optimized Targeting" opt-out; changes to the 540-day membership cap or the 100-active-members eligibility rule; Customer Match becoming usable under manual bidding.</t>
         </is>
       </c>
       <c r="R51" s="15" t="inlineStr">
@@ -4986,11 +4982,11 @@
     </row>
     <row r="52" ht="15" customHeight="1" s="13">
       <c r="A52" s="15" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>Customer Match as signal vs. target</t>
+          <t>B2B audience exclusions (demographic, in-market, HHI)</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
@@ -5000,7 +4996,7 @@
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
@@ -5010,17 +5006,17 @@
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
@@ -5030,12 +5026,12 @@
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>Have first-party lists; deciding how to use them and refresh cadence</t>
+          <t>B2B client getting consumer traffic</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L52" s="15" t="inlineStr">
@@ -5046,7 +5042,7 @@
       <c r="M52" s="15" t="n"/>
       <c r="N52" s="17" t="inlineStr">
         <is>
-          <t>skills/51-customer-match-signal-vs-target/</t>
+          <t>skills/52-b2b-audience-exclusions/</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -5057,7 +5053,7 @@
       </c>
       <c r="Q52" s="16" t="inlineStr">
         <is>
-          <t>Google removing the account-level "Use all Customer Match lists in Smart Bidding or Optimized Targeting" opt-out; changes to the 540-day membership cap or the 100-active-members eligibility rule; Customer Match becoming usable under manual bidding.</t>
+          <t>Google adding parental status, life events or custom segments to Search; HHI becoming available in European markets; Smart Bidding honouring non-(-100%) audience bid adjustments; demographics gaining an observation setting.</t>
         </is>
       </c>
       <c r="R52" s="15" t="inlineStr">
@@ -5073,11 +5069,11 @@
     </row>
     <row r="53" ht="15" customHeight="1" s="13">
       <c r="A53" s="15" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>B2B audience exclusions (demographic, in-market, HHI)</t>
+          <t>Combined segments for intent stacking</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
@@ -5102,7 +5098,7 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
@@ -5112,31 +5108,35 @@
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>B2B client getting consumer traffic</t>
+          <t>Want AND/OR/NOT audience logic for tighter targeting</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L53" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Drafting</t>
         </is>
       </c>
       <c r="M53" s="15" t="n"/>
       <c r="N53" s="17" t="inlineStr">
         <is>
-          <t>skills/52-b2b-audience-exclusions/</t>
-        </is>
-      </c>
-      <c r="O53" s="15" t="n"/>
+          <t>skills/53-combined-segments-intent-stacking/</t>
+        </is>
+      </c>
+      <c r="O53" s="15" t="inlineStr">
+        <is>
+          <t>THIN CANON stub — see SKILL.md question for Elias</t>
+        </is>
+      </c>
       <c r="P53" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5144,27 +5144,27 @@
       </c>
       <c r="Q53" s="16" t="inlineStr">
         <is>
-          <t>Google adding parental status, life events or custom segments to Search; HHI becoming available in European markets; Smart Bidding honouring non-(-100%) audience bid adjustments; demographics gaining an observation setting.</t>
+          <t>Any change to combined-segment availability by campaign type or to the AND/OR/NOT rules; Search gaining custom segments.</t>
         </is>
       </c>
       <c r="R53" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Thin</t>
         </is>
       </c>
       <c r="S53" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="13">
       <c r="A54" s="15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>Combined segments for intent stacking</t>
+          <t>GA4 first-party segments into Google Ads</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
@@ -5184,27 +5184,27 @@
       </c>
       <c r="F54" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G54" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H54" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I54" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>Want AND/OR/NOT audience logic for tighter targeting</t>
+          <t>GA4 linked; want behavioural segments as signals</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
@@ -5214,20 +5214,16 @@
       </c>
       <c r="L54" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M54" s="15" t="n"/>
       <c r="N54" s="17" t="inlineStr">
         <is>
-          <t>skills/53-combined-segments-intent-stacking/</t>
-        </is>
-      </c>
-      <c r="O54" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/54-ga4-segments-into-google-ads/</t>
+        </is>
+      </c>
+      <c r="O54" s="15" t="n"/>
       <c r="P54" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5235,32 +5231,32 @@
       </c>
       <c r="Q54" s="16" t="inlineStr">
         <is>
-          <t>Any change to combined-segment availability by campaign type or to the AND/OR/NOT rules; Search gaining custom segments.</t>
+          <t>GA4 removing the 30-day backfill or changing the 100-audience cap; GA4 Customer Match leaving beta with different mechanics; Google Ads deprecating tag-based remarketing lists; consent-mode changes to which GA4 users are exportable.</t>
         </is>
       </c>
       <c r="R54" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S54" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1" s="13">
       <c r="A55" s="15" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>GA4 first-party segments into Google Ads</t>
+          <t>PMax brand exclusions — full method</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
         <is>
-          <t>Audiences</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D55" s="15" t="inlineStr">
@@ -5270,12 +5266,12 @@
       </c>
       <c r="E55" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G55" s="15" t="inlineStr">
@@ -5290,12 +5286,12 @@
       </c>
       <c r="I55" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>GA4 linked; want behavioural segments as signals</t>
+          <t>PMax eating brand traffic and inflating ROAS</t>
         </is>
       </c>
       <c r="K55" s="15" t="inlineStr">
@@ -5311,7 +5307,7 @@
       <c r="M55" s="15" t="n"/>
       <c r="N55" s="17" t="inlineStr">
         <is>
-          <t>skills/54-ga4-segments-into-google-ads/</t>
+          <t>skills/55-pmax-brand-exclusions/</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -5322,12 +5318,12 @@
       </c>
       <c r="Q55" s="16" t="inlineStr">
         <is>
-          <t>GA4 removing the 30-day backfill or changing the 100-audience cap; GA4 Customer Match leaving beta with different mechanics; Google Ads deprecating tag-based remarketing lists; consent-mode changes to which GA4 users are exportable.</t>
+          <t>Google extending brand exclusions beyond Search, Shopping and YouTube-search inventory; a change to broad-match-based brand-list matching; removal of the "Allow Shopping ads on excluded brand searches" option; a change to the exact-match-keyword priority rule between Search and PMax.</t>
         </is>
       </c>
       <c r="R55" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S55" s="15" t="inlineStr">
@@ -5338,11 +5334,11 @@
     </row>
     <row r="56" ht="15" customHeight="1" s="13">
       <c r="A56" s="15" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>PMax brand exclusions — full method</t>
+          <t>Feed-only PMax</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
@@ -5352,7 +5348,7 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
@@ -5362,7 +5358,7 @@
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -5377,17 +5373,17 @@
       </c>
       <c r="I56" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>PMax eating brand traffic and inflating ROAS</t>
+          <t>E-com client; want Shopping-like control without creative spend</t>
         </is>
       </c>
       <c r="K56" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L56" s="15" t="inlineStr">
@@ -5398,7 +5394,7 @@
       <c r="M56" s="15" t="n"/>
       <c r="N56" s="17" t="inlineStr">
         <is>
-          <t>skills/55-pmax-brand-exclusions/</t>
+          <t>skills/56-feed-only-pmax/</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -5409,12 +5405,12 @@
       </c>
       <c r="Q56" s="16" t="inlineStr">
         <is>
-          <t>Google extending brand exclusions beyond Search, Shopping and YouTube-search inventory; a change to broad-match-based brand-list matching; removal of the "Allow Shopping ads on excluded brand searches" option; a change to the exact-match-keyword priority rule between Search and PMax.</t>
+          <t>Google removing the opt-out from auto-generated assets; a change to the channel report's "ads using product data" segmentation; deprecation of Standard Shopping as the comparison campaign.</t>
         </is>
       </c>
       <c r="R56" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S56" s="15" t="inlineStr">
@@ -5425,11 +5421,11 @@
     </row>
     <row r="57" ht="15" customHeight="1" s="13">
       <c r="A57" s="15" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>Feed-only PMax</t>
+          <t>PMax search terms insights — what you can see and mine</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
@@ -5439,7 +5435,7 @@
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -5449,7 +5445,7 @@
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
@@ -5459,22 +5455,22 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>E-com client; want Shopping-like control without creative spend</t>
+          <t>Need query-level visibility in PMax</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L57" s="15" t="inlineStr">
@@ -5485,7 +5481,7 @@
       <c r="M57" s="15" t="n"/>
       <c r="N57" s="17" t="inlineStr">
         <is>
-          <t>skills/56-feed-only-pmax/</t>
+          <t>skills/57-pmax-search-terms-insights/</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -5496,12 +5492,12 @@
       </c>
       <c r="Q57" s="16" t="inlineStr">
         <is>
-          <t>Google removing the opt-out from auto-generated assets; a change to the channel report's "ads using product data" segmentation; deprecation of Standard Shopping as the comparison campaign.</t>
+          <t>Google adding cost to term-level PMax reporting; removal of the PMax search terms report or the campaign_search_term_insight API resource; asset-group-level negatives; a change to the privacy threshold that withholds low-volume terms.</t>
         </is>
       </c>
       <c r="R57" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S57" s="15" t="inlineStr">
@@ -5512,11 +5508,11 @@
     </row>
     <row r="58" ht="15" customHeight="1" s="13">
       <c r="A58" s="15" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>PMax search terms insights — what you can see and mine</t>
+          <t>Asset groups by product vs. by audience</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -5526,7 +5522,7 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -5536,7 +5532,7 @@
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -5546,22 +5542,22 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>Need query-level visibility in PMax</t>
+          <t>Structuring a new PMax campaign</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner debate</t>
         </is>
       </c>
       <c r="L58" s="15" t="inlineStr">
@@ -5572,7 +5568,7 @@
       <c r="M58" s="15" t="n"/>
       <c r="N58" s="17" t="inlineStr">
         <is>
-          <t>skills/57-pmax-search-terms-insights/</t>
+          <t>skills/58-pmax-asset-group-structure/</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -5583,12 +5579,12 @@
       </c>
       <c r="Q58" s="16" t="inlineStr">
         <is>
-          <t>Google adding cost to term-level PMax reporting; removal of the PMax search terms report or the campaign_search_term_insight API resource; asset-group-level negatives; a change to the privacy threshold that withholds low-volume terms.</t>
+          <t>Google making audience signals hard targets; asset-group-level bidding targets; changes to listing-group mechanics.</t>
         </is>
       </c>
       <c r="R58" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S58" s="15" t="inlineStr">
@@ -5599,11 +5595,11 @@
     </row>
     <row r="59" ht="15" customHeight="1" s="13">
       <c r="A59" s="15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>Asset groups by product vs. by audience</t>
+          <t>PMax cannibalising brand/Search — diagnosis</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
@@ -5613,7 +5609,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
@@ -5623,32 +5619,32 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>Structuring a new PMax campaign</t>
+          <t>Search performance fell after PMax launch</t>
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr">
         <is>
-          <t>Practitioner debate</t>
+          <t>Mike Rhodes script + practitioner</t>
         </is>
       </c>
       <c r="L59" s="15" t="inlineStr">
@@ -5659,7 +5655,7 @@
       <c r="M59" s="15" t="n"/>
       <c r="N59" s="17" t="inlineStr">
         <is>
-          <t>skills/58-pmax-asset-group-structure/</t>
+          <t>skills/59-pmax-cannibalisation-diagnosis/</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -5670,12 +5666,12 @@
       </c>
       <c r="Q59" s="16" t="inlineStr">
         <is>
-          <t>Google making audience signals hard targets; asset-group-level bidding targets; changes to listing-group mechanics.</t>
+          <t>A change to the rule that an identical Search keyword takes precedence over PMax; cost appearing in the PMax search terms report; Google shipping Search-vs-PMax or channel-level controls; removal of the PMax search terms report.</t>
         </is>
       </c>
       <c r="R59" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S59" s="15" t="inlineStr">
@@ -5686,11 +5682,11 @@
     </row>
     <row r="60" ht="15" customHeight="1" s="13">
       <c r="A60" s="15" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>PMax cannibalising brand/Search — diagnosis</t>
+          <t>PMax placement exclusions &amp; display/video spend</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
@@ -5700,7 +5696,7 @@
       </c>
       <c r="D60" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E60" s="15" t="inlineStr">
@@ -5710,12 +5706,12 @@
       </c>
       <c r="F60" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H60" s="15" t="inlineStr">
@@ -5725,17 +5721,17 @@
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>Search performance fell after PMax launch</t>
+          <t>Too much PMax spend going to low-quality placements</t>
         </is>
       </c>
       <c r="K60" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes script + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L60" s="15" t="inlineStr">
@@ -5746,7 +5742,7 @@
       <c r="M60" s="15" t="n"/>
       <c r="N60" s="17" t="inlineStr">
         <is>
-          <t>skills/59-pmax-cannibalisation-diagnosis/</t>
+          <t>skills/60-pmax-placement-exclusions/</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -5757,7 +5753,7 @@
       </c>
       <c r="Q60" s="16" t="inlineStr">
         <is>
-          <t>A change to the rule that an identical Search keyword takes precedence over PMax; cost appearing in the PMax search terms report; Google shipping Search-vs-PMax or channel-level controls; removal of the PMax search terms report.</t>
+          <t>Campaign-level placement exclusions or channel-level budget/bid controls in PMax; cost appearing in the PMax placement report; a change to the account-level exclusion scope.</t>
         </is>
       </c>
       <c r="R60" s="15" t="inlineStr">
@@ -5773,11 +5769,11 @@
     </row>
     <row r="61" ht="15" customHeight="1" s="13">
       <c r="A61" s="15" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>PMax placement exclusions &amp; display/video spend</t>
+          <t>URL expansion off + final URL control</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
@@ -5787,7 +5783,7 @@
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
@@ -5797,7 +5793,7 @@
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G61" s="15" t="inlineStr">
@@ -5807,7 +5803,7 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I61" s="15" t="inlineStr">
@@ -5817,12 +5813,12 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>Too much PMax spend going to low-quality placements</t>
+          <t>PMax sending traffic to unintended pages</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L61" s="15" t="inlineStr">
@@ -5833,7 +5829,7 @@
       <c r="M61" s="15" t="n"/>
       <c r="N61" s="17" t="inlineStr">
         <is>
-          <t>skills/60-pmax-placement-exclusions/</t>
+          <t>skills/61-pmax-url-expansion/</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -5844,12 +5840,12 @@
       </c>
       <c r="Q61" s="16" t="inlineStr">
         <is>
-          <t>Campaign-level placement exclusions or channel-level budget/bid controls in PMax; cost appearing in the PMax placement report; a change to the account-level exclusion scope.</t>
+          <t>A change to the default-on setting; the ability to exclude the campaign's own final URL or homepage; expansion folding into AI Max page controls; removal of page feeds from PMax.</t>
         </is>
       </c>
       <c r="R61" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S61" s="15" t="inlineStr">
@@ -5860,11 +5856,11 @@
     </row>
     <row r="62" ht="15" customHeight="1" s="13">
       <c r="A62" s="15" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>URL expansion off + final URL control</t>
+          <t>PMax campaign-level negatives</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
@@ -5874,7 +5870,7 @@
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
@@ -5884,7 +5880,7 @@
       </c>
       <c r="F62" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G62" s="15" t="inlineStr">
@@ -5894,22 +5890,22 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>PMax sending traffic to unintended pages</t>
+          <t>Irrelevant queries visible in PMax insights</t>
         </is>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Google docs (recent feature)</t>
         </is>
       </c>
       <c r="L62" s="15" t="inlineStr">
@@ -5920,7 +5916,7 @@
       <c r="M62" s="15" t="n"/>
       <c r="N62" s="17" t="inlineStr">
         <is>
-          <t>skills/61-pmax-url-expansion/</t>
+          <t>skills/62-pmax-campaign-negatives/</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -5931,12 +5927,12 @@
       </c>
       <c r="Q62" s="16" t="inlineStr">
         <is>
-          <t>A change to the default-on setting; the ability to exclude the campaign's own final URL or homepage; expansion folding into AI Max page controls; removal of page feeds from PMax.</t>
+          <t>PMax negatives extending to Display, Video or Discover inventory; asset-group-level negatives; a change to the 10,000-per-campaign or 1,000-per-account limits; removal of the PMax search terms report.</t>
         </is>
       </c>
       <c r="R62" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S62" s="15" t="inlineStr">
@@ -5947,11 +5943,11 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="13">
       <c r="A63" s="15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>PMax campaign-level negatives</t>
+          <t>New customer acquisition goal — definition problem</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
@@ -5961,7 +5957,7 @@
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
@@ -5971,32 +5967,32 @@
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Irrelevant queries visible in PMax insights</t>
+          <t>Client wants to bid higher for new customers</t>
         </is>
       </c>
       <c r="K63" s="15" t="inlineStr">
         <is>
-          <t>Google docs (recent feature)</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L63" s="15" t="inlineStr">
@@ -6007,7 +6003,7 @@
       <c r="M63" s="15" t="n"/>
       <c r="N63" s="17" t="inlineStr">
         <is>
-          <t>skills/62-pmax-campaign-negatives/</t>
+          <t>skills/63-pmax-new-customer-acquisition/</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -6018,12 +6014,12 @@
       </c>
       <c r="Q63" s="16" t="inlineStr">
         <is>
-          <t>PMax negatives extending to Display, Video or Discover inventory; asset-group-level negatives; a change to the 10,000-per-campaign or 1,000-per-account limits; removal of the PMax search terms report.</t>
+          <t>A change to the 540-day auto-detection window; removal of the Original conv. value column; the premium becoming bidding-only (non-reporting); in-platform incrementality testing for lifecycle goals; removal of New Customer Only mode.</t>
         </is>
       </c>
       <c r="R63" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S63" s="15" t="inlineStr">
@@ -6034,31 +6030,31 @@
     </row>
     <row r="64" ht="15" customHeight="1" s="13">
       <c r="A64" s="15" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>New customer acquisition goal — definition problem</t>
+          <t>Custom labels by margin / stock / seasonality</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D64" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E64" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F64" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G64" s="15" t="inlineStr">
@@ -6073,17 +6069,17 @@
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>Client wants to bid higher for new customers</t>
+          <t>Want bidding tiers by profitability or availability</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L64" s="15" t="inlineStr">
@@ -6094,7 +6090,7 @@
       <c r="M64" s="15" t="n"/>
       <c r="N64" s="17" t="inlineStr">
         <is>
-          <t>skills/63-pmax-new-customer-acquisition/</t>
+          <t>skills/64-custom-labels-margin-stock-season/</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -6105,12 +6101,12 @@
       </c>
       <c r="Q64" s="16" t="inlineStr">
         <is>
-          <t>A change to the 540-day auto-detection window; removal of the Original conv. value column; the premium becoming bidding-only (non-reporting); in-platform incrementality testing for lifecycle goals; removal of New Customer Only mode.</t>
+          <t>Google changing the 5-label or 1,000-value caps, removing custom labels from PMax/AI Max listing groups, or dropping supplemental data sources from Merchant Center Next.</t>
         </is>
       </c>
       <c r="R64" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S64" s="15" t="inlineStr">
@@ -6121,11 +6117,11 @@
     </row>
     <row r="65" ht="15" customHeight="1" s="13">
       <c r="A65" s="15" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>Custom labels by margin / stock / seasonality</t>
+          <t>Feed rules &amp; supplemental feeds</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
@@ -6150,27 +6146,27 @@
       </c>
       <c r="G65" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>Want bidding tiers by profitability or availability</t>
+          <t>Need to change titles/attributes without touching the source feed</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
@@ -6181,7 +6177,7 @@
       <c r="M65" s="15" t="n"/>
       <c r="N65" s="17" t="inlineStr">
         <is>
-          <t>skills/64-custom-labels-margin-stock-season/</t>
+          <t>skills/65-feed-rules-supplemental-feeds/</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -6192,12 +6188,12 @@
       </c>
       <c r="Q65" s="16" t="inlineStr">
         <is>
-          <t>Google changing the 5-label or 1,000-value caps, removing custom labels from PMax/AI Max listing groups, or dropping supplemental data sources from Merchant Center Next.</t>
+          <t>Google removing supplemental sources or attribute rules from Merchant Center Next, dropping the Advanced data source management add-on, making id matching case-insensitive, or lifting the once-a-day scheduled-fetch limit.</t>
         </is>
       </c>
       <c r="R65" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S65" s="15" t="inlineStr">
@@ -6208,11 +6204,11 @@
     </row>
     <row r="66" ht="15" customHeight="1" s="13">
       <c r="A66" s="15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>Feed rules &amp; supplemental feeds</t>
+          <t>Title structure research — what moves CTR</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
@@ -6222,7 +6218,7 @@
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
@@ -6242,7 +6238,7 @@
       </c>
       <c r="H66" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I66" s="15" t="inlineStr">
@@ -6252,12 +6248,12 @@
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>Need to change titles/attributes without touching the source feed</t>
+          <t>Shopping CTR low; titles are generic</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Industry studies</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
@@ -6268,7 +6264,7 @@
       <c r="M66" s="15" t="n"/>
       <c r="N66" s="17" t="inlineStr">
         <is>
-          <t>skills/65-feed-rules-supplemental-feeds/</t>
+          <t>skills/66-title-structure-research/</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -6279,7 +6275,7 @@
       </c>
       <c r="Q66" s="16" t="inlineStr">
         <is>
-          <t>Google removing supplemental sources or attribute rules from Merchant Center Next, dropping the Advanced data source management add-on, making id matching case-insensitive, or lifting the once-a-day scheduled-fetch limit.</t>
+          <t>Google changing the ~70-character displayed cut-off or the 150-character title limit, AI Max / dynamic titles overriding merchant titles by default, or Merchant Center removing attribute rules and supplemental sources (the test mechanism).</t>
         </is>
       </c>
       <c r="R66" s="15" t="inlineStr">
@@ -6295,11 +6291,11 @@
     </row>
     <row r="67" ht="15" customHeight="1" s="13">
       <c r="A67" s="15" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Title structure research — what moves CTR</t>
+          <t>Merchant Center diagnostics &amp; disapproval patterns</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
@@ -6309,7 +6305,7 @@
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
@@ -6319,7 +6315,7 @@
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G67" s="15" t="inlineStr">
@@ -6329,7 +6325,7 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="I67" s="15" t="inlineStr">
@@ -6339,12 +6335,12 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>Shopping CTR low; titles are generic</t>
+          <t>Products disapproved or limited</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>Industry studies</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
@@ -6355,7 +6351,7 @@
       <c r="M67" s="15" t="n"/>
       <c r="N67" s="17" t="inlineStr">
         <is>
-          <t>skills/66-title-structure-research/</t>
+          <t>skills/67-merchant-center-diagnostics/</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -6366,7 +6362,7 @@
       </c>
       <c r="Q67" s="16" t="inlineStr">
         <is>
-          <t>Google changing the ~70-character displayed cut-off or the 150-character title limit, AI Max / dynamic titles overriding merchant titles by default, or Merchant Center removing attribute rules and supplemental sources (the test mechanism).</t>
+          <t>Google changing the misrepresentation warning windows (7/28 days) or 7-business-day review, removing the Content API product-status endpoint, or moving diagnostics wholly into Google Ads with a different issue taxonomy.</t>
         </is>
       </c>
       <c r="R67" s="15" t="inlineStr">
@@ -6382,11 +6378,11 @@
     </row>
     <row r="68" ht="15" customHeight="1" s="13">
       <c r="A68" s="15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Merchant Center diagnostics &amp; disapproval patterns</t>
+          <t>Shopping query sculpting via priority + negatives</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
@@ -6396,7 +6392,7 @@
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
@@ -6406,17 +6402,17 @@
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
@@ -6426,12 +6422,12 @@
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>Products disapproved or limited</t>
+          <t>Want generic vs. brand vs. product queries in separate campaigns</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
@@ -6442,7 +6438,7 @@
       <c r="M68" s="15" t="n"/>
       <c r="N68" s="17" t="inlineStr">
         <is>
-          <t>skills/67-merchant-center-diagnostics/</t>
+          <t>skills/68-shopping-query-sculpting/</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -6453,12 +6449,12 @@
       </c>
       <c r="Q68" s="16" t="inlineStr">
         <is>
-          <t>Google changing the misrepresentation warning windows (7/28 days) or 7-business-day review, removing the Content API product-status endpoint, or moving diagnostics wholly into Google Ads with a different issue taxonomy.</t>
+          <t>Google removing campaign priority from Standard Shopping, forcing PMax precedence without brand exclusions, removing shared budgets, or AI Max for Shopping replacing keyword-free matching with its own query rules.</t>
         </is>
       </c>
       <c r="R68" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S68" s="15" t="inlineStr">
@@ -6469,56 +6465,56 @@
     </row>
     <row r="69" ht="15" customHeight="1" s="13">
       <c r="A69" s="15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>Shopping query sculpting via priority + negatives</t>
+          <t>PMax insights script</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D69" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G69" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H69" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>Want generic vs. brand vs. product queries in separate campaigns</t>
+          <t>Running PMax; need channel/placement/query breakdown</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Mike Rhodes</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
@@ -6529,7 +6525,7 @@
       <c r="M69" s="15" t="n"/>
       <c r="N69" s="17" t="inlineStr">
         <is>
-          <t>skills/68-shopping-query-sculpting/</t>
+          <t>skills/69-pmax-insights-script/</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -6540,7 +6536,7 @@
       </c>
       <c r="Q69" s="16" t="inlineStr">
         <is>
-          <t>Google removing campaign priority from Standard Shopping, forcing PMax precedence without brand exclusions, removing shared budgets, or AI Max for Shopping replacing keyword-free matching with its own query rules.</t>
+          <t>Google exposing channel-level spend, cost-bearing search terms and placement cost natively in the PMax UI/API; deprecation of campaign_search_term_insight or performance_max_placement_view; Google Ads Scripts API-version sunsets breaking the queries.</t>
         </is>
       </c>
       <c r="R69" s="15" t="inlineStr">
@@ -6556,11 +6552,11 @@
     </row>
     <row r="70" ht="15" customHeight="1" s="13">
       <c r="A70" s="15" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>PMax insights script</t>
+          <t>N-gram script</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -6575,7 +6571,7 @@
       </c>
       <c r="E70" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F70" s="15" t="inlineStr">
@@ -6600,12 +6596,12 @@
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>Running PMax; need channel/placement/query breakdown</t>
+          <t>Want automated n-gram output for search terms</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes</t>
+          <t>Nils Rooijmans / Brainlabs</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
@@ -6616,7 +6612,7 @@
       <c r="M70" s="15" t="n"/>
       <c r="N70" s="17" t="inlineStr">
         <is>
-          <t>skills/69-pmax-insights-script/</t>
+          <t>skills/70-n-gram-script/</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -6627,7 +6623,7 @@
       </c>
       <c r="Q70" s="16" t="inlineStr">
         <is>
-          <t>Google exposing channel-level spend, cost-bearing search terms and placement cost natively in the PMax UI/API; deprecation of campaign_search_term_insight or performance_max_placement_view; Google Ads Scripts API-version sunsets breaking the queries.</t>
+          <t>Further privacy-thresholding of the search terms report; removal of search_term_view or campaign_search_term_insight from the Scripts runtime; API-version sunsets breaking the GAQL.</t>
         </is>
       </c>
       <c r="R70" s="15" t="inlineStr">
@@ -6643,11 +6639,11 @@
     </row>
     <row r="71" ht="15" customHeight="1" s="13">
       <c r="A71" s="15" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>N-gram script</t>
+          <t>Budget pacing script</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
@@ -6662,7 +6658,7 @@
       </c>
       <c r="E71" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F71" s="15" t="inlineStr">
@@ -6682,17 +6678,17 @@
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>Want automated n-gram output for search terms</t>
+          <t>Monthly budgets; need over/under-pacing alerts</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
         <is>
-          <t>Nils Rooijmans / Brainlabs</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L71" s="15" t="inlineStr">
@@ -6703,7 +6699,7 @@
       <c r="M71" s="15" t="n"/>
       <c r="N71" s="17" t="inlineStr">
         <is>
-          <t>skills/70-n-gram-script/</t>
+          <t>skills/71-budget-pacing-script/</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -6714,12 +6710,12 @@
       </c>
       <c r="Q71" s="16" t="inlineStr">
         <is>
-          <t>Further privacy-thresholding of the search terms report; removal of search_term_view or campaign_search_term_insight from the Scripts runtime; API-version sunsets breaking the GAQL.</t>
+          <t>Google changing the 2x-daily / 30.4x-monthly overdelivery rules or adding true monthly budgets to all campaign types; Scripts exposing cost for PMax/Demand Gen in the campaign iterator; GAQL version sunsets.</t>
         </is>
       </c>
       <c r="R71" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S71" s="15" t="inlineStr">
@@ -6730,11 +6726,11 @@
     </row>
     <row r="72" ht="15" customHeight="1" s="13">
       <c r="A72" s="15" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Budget pacing script</t>
+          <t>Anomaly detector script</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -6774,7 +6770,7 @@
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>Monthly budgets; need over/under-pacing alerts</t>
+          <t>Want alerts on sudden spend/CPA/conv changes</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
@@ -6790,7 +6786,7 @@
       <c r="M72" s="15" t="n"/>
       <c r="N72" s="17" t="inlineStr">
         <is>
-          <t>skills/71-budget-pacing-script/</t>
+          <t>skills/72-anomaly-detector-script/</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -6801,7 +6797,7 @@
       </c>
       <c r="Q72" s="16" t="inlineStr">
         <is>
-          <t>Google changing the 2x-daily / 30.4x-monthly overdelivery rules or adding true monthly budgets to all campaign types; Scripts exposing cost for PMax/Demand Gen in the campaign iterator; GAQL version sunsets.</t>
+          <t>Deprecation of search_term_view or change_event in Scripts; Scripts frequency or runtime limits changing; Google removing or re-pinning the Account Anomaly Detector solution.</t>
         </is>
       </c>
       <c r="R72" s="15" t="inlineStr">
@@ -6817,11 +6813,11 @@
     </row>
     <row r="73" ht="15" customHeight="1" s="13">
       <c r="A73" s="15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>Anomaly detector script</t>
+          <t>404 / broken URL checker</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
@@ -6861,7 +6857,7 @@
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>Want alerts on sudden spend/CPA/conv changes</t>
+          <t>Large site or frequent page changes</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
@@ -6877,7 +6873,7 @@
       <c r="M73" s="15" t="n"/>
       <c r="N73" s="17" t="inlineStr">
         <is>
-          <t>skills/72-anomaly-detector-script/</t>
+          <t>skills/73-broken-url-checker-script/</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -6888,7 +6884,7 @@
       </c>
       <c r="Q73" s="16" t="inlineStr">
         <is>
-          <t>Deprecation of search_term_view or change_event in Scripts; Scripts frequency or runtime limits changing; Google removing or re-pinning the Account Anomaly Detector solution.</t>
+          <t>Removal or quota reduction of UrlFetchApp in Scripts; Google making "Destination not working" disapprovals immediate and complete; removal of PMax final URL expansion.</t>
         </is>
       </c>
       <c r="R73" s="15" t="inlineStr">
@@ -6904,11 +6900,11 @@
     </row>
     <row r="74" ht="15" customHeight="1" s="13">
       <c r="A74" s="15" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>404 / broken URL checker</t>
+          <t>Negative keyword conflict script</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6923,7 +6919,7 @@
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
@@ -6948,7 +6944,7 @@
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>Large site or frequent page changes</t>
+          <t>Many negative lists; want automated conflict checks</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
@@ -6964,7 +6960,7 @@
       <c r="M74" s="15" t="n"/>
       <c r="N74" s="17" t="inlineStr">
         <is>
-          <t>skills/73-broken-url-checker-script/</t>
+          <t>skills/74-negative-keyword-conflict-script/</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -6975,7 +6971,7 @@
       </c>
       <c r="Q74" s="16" t="inlineStr">
         <is>
-          <t>Removal or quota reduction of UrlFetchApp in Scripts; Google making "Destination not working" disapprovals immediate and complete; removal of PMax final URL expansion.</t>
+          <t>Google applying close variants to negative keywords; removal of shared negative lists or keyword_view; GAQL paging changes that push the script's 250k/50k limits.</t>
         </is>
       </c>
       <c r="R74" s="15" t="inlineStr">
@@ -6991,11 +6987,11 @@
     </row>
     <row r="75" ht="15" customHeight="1" s="13">
       <c r="A75" s="15" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Negative keyword conflict script</t>
+          <t>Ad disapproval alert script</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -7010,7 +7006,7 @@
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
@@ -7030,12 +7026,12 @@
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>Many negative lists; want automated conflict checks</t>
+          <t>Compliance-sensitive vertical; disapprovals go unnoticed</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
@@ -7051,7 +7047,7 @@
       <c r="M75" s="15" t="n"/>
       <c r="N75" s="17" t="inlineStr">
         <is>
-          <t>skills/74-negative-keyword-conflict-script/</t>
+          <t>skills/75-ad-disapproval-alert-script/</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -7062,7 +7058,7 @@
       </c>
       <c r="Q75" s="16" t="inlineStr">
         <is>
-          <t>Google applying close variants to negative keywords; removal of shared negative lists or keyword_view; GAQL paging changes that push the script's 250k/50k limits.</t>
+          <t>Changes to ad_group_ad.policy_summary fields or policy topic naming; Shopping Content API deprecation in favour of the Merchant API; Google adding reliable notifications for past-violation and limited statuses.</t>
         </is>
       </c>
       <c r="R75" s="15" t="inlineStr">
@@ -7078,11 +7074,11 @@
     </row>
     <row r="76" ht="15" customHeight="1" s="13">
       <c r="A76" s="15" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>Ad disapproval alert script</t>
+          <t>Search term wasted-spend script</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
@@ -7097,7 +7093,7 @@
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
@@ -7117,12 +7113,12 @@
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>Compliance-sensitive vertical; disapprovals go unnoticed</t>
+          <t>Want a weekly list of zero-conversion spend by query</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
@@ -7138,7 +7134,7 @@
       <c r="M76" s="15" t="n"/>
       <c r="N76" s="17" t="inlineStr">
         <is>
-          <t>skills/75-ad-disapproval-alert-script/</t>
+          <t>skills/76-search-term-wasted-spend-script/</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -7149,12 +7145,12 @@
       </c>
       <c r="Q76" s="16" t="inlineStr">
         <is>
-          <t>Changes to ad_group_ad.policy_summary fields or policy topic naming; Shopping Content API deprecation in favour of the Merchant API; Google adding reliable notifications for past-violation and limited statuses.</t>
+          <t>Further privacy-thresholding of search_term_view; Google applying close variants to negatives; removal of campaign-level PMax negatives; API-version sunsets.</t>
         </is>
       </c>
       <c r="R76" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S76" s="15" t="inlineStr">
@@ -7165,11 +7161,11 @@
     </row>
     <row r="77" ht="15" customHeight="1" s="13">
       <c r="A77" s="15" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Search term wasted-spend script</t>
+          <t>Automated rules vs. scripts — when each</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
@@ -7179,12 +7175,12 @@
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
@@ -7204,17 +7200,17 @@
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Want a weekly list of zero-conversion spend by query</t>
+          <t>Deciding how to automate a recurring action</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
@@ -7225,7 +7221,7 @@
       <c r="M77" s="15" t="n"/>
       <c r="N77" s="17" t="inlineStr">
         <is>
-          <t>skills/76-search-term-wasted-spend-script/</t>
+          <t>skills/77-automated-rules-vs-scripts/</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -7236,7 +7232,7 @@
       </c>
       <c r="Q77" s="16" t="inlineStr">
         <is>
-          <t>Further privacy-thresholding of search_term_view; Google applying close variants to negatives; removal of campaign-level PMax negatives; API-version sunsets.</t>
+          <t>Google removing Automated Rules or folding them into agentic features; Scripts limits changing (30 min, hourly, 250/account); the Ads API gaining native agent tooling that collapses the scripts-as-data layer.</t>
         </is>
       </c>
       <c r="R77" s="15" t="inlineStr">
@@ -7252,11 +7248,11 @@
     </row>
     <row r="78" ht="15" customHeight="1" s="13">
       <c r="A78" s="15" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Automated rules vs. scripts — when each</t>
+          <t>Recommendations tab — auto-apply opt-out &amp; dismiss list</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
@@ -7266,7 +7262,7 @@
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
@@ -7276,7 +7272,7 @@
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -7291,12 +7287,12 @@
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>Deciding how to automate a recurring action</t>
+          <t>New or inherited account; prevent Google auto-applying changes</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
@@ -7312,7 +7308,7 @@
       <c r="M78" s="15" t="n"/>
       <c r="N78" s="17" t="inlineStr">
         <is>
-          <t>skills/77-automated-rules-vs-scripts/</t>
+          <t>skills/78-recommendations-auto-apply-opt-out/</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -7323,7 +7319,7 @@
       </c>
       <c r="Q78" s="16" t="inlineStr">
         <is>
-          <t>Google removing Automated Rules or folding them into agentic features; Scripts limits changing (30 min, hourly, 250/account); the Ads API gaining native agent tooling that collapses the scripts-as-data layer.</t>
+          <t>Google removing auto-apply as a per-account setting; Google extending system bulk changes beyond low-activity keywords and ad groups; changes to change_event retention or the 10k-row cap that break the monitoring script.</t>
         </is>
       </c>
       <c r="R78" s="15" t="inlineStr">
@@ -7339,41 +7335,41 @@
     </row>
     <row r="79" ht="15" customHeight="1" s="13">
       <c r="A79" s="15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Recommendations tab — auto-apply opt-out &amp; dismiss list</t>
+          <t>Custom experiments — split, duration, valid win</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
@@ -7383,12 +7379,12 @@
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>New or inherited account; prevent Google auto-applying changes</t>
+          <t>Want to test a bid strategy, structure or landing page properly</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
@@ -7399,7 +7395,7 @@
       <c r="M79" s="15" t="n"/>
       <c r="N79" s="17" t="inlineStr">
         <is>
-          <t>skills/78-recommendations-auto-apply-opt-out/</t>
+          <t>skills/79-custom-experiments/</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -7410,12 +7406,12 @@
       </c>
       <c r="Q79" s="16" t="inlineStr">
         <is>
-          <t>Google removing auto-apply as a per-account setting; Google extending system bulk changes beyond low-activity keywords and ad groups; changes to change_event retention or the 10k-row cap that break the monitoring script.</t>
+          <t>Changes to the 7-day ramp-up exclusion, the 80% default confidence display, budget-vs-traffic split rules per campaign type, or replacement of custom experiments by Google-recommended / multi-campaign experiments only.</t>
         </is>
       </c>
       <c r="R79" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S79" s="15" t="inlineStr">
@@ -7426,11 +7422,11 @@
     </row>
     <row r="80" ht="15" customHeight="1" s="13">
       <c r="A80" s="15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Custom experiments — split, duration, valid win</t>
+          <t>Geo experiments / conversion lift</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -7445,12 +7441,12 @@
       </c>
       <c r="E80" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F80" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G80" s="15" t="inlineStr">
@@ -7465,12 +7461,12 @@
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>Want to test a bid strategy, structure or landing page properly</t>
+          <t>Need incrementality evidence for a channel or campaign</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
@@ -7486,7 +7482,7 @@
       <c r="M80" s="15" t="n"/>
       <c r="N80" s="17" t="inlineStr">
         <is>
-          <t>skills/79-custom-experiments/</t>
+          <t>skills/80-geo-experiments-conversion-lift/</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -7497,7 +7493,7 @@
       </c>
       <c r="Q80" s="16" t="inlineStr">
         <is>
-          <t>Changes to the 7-day ramp-up exclusion, the 80% default confidence display, budget-vs-traffic split rules per campaign type, or replacement of custom experiments by Google-recommended / multi-campaign experiments only.</t>
+          <t>Changes to Conversion Lift minimums ($5k budget, 1,000 conversions, 14 days), the certainty selector, geo-based study availability, how projected cooldown conversions are included, or Google exposing/removing the priors behind its Bayesian lift estimates.</t>
         </is>
       </c>
       <c r="R80" s="15" t="inlineStr">
@@ -7513,11 +7509,11 @@
     </row>
     <row r="81" ht="15" customHeight="1" s="13">
       <c r="A81" s="15" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Geo experiments / conversion lift</t>
+          <t>Brand incrementality test</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -7532,7 +7528,7 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
@@ -7557,12 +7553,12 @@
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>Need incrementality evidence for a channel or campaign</t>
+          <t>Question whether brand spend is incremental</t>
         </is>
       </c>
       <c r="K81" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L81" s="15" t="inlineStr">
@@ -7573,7 +7569,7 @@
       <c r="M81" s="15" t="n"/>
       <c r="N81" s="17" t="inlineStr">
         <is>
-          <t>skills/80-geo-experiments-conversion-lift/</t>
+          <t>skills/81-brand-incrementality-test/</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -7584,7 +7580,7 @@
       </c>
       <c r="Q81" s="16" t="inlineStr">
         <is>
-          <t>Changes to Conversion Lift minimums ($5k budget, 1,000 conversions, 14 days), the certainty selector, geo-based study availability, how projected cooldown conversions are included, or Google exposing/removing the priors behind its Bayesian lift estimates.</t>
+          <t>Removal or change of PMax brand exclusions / Search brand lists; changes to Conversion Lift minimums; Google altering serving preference between exact-match keywords and PMax for brand queries.</t>
         </is>
       </c>
       <c r="R81" s="15" t="inlineStr">
@@ -7600,11 +7596,11 @@
     </row>
     <row r="82" ht="15" customHeight="1" s="13">
       <c r="A82" s="15" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Brand incrementality test</t>
+          <t>Statistical significance for ad tests</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -7614,22 +7610,22 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -7644,7 +7640,7 @@
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>Question whether brand spend is incremental</t>
+          <t>Calling winners in RSA/landing page tests</t>
         </is>
       </c>
       <c r="K82" s="15" t="inlineStr">
@@ -7660,7 +7656,7 @@
       <c r="M82" s="15" t="n"/>
       <c r="N82" s="17" t="inlineStr">
         <is>
-          <t>skills/81-brand-incrementality-test/</t>
+          <t>skills/82-statistical-significance-ad-tests/</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -7671,12 +7667,12 @@
       </c>
       <c r="Q82" s="16" t="inlineStr">
         <is>
-          <t>Removal or change of PMax brand exclusions / Search brand lists; changes to Conversion Lift minimums; Google altering serving preference between exact-match keywords and PMax for brand queries.</t>
+          <t>Google removing "Do not optimize" rotation entirely; changes to RSA asset limits (15/4) or pinning rules; a documented significance method in ad variations; mandatory final URL expansion or AI Max text customisation breaking ad-vs-ad comparability.</t>
         </is>
       </c>
       <c r="R82" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S82" s="15" t="inlineStr">
@@ -7687,11 +7683,11 @@
     </row>
     <row r="83" ht="15" customHeight="1" s="13">
       <c r="A83" s="15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Statistical significance for ad tests</t>
+          <t>Auction insights trend reading</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
@@ -7701,17 +7697,17 @@
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
@@ -7721,7 +7717,7 @@
       </c>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I83" s="15" t="inlineStr">
@@ -7731,7 +7727,7 @@
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>Calling winners in RSA/landing page tests</t>
+          <t>Performance shift with no internal change; suspect competitors</t>
         </is>
       </c>
       <c r="K83" s="15" t="inlineStr">
@@ -7747,7 +7743,7 @@
       <c r="M83" s="15" t="n"/>
       <c r="N83" s="17" t="inlineStr">
         <is>
-          <t>skills/82-statistical-significance-ad-tests/</t>
+          <t>skills/83-auction-insights-trend-reading/</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -7758,12 +7754,12 @@
       </c>
       <c r="Q83" s="16" t="inlineStr">
         <is>
-          <t>Google removing "Do not optimize" rotation entirely; changes to RSA asset limits (15/4) or pinning rules; a documented significance method in ad variations; mandatory final URL expansion or AI Max text customisation breaking ad-vs-ad comparability.</t>
+          <t>Google changing auction-insights metric definitions, the 10% IS display floor, or time segmentation; removal of keyword-level auction insights under keywordless Search.</t>
         </is>
       </c>
       <c r="R83" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S83" s="15" t="inlineStr">
@@ -7774,11 +7770,11 @@
     </row>
     <row r="84" ht="15" customHeight="1" s="13">
       <c r="A84" s="15" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>Auction insights trend reading</t>
+          <t>Impression share decomposition decision rule</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
@@ -7793,7 +7789,7 @@
       </c>
       <c r="E84" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F84" s="15" t="inlineStr">
@@ -7813,12 +7809,12 @@
       </c>
       <c r="I84" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>Performance shift with no internal change; suspect competitors</t>
+          <t>Lost IS; deciding budget vs. bid vs. QS action</t>
         </is>
       </c>
       <c r="K84" s="15" t="inlineStr">
@@ -7834,7 +7830,7 @@
       <c r="M84" s="15" t="n"/>
       <c r="N84" s="17" t="inlineStr">
         <is>
-          <t>skills/83-auction-insights-trend-reading/</t>
+          <t>skills/84-impression-share-decomposition/</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -7845,12 +7841,12 @@
       </c>
       <c r="Q84" s="16" t="inlineStr">
         <is>
-          <t>Google changing auction-insights metric definitions, the 10% IS display floor, or time segmentation; removal of keyword-level auction insights under keywordless Search.</t>
+          <t>Google reinstating bid suppression on budget-limited tCPA/tROAS campaigns; changes to eligible-impression estimation; removal of the budget/rank split in lost-IS columns.</t>
         </is>
       </c>
       <c r="R84" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S84" s="15" t="inlineStr">
@@ -7861,11 +7857,11 @@
     </row>
     <row r="85" ht="15" customHeight="1" s="13">
       <c r="A85" s="15" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Impression share decomposition decision rule</t>
+          <t>Hour-of-day / day-of-week heatmap analysis</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
@@ -7875,7 +7871,7 @@
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
@@ -7885,12 +7881,12 @@
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G85" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H85" s="15" t="inlineStr">
@@ -7900,12 +7896,12 @@
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>Lost IS; deciding budget vs. bid vs. QS action</t>
+          <t>Suspect performance varies by time; deciding schedules</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr">
@@ -7921,7 +7917,7 @@
       <c r="M85" s="15" t="n"/>
       <c r="N85" s="17" t="inlineStr">
         <is>
-          <t>skills/84-impression-share-decomposition/</t>
+          <t>skills/85-hour-day-heatmap-analysis/</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -7932,12 +7928,12 @@
       </c>
       <c r="Q85" s="16" t="inlineStr">
         <is>
-          <t>Google reinstating bid suppression on budget-limited tCPA/tROAS campaigns; changes to eligible-impression estimation; removal of the budget/rank split in lost-IS columns.</t>
+          <t>Google re-enabling ad-schedule bid adjustments under Smart Bidding, changing the 30.4× pacing rule for scheduled campaigns, or removing ad schedules / −100% device adjustments.</t>
         </is>
       </c>
       <c r="R85" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S85" s="15" t="inlineStr">
@@ -7948,11 +7944,11 @@
     </row>
     <row r="86" ht="15" customHeight="1" s="13">
       <c r="A86" s="15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Hour-of-day / day-of-week heatmap analysis</t>
+          <t>Attribution model comparison (DDA vs last click)</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
@@ -7962,7 +7958,7 @@
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
@@ -7972,7 +7968,7 @@
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
@@ -7982,22 +7978,22 @@
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
-          <t>Suspect performance varies by time; deciding schedules</t>
+          <t>Reporting delta vs. client's analytics; upper-funnel credit</t>
         </is>
       </c>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L86" s="15" t="inlineStr">
@@ -8008,7 +8004,7 @@
       <c r="M86" s="15" t="n"/>
       <c r="N86" s="17" t="inlineStr">
         <is>
-          <t>skills/85-hour-day-heatmap-analysis/</t>
+          <t>skills/86-attribution-model-comparison/</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -8019,7 +8015,7 @@
       </c>
       <c r="Q86" s="16" t="inlineStr">
         <is>
-          <t>Google re-enabling ad-schedule bid adjustments under Smart Bidding, changing the 30.4× pacing rule for scheduled campaigns, or removing ad schedules / −100% device adjustments.</t>
+          <t>Google changing the DDA default or its 200-conversion / 2,000-interaction recommendation, the 90-day GCLID import window, the new-customer value adjustment columns, or by-conversion-time reporting.</t>
         </is>
       </c>
       <c r="R86" s="15" t="inlineStr">
@@ -8035,21 +8031,21 @@
     </row>
     <row r="87" ht="15" customHeight="1" s="13">
       <c r="A87" s="15" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Attribution model comparison (DDA vs last click)</t>
+          <t>Location options: presence vs. presence-or-interest</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Defaults to override</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
@@ -8059,32 +8055,32 @@
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G87" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Reporting delta vs. client's analytics; upper-funnel credit</t>
+          <t>Every new campaign; auditing inherited accounts</t>
         </is>
       </c>
       <c r="K87" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L87" s="15" t="inlineStr">
@@ -8095,7 +8091,7 @@
       <c r="M87" s="15" t="n"/>
       <c r="N87" s="17" t="inlineStr">
         <is>
-          <t>skills/86-attribution-model-comparison/</t>
+          <t>skills/87-location-options-presence/</t>
         </is>
       </c>
       <c r="O87" s="15" t="n"/>
@@ -8106,7 +8102,7 @@
       </c>
       <c r="Q87" s="16" t="inlineStr">
         <is>
-          <t>Google changing the DDA default or its 200-conversion / 2,000-interaction recommendation, the 90-day GCLID import window, the new-customer value adjustment columns, or by-conversion-time reporting.</t>
+          <t>Google removing the "Presence" targeting option (as it removed "Search interest" in April 2023); a native User-location report returning to the UI; location bid modifiers becoming available under tCPA/tROAS.</t>
         </is>
       </c>
       <c r="R87" s="15" t="inlineStr">
@@ -8122,11 +8118,11 @@
     </row>
     <row r="88" ht="15" customHeight="1" s="13">
       <c r="A88" s="15" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>Location options: presence vs. presence-or-interest</t>
+          <t>Standard off-list (partners, display expansion, URL expansion, auto-apply)</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
@@ -8171,7 +8167,7 @@
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L88" s="15" t="inlineStr">
@@ -8182,7 +8178,7 @@
       <c r="M88" s="15" t="n"/>
       <c r="N88" s="17" t="inlineStr">
         <is>
-          <t>skills/87-location-options-presence/</t>
+          <t>skills/88-standard-off-list/</t>
         </is>
       </c>
       <c r="O88" s="15" t="n"/>
@@ -8193,12 +8189,12 @@
       </c>
       <c r="Q88" s="16" t="inlineStr">
         <is>
-          <t>Google removing the "Presence" targeting option (as it removed "Search interest" in April 2023); a native User-location report returning to the UI; location bid modifiers becoming available under tCPA/tROAS.</t>
+          <t>Google defaulting search partners or Display Expansion to off; partner-site reporting or exclusions arriving for Search; Final URL expansion defaulting to off or gaining keyword-level control; auto-apply recommendations being removed or moved to MCC level.</t>
         </is>
       </c>
       <c r="R88" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S88" s="15" t="inlineStr">
@@ -8209,11 +8205,11 @@
     </row>
     <row r="89" ht="23.25" customHeight="1" s="13">
       <c r="A89" s="15" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Standard off-list (partners, display expansion, URL expansion, auto-apply)</t>
+          <t>Ad rotation settings under Smart Bidding</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
@@ -8228,7 +8224,7 @@
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
@@ -8248,17 +8244,17 @@
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>Every new campaign; auditing inherited accounts</t>
+          <t>Setting up or auditing ad rotation</t>
         </is>
       </c>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L89" s="15" t="inlineStr">
@@ -8269,7 +8265,7 @@
       <c r="M89" s="15" t="n"/>
       <c r="N89" s="17" t="inlineStr">
         <is>
-          <t>skills/88-standard-off-list/</t>
+          <t>skills/89-ad-rotation-smart-bidding/</t>
         </is>
       </c>
       <c r="O89" s="15" t="n"/>
@@ -8280,12 +8276,12 @@
       </c>
       <c r="Q89" s="16" t="inlineStr">
         <is>
-          <t>Google defaulting search partners or Display Expansion to off; partner-site reporting or exclusions arriving for Search; Final URL expansion defaulting to off or gaining keyword-level control; auto-apply recommendations being removed or moved to MCC level.</t>
+          <t>Google honouring "Do not optimize" under Smart Bidding; Optimize being re-tuned to conversions rather than clicks; the rotation setting being removed; Ad variations experiments being withdrawn.</t>
         </is>
       </c>
       <c r="R89" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S89" s="15" t="inlineStr">
@@ -8296,11 +8292,11 @@
     </row>
     <row r="90" ht="15" customHeight="1" s="13">
       <c r="A90" s="15" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>Ad rotation settings under Smart Bidding</t>
+          <t>Account-level negatives &amp; brand restrictions</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
@@ -8315,12 +8311,12 @@
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -8335,17 +8331,17 @@
       </c>
       <c r="I90" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>Setting up or auditing ad rotation</t>
+          <t>Account-wide exclusions needed across many campaigns</t>
         </is>
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Google docs (recent feature)</t>
         </is>
       </c>
       <c r="L90" s="15" t="inlineStr">
@@ -8356,7 +8352,7 @@
       <c r="M90" s="15" t="n"/>
       <c r="N90" s="17" t="inlineStr">
         <is>
-          <t>skills/89-ad-rotation-smart-bidding/</t>
+          <t>skills/90-account-level-negatives-brand-restrictions/</t>
         </is>
       </c>
       <c r="O90" s="15" t="n"/>
@@ -8367,7 +8363,7 @@
       </c>
       <c r="Q90" s="16" t="inlineStr">
         <is>
-          <t>Google honouring "Do not optimize" under Smart Bidding; Optimize being re-tuned to conversions rather than clicks; the rotation setting being removed; Ad variations experiments being withdrawn.</t>
+          <t>The 1,000-keyword account-level cap changing; account-level negatives gaining per-campaign-type scoping; brand exclusions reliably covering close variants (new cross-account evidence); PMax negatives at asset-group level.</t>
         </is>
       </c>
       <c r="R90" s="15" t="inlineStr">
@@ -8383,21 +8379,21 @@
     </row>
     <row r="91" ht="15" customHeight="1" s="13">
       <c r="A91" s="15" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Account-level negatives &amp; brand restrictions</t>
+          <t>Full account audit — multi-module diagnostic</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Defaults to override</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
@@ -8407,7 +8403,7 @@
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr">
@@ -8417,7 +8413,7 @@
       </c>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
@@ -8427,59 +8423,47 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>Account-wide exclusions needed across many campaigns</t>
+          <t>Taking over an account, quarterly review, or pre-pitch; need a ranked list of critical issues across tracking, structure, settings, keywords/search terms, bids/budgets, ads, landing pages</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Google docs (recent feature)</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L91" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="M91" s="15" t="n"/>
-      <c r="N91" s="17" t="inlineStr">
-        <is>
-          <t>skills/90-account-level-negatives-brand-restrictions/</t>
-        </is>
-      </c>
-      <c r="O91" s="15" t="n"/>
-      <c r="P91" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Q91" s="16" t="inlineStr">
-        <is>
-          <t>The 1,000-keyword account-level cap changing; account-level negatives gaining per-campaign-type scoping; brand exclusions reliably covering close variants (new cross-account evidence); PMax negatives at asset-group level.</t>
-        </is>
-      </c>
-      <c r="R91" s="15" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
+      <c r="N91" s="17" t="n"/>
+      <c r="O91" s="15" t="inlineStr">
+        <is>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+        </is>
+      </c>
+      <c r="P91" s="15" t="n"/>
+      <c r="Q91" s="16" t="n"/>
+      <c r="R91" s="15" t="n"/>
       <c r="S91" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Full account audit — multi-module diagnostic</t>
+          <t>Conversion tracking audit</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
@@ -8494,7 +8478,7 @@
       </c>
       <c r="F92" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G92" s="15" t="inlineStr">
@@ -8504,7 +8488,7 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -8514,7 +8498,7 @@
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>Taking over an account, quarterly review, or pre-pitch; need a ranked list of critical issues across tracking, structure, settings, keywords/search terms, bids/budgets, ads, landing pages</t>
+          <t>Before trusting Smart Bidding on any account: verify tags, primary/secondary actions, duplicates, attribution, Enhanced Conversions, Consent Mode v2, OCI, counting method</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr">
@@ -8531,7 +8515,7 @@
       <c r="N92" s="17" t="n"/>
       <c r="O92" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
         </is>
       </c>
       <c r="P92" s="15" t="n"/>
@@ -8545,21 +8529,21 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Conversion tracking audit</t>
+          <t>Weekly account review routine</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E93" s="15" t="inlineStr">
@@ -8569,7 +8553,7 @@
       </c>
       <c r="F93" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G93" s="15" t="inlineStr">
@@ -8579,17 +8563,17 @@
       </c>
       <c r="H93" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>Before trusting Smart Bidding on any account: verify tags, primary/secondary actions, duplicates, attribution, Enhanced Conversions, Consent Mode v2, OCI, counting method</t>
+          <t>Running the standing weekly check: what to look at, in what order, over which lookbacks, and what triggers an action vs a watch</t>
         </is>
       </c>
       <c r="K93" s="15" t="inlineStr">
@@ -8606,7 +8590,7 @@
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
         </is>
       </c>
       <c r="P93" s="15" t="n"/>
@@ -8620,11 +8604,11 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Weekly account review routine</t>
+          <t>Performance change root-cause diagnosis</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
@@ -8634,7 +8618,7 @@
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
@@ -8644,7 +8628,7 @@
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
@@ -8654,22 +8638,22 @@
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>Running the standing weekly check: what to look at, in what order, over which lookbacks, and what triggers an action vs a watch</t>
+          <t>CPC, CTR, clicks, conversions or CPA moved and nobody knows why; need a decomposition tree before touching anything</t>
         </is>
       </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Adalysis KPI monitoring series</t>
         </is>
       </c>
       <c r="L94" s="15" t="inlineStr">
@@ -8681,7 +8665,7 @@
       <c r="N94" s="17" t="n"/>
       <c r="O94" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
         </is>
       </c>
       <c r="P94" s="15" t="n"/>
@@ -8695,21 +8679,21 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Performance change root-cause diagnosis</t>
+          <t>Bid strategy selection — Smart Bidding vs manual, target vs maximise</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E95" s="15" t="inlineStr">
@@ -8719,7 +8703,7 @@
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G95" s="15" t="inlineStr">
@@ -8729,7 +8713,7 @@
       </c>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
@@ -8739,12 +8723,12 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>CPC, CTR, clicks, conversions or CPA moved and nobody knows why; need a decomposition tree before touching anything</t>
+          <t>Choosing or changing a bid strategy per campaign; deciding whether volume, signal quality and spend-control needs justify Smart Bidding at all</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>Adalysis KPI monitoring series</t>
+          <t>Optmyzr / Adalysis / PPC Mastery</t>
         </is>
       </c>
       <c r="L95" s="15" t="inlineStr">
@@ -8756,7 +8740,7 @@
       <c r="N95" s="17" t="n"/>
       <c r="O95" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
         </is>
       </c>
       <c r="P95" s="15" t="n"/>
@@ -8770,11 +8754,11 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>Bid strategy selection — Smart Bidding vs manual, target vs maximise</t>
+          <t>Targets from unit economics — break-even ROAS, profit curve, growth vs efficiency</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -8804,7 +8788,7 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -8814,12 +8798,12 @@
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>Choosing or changing a bid strategy per campaign; deciding whether volume, signal quality and spend-control needs justify Smart Bidding at all</t>
+          <t>Setting or renegotiating tCPA/tROAS with a client; need margin, LTV, payback and a primary-goal/guardrail pair before touching the target</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Optmyzr / Adalysis / PPC Mastery</t>
+          <t>Mike Rhodes / PPC Mastery</t>
         </is>
       </c>
       <c r="L96" s="15" t="inlineStr">
@@ -8831,7 +8815,7 @@
       <c r="N96" s="17" t="n"/>
       <c r="O96" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
         </is>
       </c>
       <c r="P96" s="15" t="n"/>
@@ -8845,11 +8829,11 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Targets from unit economics — break-even ROAS, profit curve, growth vs efficiency</t>
+          <t>Smart Bidding learning period — what resets it and change-size rules</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
@@ -8859,7 +8843,7 @@
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E97" s="15" t="inlineStr">
@@ -8869,7 +8853,7 @@
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G97" s="15" t="inlineStr">
@@ -8889,12 +8873,12 @@
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>Setting or renegotiating tCPA/tROAS with a client; need margin, LTV, payback and a primary-goal/guardrail pair before touching the target</t>
+          <t>Planning any target, budget, structure or conversion-action change on a Smart Bidding campaign; deciding step size and spacing to avoid relearning</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes / PPC Mastery</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L97" s="15" t="inlineStr">
@@ -8906,7 +8890,7 @@
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
         </is>
       </c>
       <c r="P97" s="15" t="n"/>
@@ -8920,16 +8904,16 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>Smart Bidding learning period — what resets it and change-size rules</t>
+          <t>AI Max for Search — test design and evaluation</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Keyword &amp; query</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
@@ -8939,22 +8923,22 @@
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G98" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
@@ -8964,12 +8948,12 @@
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>Planning any target, budget, structure or conversion-action change on a Smart Bidding campaign; deciding step size and spacing to avoid relearning</t>
+          <t>Google is pushing AI Max; need prerequisites, a limited test, and how to read search terms, asset source and URL expansion before keeping it on</t>
         </is>
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Adalysis / ZATO</t>
         </is>
       </c>
       <c r="L98" s="15" t="inlineStr">
@@ -8981,7 +8965,7 @@
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
         </is>
       </c>
       <c r="P98" s="15" t="n"/>
@@ -8995,16 +8979,16 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>AI Max for Search — test design and evaluation</t>
+          <t>Product performance bucketing for Shopping and PMax</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Keyword &amp; query</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
@@ -9014,12 +8998,12 @@
       </c>
       <c r="E99" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G99" s="15" t="inlineStr">
@@ -9029,7 +9013,7 @@
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I99" s="15" t="inlineStr">
@@ -9039,12 +9023,12 @@
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>Google is pushing AI Max; need prerequisites, a limited test, and how to read search terms, asset source and URL expansion before keeping it on</t>
+          <t>Spend concentrated on a few SKUs while most products get no impressions; want zombies/heroes/sidekicks split into campaigns or asset groups</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
         <is>
-          <t>Adalysis / ZATO</t>
+          <t>Mike Rhodes / Optmyzr</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
@@ -9056,7 +9040,7 @@
       <c r="N99" s="17" t="n"/>
       <c r="O99" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
         </is>
       </c>
       <c r="P99" s="15" t="n"/>
@@ -9070,56 +9054,56 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>Product performance bucketing for Shopping and PMax</t>
+          <t>Bid adjustments under Smart Bidding — what still applies</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H100" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>Spend concentrated on a few SKUs while most products get no impressions; want zombies/heroes/sidekicks split into campaigns or asset groups</t>
+          <t>Inherited account full of device/location/schedule/audience adjustments on tCPA/tROAS; deciding what to strip, what -100% exclusions remain valid</t>
         </is>
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes / Optmyzr</t>
+          <t>PPC Mastery / Adalysis</t>
         </is>
       </c>
       <c r="L100" s="15" t="inlineStr">
@@ -9131,7 +9115,7 @@
       <c r="N100" s="17" t="n"/>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
         </is>
       </c>
       <c r="P100" s="15" t="n"/>
@@ -9145,11 +9129,11 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Bid adjustments under Smart Bidding — what still applies</t>
+          <t>Budget reallocation across campaigns by marginal return</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
@@ -9159,7 +9143,7 @@
       </c>
       <c r="D101" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E101" s="15" t="inlineStr">
@@ -9169,17 +9153,17 @@
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I101" s="15" t="inlineStr">
@@ -9189,12 +9173,12 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>Inherited account full of device/location/schedule/audience adjustments on tCPA/tROAS; deciding what to strip, what -100% exclusions remain valid</t>
+          <t>Fixed account budget; some campaigns limited by budget, others underspending; deciding where the next euro goes and whether shared budgets help</t>
         </is>
       </c>
       <c r="K101" s="15" t="inlineStr">
         <is>
-          <t>PPC Mastery / Adalysis</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L101" s="15" t="inlineStr">
@@ -9206,7 +9190,7 @@
       <c r="N101" s="17" t="n"/>
       <c r="O101" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
         </is>
       </c>
       <c r="P101" s="15" t="n"/>
@@ -9220,11 +9204,11 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Budget reallocation across campaigns by marginal return</t>
+          <t>Scaling without breaking efficiency — budget and target step rules</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
@@ -9234,7 +9218,7 @@
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
@@ -9254,7 +9238,7 @@
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -9264,12 +9248,12 @@
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>Fixed account budget; some campaigns limited by budget, others underspending; deciding where the next euro goes and whether shared budgets help</t>
+          <t>Client wants 2x volume; deciding the order of levers (budget, target, match type, campaign type) and step sizes without CPA blowing up</t>
         </is>
       </c>
       <c r="K102" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>ZATO / PPC Mastery</t>
         </is>
       </c>
       <c r="L102" s="15" t="inlineStr">
@@ -9281,7 +9265,7 @@
       <c r="N102" s="17" t="n"/>
       <c r="O102" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
         </is>
       </c>
       <c r="P102" s="15" t="n"/>
@@ -9295,21 +9279,21 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Scaling without breaking efficiency — budget and target step rules</t>
+          <t>Campaign not serving / zero impressions troubleshooting</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E103" s="15" t="inlineStr">
@@ -9319,12 +9303,12 @@
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G103" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H103" s="15" t="inlineStr">
@@ -9339,12 +9323,12 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>Client wants 2x volume; deciding the order of levers (budget, target, match type, campaign type) and step sizes without CPA blowing up</t>
+          <t>Live campaign with no or near-zero impressions; need the ordered checklist (billing, policy, status, targeting, bids/targets, negatives, eligibility) before escalating</t>
         </is>
       </c>
       <c r="K103" s="15" t="inlineStr">
         <is>
-          <t>ZATO / PPC Mastery</t>
+          <t>ZATO / Navah Hopkins</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
@@ -9356,7 +9340,7 @@
       <c r="N103" s="17" t="n"/>
       <c r="O103" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
         </is>
       </c>
       <c r="P103" s="15" t="n"/>
@@ -9370,41 +9354,41 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>Campaign not serving / zero impressions troubleshooting</t>
+          <t>New Search campaign launch checklist and first-30-days watch</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Account structure</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -9414,12 +9398,12 @@
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
-          <t>Live campaign with no or near-zero impressions; need the ordered checklist (billing, policy, status, targeting, bids/targets, negatives, eligibility) before escalating</t>
+          <t>Launching a new Search campaign; pre-launch settings check and what to review in weeks 1–2 (relevance, net-new impressions, IS) vs weeks 3–4 (conversion quality, serving, match type, bid method switch)</t>
         </is>
       </c>
       <c r="K104" s="15" t="inlineStr">
         <is>
-          <t>ZATO / Navah Hopkins</t>
+          <t>Adalysis / PPC Mastery</t>
         </is>
       </c>
       <c r="L104" s="15" t="inlineStr">
@@ -9431,7 +9415,7 @@
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
         </is>
       </c>
       <c r="P104" s="15" t="n"/>
@@ -9445,16 +9429,16 @@
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>New Search campaign launch checklist and first-30-days watch</t>
+          <t>Ad assets (sitelinks, callouts, snippets, images) — build and evaluate</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>Account structure</t>
+          <t>RSA &amp; ad copy</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -9469,17 +9453,17 @@
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G105" s="15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H105" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I105" s="15" t="inlineStr">
@@ -9489,12 +9473,12 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>Launching a new Search campaign; pre-launch settings check and what to review in weeks 1–2 (relevance, net-new impressions, IS) vs weeks 3–4 (conversion quality, serving, match type, bid method switch)</t>
+          <t>Setting up or auditing assets; reading asset-level performance and the asset-vs-ad report; which assets to pin to campaign vs account level</t>
         </is>
       </c>
       <c r="K105" s="15" t="inlineStr">
         <is>
-          <t>Adalysis / PPC Mastery</t>
+          <t>Adalysis</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
@@ -9506,7 +9490,7 @@
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
         </is>
       </c>
       <c r="P105" s="15" t="n"/>
@@ -9520,16 +9504,16 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>Ad assets (sitelinks, callouts, snippets, images) — build and evaluate</t>
+          <t>Feed attribute optimisation beyond titles (product_type, google_product_category, id, description)</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
@@ -9539,12 +9523,12 @@
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
@@ -9554,7 +9538,7 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
@@ -9564,12 +9548,12 @@
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>Setting up or auditing assets; reading asset-level performance and the asset-vs-ad report; which assets to pin to campaign vs account level</t>
+          <t>Titles done; want the secondary attributes that drive matching and segmentation right, and stable product IDs before any feed-provider change</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr">
         <is>
-          <t>Adalysis</t>
+          <t>ZATO Merchant Center Mastery</t>
         </is>
       </c>
       <c r="L106" s="15" t="inlineStr">
@@ -9581,7 +9565,7 @@
       <c r="N106" s="17" t="n"/>
       <c r="O106" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
         </is>
       </c>
       <c r="P106" s="15" t="n"/>
@@ -9595,11 +9579,11 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>Feed attribute optimisation beyond titles (product_type, google_product_category, id, description)</t>
+          <t>Merchant Center account suspension recovery</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
@@ -9609,7 +9593,7 @@
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E107" s="15" t="inlineStr">
@@ -9619,7 +9603,7 @@
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G107" s="15" t="inlineStr">
@@ -9629,7 +9613,7 @@
       </c>
       <c r="H107" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I107" s="15" t="inlineStr">
@@ -9639,12 +9623,12 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>Titles done; want the secondary attributes that drive matching and segmentation right, and stable product IDs before any feed-provider change</t>
+          <t>Account-level suspension (misrepresentation, unacceptable business practices, tax/shipping) rather than item disapprovals; need the compliance checklist and appeal sequence</t>
         </is>
       </c>
       <c r="K107" s="15" t="inlineStr">
         <is>
-          <t>ZATO Merchant Center Mastery</t>
+          <t>ZATO</t>
         </is>
       </c>
       <c r="L107" s="15" t="inlineStr">
@@ -9656,7 +9640,7 @@
       <c r="N107" s="17" t="n"/>
       <c r="O107" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
         </is>
       </c>
       <c r="P107" s="15" t="n"/>
@@ -9670,16 +9654,16 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>Merchant Center account suspension recovery</t>
+          <t>PMax asset group and asset performance review</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
@@ -9689,22 +9673,22 @@
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
@@ -9714,12 +9698,12 @@
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>Account-level suspension (misrepresentation, unacceptable business practices, tax/shipping) rather than item disapprovals; need the compliance checklist and appeal sequence</t>
+          <t>Deciding which assets and asset groups to replace; reading asset ratings, asset-group spend and conversion split, and auto-generated vs supplied assets</t>
         </is>
       </c>
       <c r="K108" s="15" t="inlineStr">
         <is>
-          <t>ZATO</t>
+          <t>Mike Rhodes</t>
         </is>
       </c>
       <c r="L108" s="15" t="inlineStr">
@@ -9731,7 +9715,7 @@
       <c r="N108" s="17" t="n"/>
       <c r="O108" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
         </is>
       </c>
       <c r="P108" s="15" t="n"/>
@@ -9745,16 +9729,16 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>PMax asset group and asset performance review</t>
+          <t>Spam conversions and invalid traffic polluting Smart Bidding</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -9764,22 +9748,22 @@
       </c>
       <c r="E109" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I109" s="15" t="inlineStr">
@@ -9789,12 +9773,12 @@
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>Deciding which assets and asset groups to replace; reading asset ratings, asset-group spend and conversion split, and auto-generated vs supplied assets</t>
+          <t>Sudden conversion spike with no revenue, bot form fills, or suspected click fraud; detect, confirm, negate/exclude, and clean the bidding signal</t>
         </is>
       </c>
       <c r="K109" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
@@ -9806,7 +9790,7 @@
       <c r="N109" s="17" t="n"/>
       <c r="O109" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
         </is>
       </c>
       <c r="P109" s="15" t="n"/>
@@ -9820,21 +9804,21 @@
     </row>
     <row r="110">
       <c r="A110" s="15" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B110" s="16" t="inlineStr">
         <is>
-          <t>Spam conversions and invalid traffic polluting Smart Bidding</t>
+          <t>Landing page audit for paid search</t>
         </is>
       </c>
       <c r="C110" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E110" s="15" t="inlineStr">
@@ -9844,7 +9828,7 @@
       </c>
       <c r="F110" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G110" s="15" t="inlineStr">
@@ -9864,12 +9848,12 @@
       </c>
       <c r="J110" s="16" t="inlineStr">
         <is>
-          <t>Sudden conversion spike with no revenue, bot form fills, or suspected click fraud; detect, confirm, negate/exclude, and clean the bidding signal</t>
+          <t>CVR low despite relevant traffic; structured LP audit (message match, hero, proof, speed, form/CTA, guarantee) and how to test LP with ad together</t>
         </is>
       </c>
       <c r="K110" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>PPC Mastery / Adalysis</t>
         </is>
       </c>
       <c r="L110" s="15" t="inlineStr">
@@ -9881,7 +9865,7 @@
       <c r="N110" s="17" t="n"/>
       <c r="O110" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
         </is>
       </c>
       <c r="P110" s="15" t="n"/>
@@ -9895,21 +9879,21 @@
     </row>
     <row r="111">
       <c r="A111" s="15" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B111" s="16" t="inlineStr">
         <is>
-          <t>Landing page audit for paid search</t>
+          <t>Automation layering — guardrail automations over Google's automation</t>
         </is>
       </c>
       <c r="C111" s="15" t="inlineStr">
         <is>
-          <t>Quality Score</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E111" s="15" t="inlineStr">
@@ -9924,12 +9908,12 @@
       </c>
       <c r="G111" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H111" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I111" s="15" t="inlineStr">
@@ -9939,12 +9923,12 @@
       </c>
       <c r="J111" s="16" t="inlineStr">
         <is>
-          <t>CVR low despite relevant traffic; structured LP audit (message match, hero, proof, speed, form/CTA, guarantee) and how to test LP with ad together</t>
+          <t>Deciding which Google automations to adopt and which monitors (alerts, rules, scripts) must sit on top of each before go-live</t>
         </is>
       </c>
       <c r="K111" s="15" t="inlineStr">
         <is>
-          <t>PPC Mastery / Adalysis</t>
+          <t>Fred Vallaeys</t>
         </is>
       </c>
       <c r="L111" s="15" t="inlineStr">
@@ -9956,7 +9940,7 @@
       <c r="N111" s="17" t="n"/>
       <c r="O111" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
         </is>
       </c>
       <c r="P111" s="15" t="n"/>
@@ -9970,11 +9954,11 @@
     </row>
     <row r="112">
       <c r="A112" s="15" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B112" s="16" t="inlineStr">
         <is>
-          <t>Automation layering — guardrail automations over Google's automation</t>
+          <t>Change history monitoring</t>
         </is>
       </c>
       <c r="C112" s="15" t="inlineStr">
@@ -9984,7 +9968,7 @@
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E112" s="15" t="inlineStr">
@@ -9994,12 +9978,12 @@
       </c>
       <c r="F112" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G112" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H112" s="15" t="inlineStr">
@@ -10009,17 +9993,17 @@
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J112" s="16" t="inlineStr">
         <is>
-          <t>Deciding which Google automations to adopt and which monitors (alerts, rules, scripts) must sit on top of each before go-live</t>
+          <t>Multiple users, Google reps or auto-apply touching the account; want daily alerts on unexpected changes with who/what</t>
         </is>
       </c>
       <c r="K112" s="15" t="inlineStr">
         <is>
-          <t>Fred Vallaeys</t>
+          <t>Nils Rooijmans</t>
         </is>
       </c>
       <c r="L112" s="15" t="inlineStr">
@@ -10031,7 +10015,7 @@
       <c r="N112" s="17" t="n"/>
       <c r="O112" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
         </is>
       </c>
       <c r="P112" s="15" t="n"/>
@@ -10045,41 +10029,41 @@
     </row>
     <row r="113">
       <c r="A113" s="15" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B113" s="16" t="inlineStr">
         <is>
-          <t>Change history monitoring</t>
+          <t>Lin-Rodnitzky ratio as a search-term health metric</t>
         </is>
       </c>
       <c r="C113" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Keyword &amp; query</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E113" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F113" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G113" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H113" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I113" s="15" t="inlineStr">
@@ -10089,12 +10073,12 @@
       </c>
       <c r="J113" s="16" t="inlineStr">
         <is>
-          <t>Multiple users, Google reps or auto-apply touching the account; want daily alerts on unexpected changes with who/what</t>
+          <t>Need one account-level number for whether query mining is too conservative or too loose (all-query CPA ÷ converting-query CPA, bands 1.0–1.5 / 1.5–2.0 / 2.0–2.5 / 2.5+)</t>
         </is>
       </c>
       <c r="K113" s="15" t="inlineStr">
         <is>
-          <t>Nils Rooijmans</t>
+          <t>Nils Rooijmans script</t>
         </is>
       </c>
       <c r="L113" s="15" t="inlineStr">
@@ -10106,7 +10090,7 @@
       <c r="N113" s="17" t="n"/>
       <c r="O113" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
         </is>
       </c>
       <c r="P113" s="15" t="n"/>
@@ -10118,117 +10102,42 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="B114" s="16" t="inlineStr">
-        <is>
-          <t>Lin-Rodnitzky ratio as a search-term health metric</t>
-        </is>
-      </c>
-      <c r="C114" s="15" t="inlineStr">
-        <is>
-          <t>Keyword &amp; query</t>
-        </is>
-      </c>
-      <c r="D114" s="15" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="E114" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="F114" s="15" t="inlineStr">
-        <is>
-          <t>Diagnose</t>
-        </is>
-      </c>
-      <c r="G114" s="15" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="H114" s="15" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="I114" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J114" s="16" t="inlineStr">
-        <is>
-          <t>Need one account-level number for whether query mining is too conservative or too loose (all-query CPA ÷ converting-query CPA, bands 1.0–1.5 / 1.5–2.0 / 2.0–2.5 / 2.5+)</t>
-        </is>
-      </c>
-      <c r="K114" s="15" t="inlineStr">
-        <is>
-          <t>Nils Rooijmans script</t>
-        </is>
-      </c>
-      <c r="L114" s="15" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M114" s="15" t="n"/>
-      <c r="N114" s="17" t="n"/>
-      <c r="O114" s="15" t="inlineStr">
-        <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
-        </is>
-      </c>
-      <c r="P114" s="15" t="n"/>
-      <c r="Q114" s="16" t="n"/>
-      <c r="R114" s="15" t="n"/>
-      <c r="S114" s="15" t="inlineStr">
-        <is>
-          <t>NEEDS ELIAS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:S91"/>
   <dataValidations count="9">
-    <dataValidation sqref="D2:D114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D2:D113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Structure,Strategy,Technique,Script,Research,Diagnostic,Setting"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E2:E113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Search,Shopping,PMax,All"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F2:F114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F2:F113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Setup,Scale,Optimise,Diagnose,Protect"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G2:G113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"New,Established,Any"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H2:H113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"One-off,Weekly,Monthly,As needed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="I2:I114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="I2:I113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L2:L113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,Drafting,Review,Done,Proposed,Re-check"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="R2:R114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R2:R113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Strong,Adequate,Thin"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S114" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="S2:S113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"PASS,FAIL,NEEDS ELIAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10323,7 +10232,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N91" r:id="rId90"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10837,11 +10745,11 @@
         </is>
       </c>
       <c r="B2" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A2)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A2)</f>
         <v/>
       </c>
       <c r="C2" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A2,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A2,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D2" s="22" t="n"/>
@@ -10851,7 +10759,7 @@
         </is>
       </c>
       <c r="F2" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$114,E2)</f>
+        <f>COUNTIF(Skills!$I$2:$I$113,E2)</f>
         <v/>
       </c>
       <c r="G2" s="22" t="n"/>
@@ -10861,7 +10769,7 @@
         </is>
       </c>
       <c r="I2" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$114,H2)</f>
+        <f>COUNTIF(Skills!$F$2:$F$113,H2)</f>
         <v/>
       </c>
     </row>
@@ -10872,11 +10780,11 @@
         </is>
       </c>
       <c r="B3" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A3)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A3)</f>
         <v/>
       </c>
       <c r="C3" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A3,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A3,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D3" s="22" t="n"/>
@@ -10886,7 +10794,7 @@
         </is>
       </c>
       <c r="F3" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$114,E3)</f>
+        <f>COUNTIF(Skills!$I$2:$I$113,E3)</f>
         <v/>
       </c>
       <c r="G3" s="22" t="n"/>
@@ -10896,7 +10804,7 @@
         </is>
       </c>
       <c r="I3" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$114,H3)</f>
+        <f>COUNTIF(Skills!$F$2:$F$113,H3)</f>
         <v/>
       </c>
     </row>
@@ -10907,11 +10815,11 @@
         </is>
       </c>
       <c r="B4" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A4)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A4)</f>
         <v/>
       </c>
       <c r="C4" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A4,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A4,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D4" s="22" t="n"/>
@@ -10921,7 +10829,7 @@
         </is>
       </c>
       <c r="F4" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$114,E4)</f>
+        <f>COUNTIF(Skills!$I$2:$I$113,E4)</f>
         <v/>
       </c>
       <c r="G4" s="22" t="n"/>
@@ -10931,7 +10839,7 @@
         </is>
       </c>
       <c r="I4" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$114,H4)</f>
+        <f>COUNTIF(Skills!$F$2:$F$113,H4)</f>
         <v/>
       </c>
     </row>
@@ -10942,11 +10850,11 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A5)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A5)</f>
         <v/>
       </c>
       <c r="C5" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A5,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A5,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D5" s="22" t="n"/>
@@ -10959,7 +10867,7 @@
         </is>
       </c>
       <c r="I5" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$114,H5)</f>
+        <f>COUNTIF(Skills!$F$2:$F$113,H5)</f>
         <v/>
       </c>
     </row>
@@ -10970,11 +10878,11 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A6)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A6)</f>
         <v/>
       </c>
       <c r="C6" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A6,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A6,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D6" s="22" t="n"/>
@@ -10987,7 +10895,7 @@
         </is>
       </c>
       <c r="I6" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$114,H6)</f>
+        <f>COUNTIF(Skills!$F$2:$F$113,H6)</f>
         <v/>
       </c>
     </row>
@@ -10998,11 +10906,11 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A7)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A7)</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A7,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A7,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D7" s="22" t="n"/>
@@ -11019,11 +10927,11 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A8)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A8)</f>
         <v/>
       </c>
       <c r="C8" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A8,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A8,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D8" s="22" t="n"/>
@@ -11040,11 +10948,11 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A9)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A9)</f>
         <v/>
       </c>
       <c r="C9" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A9,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A9,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -11061,11 +10969,11 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A10)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A10)</f>
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A10,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A10,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -11082,11 +10990,11 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A11)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A11)</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A11,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A11,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -11103,11 +11011,11 @@
         </is>
       </c>
       <c r="B12" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$114,A12)</f>
+        <f>COUNTIF(Skills!$C$2:$C$113,A12)</f>
         <v/>
       </c>
       <c r="C12" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$114,A12,Skills!$L$2:$L$114,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$113,A12,Skills!$L$2:$L$113,"Done")</f>
         <v/>
       </c>
       <c r="D12" s="22" t="n"/>

--- a/google-ads-skills-index.xlsx
+++ b/google-ads-skills-index.xlsx
@@ -498,7 +498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:S113"/>
+  <dimension ref="A1:S109"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="12" min="1" max="1"/>
@@ -1055,11 +1055,11 @@
     </row>
     <row r="7" ht="15" customHeight="1" s="13">
       <c r="A7" s="15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>Tiered campaign priorities for Shopping</t>
+          <t>Geo-split campaigns vs. bid adjustments</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -1069,12 +1069,12 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Structure</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F7" s="15" t="inlineStr">
@@ -1089,17 +1089,17 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I7" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
-          <t>Running Standard Shopping and want query-level control</t>
+          <t>Markets need separate budgets or messaging; deciding split vs. adjustment</t>
         </is>
       </c>
       <c r="K7" s="15" t="inlineStr">
@@ -1109,20 +1109,16 @@
       </c>
       <c r="L7" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M7" s="15" t="n"/>
       <c r="N7" s="17" t="inlineStr">
         <is>
-          <t>skills/6-tiered-shopping-priorities/</t>
-        </is>
-      </c>
-      <c r="O7" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/7-geo-split-vs-bid-adjustments/</t>
+        </is>
+      </c>
+      <c r="O7" s="15" t="n"/>
       <c r="P7" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -1130,27 +1126,27 @@
       </c>
       <c r="Q7" s="16" t="inlineStr">
         <is>
-          <t>Removal of campaign priority from Standard Shopping; Standard Shopping retired in favour of PMax; brand lists available in Standard Shopping.</t>
+          <t>Google re-enabling location bid adjustments under Smart Bidding; ad-group-level location targeting; per-geo budget allocation inside one campaign.</t>
         </is>
       </c>
       <c r="R7" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S7" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="8" ht="23.25" customHeight="1" s="13">
       <c r="A8" s="15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>Geo-split campaigns vs. bid adjustments</t>
+          <t>Mirror campaigns for Smart Bidding A/B</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
@@ -1165,17 +1161,17 @@
       </c>
       <c r="E8" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F8" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G8" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H8" s="15" t="inlineStr">
@@ -1190,7 +1186,7 @@
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
-          <t>Markets need separate budgets or messaging; deciding split vs. adjustment</t>
+          <t>Want to compare bid strategies; deciding mirror vs. custom experiment</t>
         </is>
       </c>
       <c r="K8" s="15" t="inlineStr">
@@ -1206,7 +1202,7 @@
       <c r="M8" s="15" t="n"/>
       <c r="N8" s="17" t="inlineStr">
         <is>
-          <t>skills/7-geo-split-vs-bid-adjustments/</t>
+          <t>skills/8-mirror-campaigns-bid-strategy-ab/</t>
         </is>
       </c>
       <c r="O8" s="15" t="n"/>
@@ -1217,7 +1213,7 @@
       </c>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>Google re-enabling location bid adjustments under Smart Bidding; ad-group-level location targeting; per-geo budget allocation inside one campaign.</t>
+          <t>Custom experiments extended to Shopping/PMax and shared budgets; experiments syncing base-campaign changes; a Smart Bidding learning change that removes the 2–3-week stabilisation.</t>
         </is>
       </c>
       <c r="R8" s="15" t="inlineStr">
@@ -1233,11 +1229,11 @@
     </row>
     <row r="9" ht="15" customHeight="1" s="13">
       <c r="A9" s="15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>Mirror campaigns for Smart Bidding A/B</t>
+          <t>Micro-campaign consolidation for low-volume accounts</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
@@ -1257,27 +1253,27 @@
       </c>
       <c r="F9" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G9" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I9" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
-          <t>Want to compare bid strategies; deciding mirror vs. custom experiment</t>
+          <t>Campaigns stuck in learning; &lt;15–30 conv/month per campaign</t>
         </is>
       </c>
       <c r="K9" s="15" t="inlineStr">
@@ -1293,7 +1289,7 @@
       <c r="M9" s="15" t="n"/>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>skills/8-mirror-campaigns-bid-strategy-ab/</t>
+          <t>skills/9-micro-campaign-consolidation/</t>
         </is>
       </c>
       <c r="O9" s="15" t="n"/>
@@ -1304,12 +1300,12 @@
       </c>
       <c r="Q9" s="16" t="inlineStr">
         <is>
-          <t>Custom experiments extended to Shopping/PMax and shared budgets; experiments syncing base-campaign changes; a Smart Bidding learning change that removes the 2–3-week stabilisation.</t>
+          <t>Bid limits exposed on campaign-level tCPA; Smart Bidding learning changes that stabilise low-volume campaigns; removal of secondary/soft conversion goals.</t>
         </is>
       </c>
       <c r="R9" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S9" s="15" t="inlineStr">
@@ -1320,21 +1316,21 @@
     </row>
     <row r="10" ht="15" customHeight="1" s="13">
       <c r="A10" s="15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="16" t="inlineStr">
         <is>
-          <t>Micro-campaign consolidation for low-volume accounts</t>
+          <t>N-gram analysis of search terms</t>
         </is>
       </c>
       <c r="C10" s="15" t="inlineStr">
         <is>
-          <t>Account structure</t>
+          <t>Keyword &amp; query</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -1344,32 +1340,32 @@
       </c>
       <c r="F10" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G10" s="15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H10" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I10" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
-          <t>Campaigns stuck in learning; &lt;15–30 conv/month per campaign</t>
+          <t>Large search terms report; need to find patterns rather than single terms</t>
         </is>
       </c>
       <c r="K10" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L10" s="15" t="inlineStr">
@@ -1380,7 +1376,7 @@
       <c r="M10" s="15" t="n"/>
       <c r="N10" s="17" t="inlineStr">
         <is>
-          <t>skills/9-micro-campaign-consolidation/</t>
+          <t>skills/10-n-gram-analysis/</t>
         </is>
       </c>
       <c r="O10" s="15" t="n"/>
@@ -1391,7 +1387,7 @@
       </c>
       <c r="Q10" s="16" t="inlineStr">
         <is>
-          <t>Bid limits exposed on campaign-level tCPA; Smart Bidding learning changes that stabilise low-volume campaigns; removal of secondary/soft conversion goals.</t>
+          <t>Further cuts to search terms report visibility; negative keywords starting to match close variants or synonyms; Scripts/GAQL changes to the search_term_view resource; removal of PMax search term reporting.</t>
         </is>
       </c>
       <c r="R10" s="15" t="inlineStr">
@@ -1407,11 +1403,11 @@
     </row>
     <row r="11" ht="15" customHeight="1" s="13">
       <c r="A11" s="15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>N-gram analysis of search terms</t>
+          <t>Close-variant leakage audit</t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
@@ -1421,7 +1417,7 @@
       </c>
       <c r="D11" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E11" s="15" t="inlineStr">
@@ -1431,12 +1427,12 @@
       </c>
       <c r="F11" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G11" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H11" s="15" t="inlineStr">
@@ -1451,12 +1447,12 @@
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
-          <t>Large search terms report; need to find patterns rather than single terms</t>
+          <t>Exact-match CPA drifting; suspect Google is stretching match</t>
         </is>
       </c>
       <c r="K11" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L11" s="15" t="inlineStr">
@@ -1467,7 +1463,7 @@
       <c r="M11" s="15" t="n"/>
       <c r="N11" s="17" t="inlineStr">
         <is>
-          <t>skills/10-n-gram-analysis/</t>
+          <t>skills/11-close-variant-leakage-audit/</t>
         </is>
       </c>
       <c r="O11" s="15" t="n"/>
@@ -1478,7 +1474,7 @@
       </c>
       <c r="Q11" s="16" t="inlineStr">
         <is>
-          <t>Further cuts to search terms report visibility; negative keywords starting to match close variants or synonyms; Scripts/GAQL changes to the search_term_view resource; removal of PMax search term reporting.</t>
+          <t>Removal of the "(close variant)" label from the search terms report; keyword prioritisation changes that make identical exact keywords reliably win; negatives beginning to match close variants or synonyms; further search-term visibility cuts.</t>
         </is>
       </c>
       <c r="R11" s="15" t="inlineStr">
@@ -1494,11 +1490,11 @@
     </row>
     <row r="12" ht="15" customHeight="1" s="13">
       <c r="A12" s="15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>Close-variant leakage audit</t>
+          <t>Negative keyword sculpting across campaigns</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
@@ -1508,7 +1504,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -1518,17 +1514,17 @@
       </c>
       <c r="F12" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G12" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H12" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I12" s="15" t="inlineStr">
@@ -1538,7 +1534,7 @@
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
-          <t>Exact-match CPA drifting; suspect Google is stretching match</t>
+          <t>Same query matching in several campaigns; routing traffic to the right one</t>
         </is>
       </c>
       <c r="K12" s="15" t="inlineStr">
@@ -1554,7 +1550,7 @@
       <c r="M12" s="15" t="n"/>
       <c r="N12" s="17" t="inlineStr">
         <is>
-          <t>skills/11-close-variant-leakage-audit/</t>
+          <t>skills/12-negative-keyword-sculpting/</t>
         </is>
       </c>
       <c r="O12" s="15" t="n"/>
@@ -1565,7 +1561,7 @@
       </c>
       <c r="Q12" s="16" t="inlineStr">
         <is>
-          <t>Removal of the "(close variant)" label from the search terms report; keyword prioritisation changes that make identical exact keywords reliably win; negatives beginning to match close variants or synonyms; further search-term visibility cuts.</t>
+          <t>Google changing keyword prioritisation so identical keywords always win regardless of campaign restrictions; negatives starting to match close variants; removal of campaign-level PMax negatives; AI Max replacing keyword-level control in Search (DSA auto-upgrade to AI Max scheduled Feb 2027).</t>
         </is>
       </c>
       <c r="R12" s="15" t="inlineStr">
@@ -1581,11 +1577,11 @@
     </row>
     <row r="13" ht="15" customHeight="1" s="13">
       <c r="A13" s="15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>Negative keyword sculpting across campaigns</t>
+          <t>Keyword funnelling via tiered negatives</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
@@ -1605,7 +1601,7 @@
       </c>
       <c r="F13" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G13" s="15" t="inlineStr">
@@ -1615,17 +1611,17 @@
       </c>
       <c r="H13" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I13" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
-          <t>Same query matching in several campaigns; routing traffic to the right one</t>
+          <t>Broad/phrase/exact live side by side; want deterministic routing</t>
         </is>
       </c>
       <c r="K13" s="15" t="inlineStr">
@@ -1641,7 +1637,7 @@
       <c r="M13" s="15" t="n"/>
       <c r="N13" s="17" t="inlineStr">
         <is>
-          <t>skills/12-negative-keyword-sculpting/</t>
+          <t>skills/13-keyword-funnelling-tiered-negatives/</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -1652,7 +1648,7 @@
       </c>
       <c r="Q13" s="16" t="inlineStr">
         <is>
-          <t>Google changing keyword prioritisation so identical keywords always win regardless of campaign restrictions; negatives starting to match close variants; removal of campaign-level PMax negatives; AI Max replacing keyword-level control in Search (DSA auto-upgrade to AI Max scheduled Feb 2027).</t>
+          <t>Keyword prioritisation changes removing identical-exact priority; negatives matching close variants; retirement of exact or phrase match; changes to the low-search-volume threshold or the 13-month zero-impression auto-pause.</t>
         </is>
       </c>
       <c r="R13" s="15" t="inlineStr">
@@ -1668,11 +1664,11 @@
     </row>
     <row r="14" ht="15" customHeight="1" s="13">
       <c r="A14" s="15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" s="16" t="inlineStr">
         <is>
-          <t>Keyword funnelling via tiered negatives</t>
+          <t>DSA as a long-tail harvesting engine</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
@@ -1682,7 +1678,7 @@
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E14" s="15" t="inlineStr">
@@ -1692,7 +1688,7 @@
       </c>
       <c r="F14" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1712,7 +1708,7 @@
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
-          <t>Broad/phrase/exact live side by side; want deterministic routing</t>
+          <t>Large site, keyword coverage incomplete; want query discovery</t>
         </is>
       </c>
       <c r="K14" s="15" t="inlineStr">
@@ -1728,7 +1724,7 @@
       <c r="M14" s="15" t="n"/>
       <c r="N14" s="17" t="inlineStr">
         <is>
-          <t>skills/13-keyword-funnelling-tiered-negatives/</t>
+          <t>skills/14-dsa-long-tail-harvesting/</t>
         </is>
       </c>
       <c r="O14" s="15" t="n"/>
@@ -1739,12 +1735,12 @@
       </c>
       <c r="Q14" s="16" t="inlineStr">
         <is>
-          <t>Keyword prioritisation changes removing identical-exact priority; negatives matching close variants; retirement of exact or phrase match; changes to the low-search-volume threshold or the 13-month zero-impression auto-pause.</t>
+          <t>The scheduled February 2027 automatic upgrade of DSA campaigns to AI Max; removal of DSA search term reporting; changes to keyword prioritisation between DSA/AI Max and keyword campaigns.</t>
         </is>
       </c>
       <c r="R14" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S14" s="15" t="inlineStr">
@@ -1755,11 +1751,11 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="13">
       <c r="A15" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" s="16" t="inlineStr">
         <is>
-          <t>DSA as a long-tail harvesting engine</t>
+          <t>Competitor conquesting</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
@@ -1789,17 +1785,17 @@
       </c>
       <c r="H15" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I15" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
-          <t>Large site, keyword coverage incomplete; want query discovery</t>
+          <t>Considering bidding on competitor brand terms</t>
         </is>
       </c>
       <c r="K15" s="15" t="inlineStr">
@@ -1815,7 +1811,7 @@
       <c r="M15" s="15" t="n"/>
       <c r="N15" s="17" t="inlineStr">
         <is>
-          <t>skills/14-dsa-long-tail-harvesting/</t>
+          <t>skills/15-competitor-conquesting/</t>
         </is>
       </c>
       <c r="O15" s="15" t="n"/>
@@ -1826,7 +1822,7 @@
       </c>
       <c r="Q15" s="16" t="inlineStr">
         <is>
-          <t>The scheduled February 2027 automatic upgrade of DSA campaigns to AI Max; removal of DSA search term reporting; changes to keyword prioritisation between DSA/AI Max and keyword campaigns.</t>
+          <t>Changes to Google's brand list / brand exclusion features; trademark policy changes on competitor names in ads; removal of bid caps or CPC floors from portfolio strategies; AI Max removing keyword-level control over competitor terms.</t>
         </is>
       </c>
       <c r="R15" s="15" t="inlineStr">
@@ -1842,11 +1838,11 @@
     </row>
     <row r="16" ht="15" customHeight="1" s="13">
       <c r="A16" s="15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="16" t="inlineStr">
         <is>
-          <t>Competitor conquesting</t>
+          <t>Broad match + Smart Bidding guardrails</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1856,7 +1852,7 @@
       </c>
       <c r="D16" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E16" s="15" t="inlineStr">
@@ -1876,22 +1872,22 @@
       </c>
       <c r="H16" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I16" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
-          <t>Considering bidding on competitor brand terms</t>
+          <t>Testing broad match; need the evidence and the guardrails before rollout</t>
         </is>
       </c>
       <c r="K16" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Optmyzr / Google research</t>
         </is>
       </c>
       <c r="L16" s="15" t="inlineStr">
@@ -1902,7 +1898,7 @@
       <c r="M16" s="15" t="n"/>
       <c r="N16" s="17" t="inlineStr">
         <is>
-          <t>skills/15-competitor-conquesting/</t>
+          <t>skills/16-broad-match-smart-bidding-guardrails/</t>
         </is>
       </c>
       <c r="O16" s="15" t="n"/>
@@ -1913,12 +1909,12 @@
       </c>
       <c r="Q16" s="16" t="inlineStr">
         <is>
-          <t>Changes to Google's brand list / brand exclusion features; trademark policy changes on competitor names in ads; removal of bid caps or CPC floors from portfolio strategies; AI Max removing keyword-level control over competitor terms.</t>
+          <t>Google removing phrase or exact match or folding Search into AI Max by default; changes to the signals broad match uses (landing page, ad group keywords, recent searches); Smart Bidding learning thresholds changing; search terms visibility cuts that prevent policing broad.</t>
         </is>
       </c>
       <c r="R16" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S16" s="15" t="inlineStr">
@@ -1929,11 +1925,11 @@
     </row>
     <row r="17" ht="15" customHeight="1" s="13">
       <c r="A17" s="15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" s="16" t="inlineStr">
         <is>
-          <t>Broad match + Smart Bidding guardrails</t>
+          <t>Search partners &amp; Display expansion exclusion test</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
@@ -1943,7 +1939,7 @@
       </c>
       <c r="D17" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E17" s="15" t="inlineStr">
@@ -1953,12 +1949,12 @@
       </c>
       <c r="F17" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H17" s="15" t="inlineStr">
@@ -1968,17 +1964,17 @@
       </c>
       <c r="I17" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
-          <t>Testing broad match; need the evidence and the guardrails before rollout</t>
+          <t>New campaign or auditing an inherited one</t>
         </is>
       </c>
       <c r="K17" s="15" t="inlineStr">
         <is>
-          <t>Optmyzr / Google research</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L17" s="15" t="inlineStr">
@@ -1989,7 +1985,7 @@
       <c r="M17" s="15" t="n"/>
       <c r="N17" s="17" t="inlineStr">
         <is>
-          <t>skills/16-broad-match-smart-bidding-guardrails/</t>
+          <t>skills/17-search-partners-display-expansion/</t>
         </is>
       </c>
       <c r="O17" s="15" t="n"/>
@@ -2000,12 +1996,12 @@
       </c>
       <c r="Q17" s="16" t="inlineStr">
         <is>
-          <t>Google removing phrase or exact match or folding Search into AI Max by default; changes to the signals broad match uses (landing page, ad group keywords, recent searches); Smart Bidding learning thresholds changing; search terms visibility cuts that prevent policing broad.</t>
+          <t>Google adding per-partner reporting or exclusions; removal of the campaign-level partner toggle; another change to the partner auction like the November 2021 position-first move; Google documenting Display Expansion behaviour differently from the assumption stated below.</t>
         </is>
       </c>
       <c r="R17" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S17" s="15" t="inlineStr">
@@ -2016,11 +2012,11 @@
     </row>
     <row r="18" ht="15" customHeight="1" s="13">
       <c r="A18" s="15" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B18" s="16" t="inlineStr">
         <is>
-          <t>Search partners &amp; Display expansion exclusion test</t>
+          <t>Low search volume / rarely shown keyword handling</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -2030,7 +2026,7 @@
       </c>
       <c r="D18" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E18" s="15" t="inlineStr">
@@ -2040,7 +2036,7 @@
       </c>
       <c r="F18" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G18" s="15" t="inlineStr">
@@ -2050,17 +2046,17 @@
       </c>
       <c r="H18" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I18" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
-          <t>New campaign or auditing an inherited one</t>
+          <t>Keywords flagged low volume or rarely shown</t>
         </is>
       </c>
       <c r="K18" s="15" t="inlineStr">
@@ -2076,7 +2072,7 @@
       <c r="M18" s="15" t="n"/>
       <c r="N18" s="17" t="inlineStr">
         <is>
-          <t>skills/17-search-partners-display-expansion/</t>
+          <t>skills/19-low-search-volume-handling/</t>
         </is>
       </c>
       <c r="O18" s="15" t="n"/>
@@ -2087,7 +2083,7 @@
       </c>
       <c r="Q18" s="16" t="inlineStr">
         <is>
-          <t>Google adding per-partner reporting or exclusions; removal of the campaign-level partner toggle; another change to the partner auction like the November 2021 position-first move; Google documenting Display Expansion behaviour differently from the assumption stated below.</t>
+          <t>Google changing the low-search-volume threshold or review cadence; changes to the 13-month zero-impression ad-group auto-pause; changes to PMax routing of low-volume keywords; retirement of exact match.</t>
         </is>
       </c>
       <c r="R18" s="15" t="inlineStr">
@@ -2103,11 +2099,11 @@
     </row>
     <row r="19" ht="15" customHeight="1" s="13">
       <c r="A19" s="15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B19" s="16" t="inlineStr">
         <is>
-          <t>Keyword insertion case variants and DKI risks</t>
+          <t>Intent-tier keyword taxonomy with per-tier bidding</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
@@ -2117,7 +2113,7 @@
       </c>
       <c r="D19" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E19" s="15" t="inlineStr">
@@ -2127,7 +2123,7 @@
       </c>
       <c r="F19" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G19" s="15" t="inlineStr">
@@ -2137,40 +2133,36 @@
       </c>
       <c r="H19" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I19" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J19" s="16" t="inlineStr">
         <is>
-          <t>Considering DKI; large keyword lists with uniform intent</t>
+          <t>Building keyword lists; want bidding to follow intent</t>
         </is>
       </c>
       <c r="K19" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L19" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M19" s="15" t="n"/>
       <c r="N19" s="17" t="inlineStr">
         <is>
-          <t>skills/18-dki-case-variants-risks/</t>
-        </is>
-      </c>
-      <c r="O19" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/20-intent-tier-keyword-taxonomy/</t>
+        </is>
+      </c>
+      <c r="O19" s="15" t="n"/>
       <c r="P19" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -2178,27 +2170,27 @@
       </c>
       <c r="Q19" s="16" t="inlineStr">
         <is>
-          <t>Google changing keyword insertion syntax or removing it from RSAs; trademark policy changes on inserted keywords.</t>
+          <t>Removal of campaign-level bid targets and budgets; removal of conversion values or primary/secondary conversion actions; AI Max replacing keyword-level control in Search campaigns.</t>
         </is>
       </c>
       <c r="R19" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S19" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="20" ht="15" customHeight="1" s="13">
       <c r="A20" s="15" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" s="16" t="inlineStr">
         <is>
-          <t>Low search volume / rarely shown keyword handling</t>
+          <t>Negative keyword conflict detection</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -2228,22 +2220,22 @@
       </c>
       <c r="H20" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I20" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J20" s="16" t="inlineStr">
         <is>
-          <t>Keywords flagged low volume or rarely shown</t>
+          <t>Impressions dropped after adding negatives; routine hygiene</t>
         </is>
       </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L20" s="15" t="inlineStr">
@@ -2254,7 +2246,7 @@
       <c r="M20" s="15" t="n"/>
       <c r="N20" s="17" t="inlineStr">
         <is>
-          <t>skills/19-low-search-volume-handling/</t>
+          <t>skills/21-negative-keyword-conflict-detection/</t>
         </is>
       </c>
       <c r="O20" s="15" t="n"/>
@@ -2265,7 +2257,7 @@
       </c>
       <c r="Q20" s="16" t="inlineStr">
         <is>
-          <t>Google changing the low-search-volume threshold or review cadence; changes to the 13-month zero-impression ad-group auto-pause; changes to PMax routing of low-volume keywords; retirement of exact match.</t>
+          <t>Negatives starting to match close variants or synonyms (changes what a conflict is); Google Ads Scripts API changes breaking keyword/negative/shared-set queries; Google's built-in conflict recommendation starting to cover shared lists and match types.</t>
         </is>
       </c>
       <c r="R20" s="15" t="inlineStr">
@@ -2281,21 +2273,21 @@
     </row>
     <row r="21" ht="15" customHeight="1" s="13">
       <c r="A21" s="15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="16" t="inlineStr">
         <is>
-          <t>Intent-tier keyword taxonomy with per-tier bidding</t>
+          <t>RSA iteration loop</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>Keyword &amp; query</t>
+          <t>RSA &amp; ad copy</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -2305,7 +2297,7 @@
       </c>
       <c r="F21" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G21" s="15" t="inlineStr">
@@ -2315,22 +2307,22 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I21" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J21" s="16" t="inlineStr">
         <is>
-          <t>Building keyword lists; want bidding to follow intent</t>
+          <t>Ongoing ad copy improvement; the core testing cadence</t>
         </is>
       </c>
       <c r="K21" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L21" s="15" t="inlineStr">
@@ -2341,7 +2333,7 @@
       <c r="M21" s="15" t="n"/>
       <c r="N21" s="17" t="inlineStr">
         <is>
-          <t>skills/20-intent-tier-keyword-taxonomy/</t>
+          <t>skills/22-rsa-iteration-loop/</t>
         </is>
       </c>
       <c r="O21" s="15" t="n"/>
@@ -2352,12 +2344,12 @@
       </c>
       <c r="Q21" s="16" t="inlineStr">
         <is>
-          <t>Removal of campaign-level bid targets and budgets; removal of conversion values or primary/secondary conversion actions; AI Max replacing keyword-level control in Search campaigns.</t>
+          <t>Removal of asset-level click and conversion reporting; change to the 15/4 asset limits or the always-shown H1/H2/D1 slots; AI Max text customisation becoming mandatory for Search.</t>
         </is>
       </c>
       <c r="R21" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S21" s="15" t="inlineStr">
@@ -2368,21 +2360,21 @@
     </row>
     <row r="22" ht="15" customHeight="1" s="13">
       <c r="A22" s="15" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B22" s="16" t="inlineStr">
         <is>
-          <t>Negative keyword conflict detection</t>
+          <t>Write compelling RSAs</t>
         </is>
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>Keyword &amp; query</t>
+          <t>RSA &amp; ad copy</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E22" s="15" t="inlineStr">
@@ -2392,7 +2384,7 @@
       </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G22" s="15" t="inlineStr">
@@ -2402,22 +2394,22 @@
       </c>
       <c r="H22" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I22" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J22" s="16" t="inlineStr">
         <is>
-          <t>Impressions dropped after adding negatives; routine hygiene</t>
+          <t>Writing new RSAs or rewriting underperformers</t>
         </is>
       </c>
       <c r="K22" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L22" s="15" t="inlineStr">
@@ -2428,7 +2420,7 @@
       <c r="M22" s="15" t="n"/>
       <c r="N22" s="17" t="inlineStr">
         <is>
-          <t>skills/21-negative-keyword-conflict-detection/</t>
+          <t>skills/23-write-compelling-rsas/</t>
         </is>
       </c>
       <c r="O22" s="15" t="n"/>
@@ -2439,12 +2431,12 @@
       </c>
       <c r="Q22" s="16" t="inlineStr">
         <is>
-          <t>Negatives starting to match close variants or synonyms (changes what a conflict is); Google Ads Scripts API changes breaking keyword/negative/shared-set queries; Google's built-in conflict recommendation starting to cover shared lists and match types.</t>
+          <t>Change to the 30/90 character limits or to which slots are always shown; Google routinely serving more than three headlines; mandatory AI Max text assets in Search.</t>
         </is>
       </c>
       <c r="R22" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S22" s="15" t="inlineStr">
@@ -2455,11 +2447,11 @@
     </row>
     <row r="23" ht="15" customHeight="1" s="13">
       <c r="A23" s="15" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B23" s="16" t="inlineStr">
         <is>
-          <t>RSA iteration loop</t>
+          <t>Pinning strategies</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
@@ -2469,7 +2461,7 @@
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -2489,7 +2481,7 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I23" s="15" t="inlineStr">
@@ -2499,12 +2491,12 @@
       </c>
       <c r="J23" s="16" t="inlineStr">
         <is>
-          <t>Ongoing ad copy improvement; the core testing cadence</t>
+          <t>Need message control (compliance, offer) vs. letting Google combine</t>
         </is>
       </c>
       <c r="K23" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L23" s="15" t="inlineStr">
@@ -2515,7 +2507,7 @@
       <c r="M23" s="15" t="n"/>
       <c r="N23" s="17" t="inlineStr">
         <is>
-          <t>skills/22-rsa-iteration-loop/</t>
+          <t>skills/24-pinning-strategies/</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -2526,7 +2518,7 @@
       </c>
       <c r="Q23" s="16" t="inlineStr">
         <is>
-          <t>Removal of asset-level click and conversion reporting; change to the 15/4 asset limits or the always-shown H1/H2/D1 slots; AI Max text customisation becoming mandatory for Search.</t>
+          <t>Change to which positions are guaranteed to show (H1/H2/D1); pins allowed beyond three headline positions; unpinned serving made mandatory under AI Max.</t>
         </is>
       </c>
       <c r="R23" s="15" t="inlineStr">
@@ -2542,11 +2534,11 @@
     </row>
     <row r="24" ht="15" customHeight="1" s="13">
       <c r="A24" s="15" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B24" s="16" t="inlineStr">
         <is>
-          <t>Write compelling RSAs</t>
+          <t>Ad Strength doesn't predict performance</t>
         </is>
       </c>
       <c r="C24" s="15" t="inlineStr">
@@ -2556,7 +2548,7 @@
       </c>
       <c r="D24" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E24" s="15" t="inlineStr">
@@ -2566,7 +2558,7 @@
       </c>
       <c r="F24" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G24" s="15" t="inlineStr">
@@ -2576,22 +2568,22 @@
       </c>
       <c r="H24" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I24" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J24" s="16" t="inlineStr">
         <is>
-          <t>Writing new RSAs or rewriting underperformers</t>
+          <t>Pressure to chase Excellent ad strength; deciding what to optimise instead</t>
         </is>
       </c>
       <c r="K24" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Optmyzr study</t>
         </is>
       </c>
       <c r="L24" s="15" t="inlineStr">
@@ -2602,7 +2594,7 @@
       <c r="M24" s="15" t="n"/>
       <c r="N24" s="17" t="inlineStr">
         <is>
-          <t>skills/23-write-compelling-rsas/</t>
+          <t>skills/25-ad-strength-not-performance/</t>
         </is>
       </c>
       <c r="O24" s="15" t="n"/>
@@ -2613,7 +2605,7 @@
       </c>
       <c r="Q24" s="16" t="inlineStr">
         <is>
-          <t>Change to the 30/90 character limits or to which slots are always shown; Google routinely serving more than three headlines; mandatory AI Max text assets in Search.</t>
+          <t>Google replacing Ad Strength with a performance-based score, or using it in Ad Rank or serving eligibility.</t>
         </is>
       </c>
       <c r="R24" s="15" t="inlineStr">
@@ -2629,11 +2621,11 @@
     </row>
     <row r="25" ht="15" customHeight="1" s="13">
       <c r="A25" s="15" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B25" s="16" t="inlineStr">
         <is>
-          <t>Pinning strategies</t>
+          <t>Combinations report &amp; asset ratings — what they hide</t>
         </is>
       </c>
       <c r="C25" s="15" t="inlineStr">
@@ -2643,7 +2635,7 @@
       </c>
       <c r="D25" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E25" s="15" t="inlineStr">
@@ -2653,27 +2645,27 @@
       </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G25" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H25" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I25" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J25" s="16" t="inlineStr">
         <is>
-          <t>Need message control (compliance, offer) vs. letting Google combine</t>
+          <t>Reviewing RSA assets; deciding what to replace</t>
         </is>
       </c>
       <c r="K25" s="15" t="inlineStr">
@@ -2689,7 +2681,7 @@
       <c r="M25" s="15" t="n"/>
       <c r="N25" s="17" t="inlineStr">
         <is>
-          <t>skills/24-pinning-strategies/</t>
+          <t>skills/26-combinations-and-asset-stats/</t>
         </is>
       </c>
       <c r="O25" s="15" t="n"/>
@@ -2700,7 +2692,7 @@
       </c>
       <c r="Q25" s="16" t="inlineStr">
         <is>
-          <t>Change to which positions are guaranteed to show (H1/H2/D1); pins allowed beyond three headline positions; unpinned serving made mandatory under AI Max.</t>
+          <t>Google exposing per-combination clicks and conversions; removal of asset-level statistics; return of a performance-label column as the only asset signal.</t>
         </is>
       </c>
       <c r="R25" s="15" t="inlineStr">
@@ -2716,11 +2708,11 @@
     </row>
     <row r="26" ht="23.25" customHeight="1" s="13">
       <c r="A26" s="15" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B26" s="16" t="inlineStr">
         <is>
-          <t>Ad Strength doesn't predict performance</t>
+          <t>Ad variations tool for account-wide copy tests</t>
         </is>
       </c>
       <c r="C26" s="15" t="inlineStr">
@@ -2730,7 +2722,7 @@
       </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E26" s="15" t="inlineStr">
@@ -2745,27 +2737,27 @@
       </c>
       <c r="G26" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H26" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I26" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J26" s="16" t="inlineStr">
         <is>
-          <t>Pressure to chase Excellent ad strength; deciding what to optimise instead</t>
+          <t>Want to test one change (CTA, price, claim) across many ads</t>
         </is>
       </c>
       <c r="K26" s="15" t="inlineStr">
         <is>
-          <t>Optmyzr study</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L26" s="15" t="inlineStr">
@@ -2776,7 +2768,7 @@
       <c r="M26" s="15" t="n"/>
       <c r="N26" s="17" t="inlineStr">
         <is>
-          <t>skills/25-ad-strength-not-performance/</t>
+          <t>skills/27-ad-variations-account-wide-tests/</t>
         </is>
       </c>
       <c r="O26" s="15" t="n"/>
@@ -2787,12 +2779,12 @@
       </c>
       <c r="Q26" s="16" t="inlineStr">
         <is>
-          <t>Google replacing Ad Strength with a performance-based score, or using it in Ad Rank or serving eligibility.</t>
+          <t>Google removing or redesigning Ad variations; removal of asset-level statistics; change to the 3-RSA-per-ad-group limit.</t>
         </is>
       </c>
       <c r="R26" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S26" s="15" t="inlineStr">
@@ -2803,11 +2795,11 @@
     </row>
     <row r="27" ht="15" customHeight="1" s="13">
       <c r="A27" s="15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B27" s="16" t="inlineStr">
         <is>
-          <t>Combinations report &amp; asset ratings — what they hide</t>
+          <t>Keyword-level ad customizers</t>
         </is>
       </c>
       <c r="C27" s="15" t="inlineStr">
@@ -2817,7 +2809,7 @@
       </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E27" s="15" t="inlineStr">
@@ -2827,7 +2819,7 @@
       </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G27" s="15" t="inlineStr">
@@ -2837,7 +2829,7 @@
       </c>
       <c r="H27" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I27" s="15" t="inlineStr">
@@ -2847,12 +2839,12 @@
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
-          <t>Reviewing RSA assets; deciding what to replace</t>
+          <t>Many keywords with distinct prices/variants; want 1:1 copy at scale</t>
         </is>
       </c>
       <c r="K27" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L27" s="15" t="inlineStr">
@@ -2863,7 +2855,7 @@
       <c r="M27" s="15" t="n"/>
       <c r="N27" s="17" t="inlineStr">
         <is>
-          <t>skills/26-combinations-and-asset-stats/</t>
+          <t>skills/28-keyword-level-ad-customizers/</t>
         </is>
       </c>
       <c r="O27" s="15" t="n"/>
@@ -2874,12 +2866,12 @@
       </c>
       <c r="Q27" s="16" t="inlineStr">
         <is>
-          <t>Google exposing per-combination clicks and conversions; removal of asset-level statistics; return of a performance-label column as the only asset signal.</t>
+          <t>Changes to customizer precedence or the 40-attribute cap; removal of keyword-level customizers; AI Max text customisation overriding advertiser customizer values.</t>
         </is>
       </c>
       <c r="R27" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S27" s="15" t="inlineStr">
@@ -2890,11 +2882,11 @@
     </row>
     <row r="28" ht="15" customHeight="1" s="13">
       <c r="A28" s="15" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B28" s="16" t="inlineStr">
         <is>
-          <t>Ad variations tool for account-wide copy tests</t>
+          <t>Dynamic ad customizers (countdown, location, business data)</t>
         </is>
       </c>
       <c r="C28" s="15" t="inlineStr">
@@ -2914,7 +2906,7 @@
       </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G28" s="15" t="inlineStr">
@@ -2924,17 +2916,17 @@
       </c>
       <c r="H28" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I28" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
-          <t>Want to test one change (CTA, price, claim) across many ads</t>
+          <t>Promotions with deadlines, multi-location, or feed-driven copy</t>
         </is>
       </c>
       <c r="K28" s="15" t="inlineStr">
@@ -2950,7 +2942,7 @@
       <c r="M28" s="15" t="n"/>
       <c r="N28" s="17" t="inlineStr">
         <is>
-          <t>skills/27-ad-variations-account-wide-tests/</t>
+          <t>skills/29-dynamic-ad-customizers/</t>
         </is>
       </c>
       <c r="O28" s="15" t="n"/>
@@ -2961,7 +2953,7 @@
       </c>
       <c r="Q28" s="16" t="inlineStr">
         <is>
-          <t>Google removing or redesigning Ad variations; removal of asset-level statistics; change to the 3-RSA-per-ad-group limit.</t>
+          <t>Changes to COUNTDOWN/LOCATION syntax or fallback behaviour; removal of business-data customizers; AI Max text customisation overriding advertiser customizer values.</t>
         </is>
       </c>
       <c r="R28" s="15" t="inlineStr">
@@ -2977,11 +2969,11 @@
     </row>
     <row r="29" ht="15" customHeight="1" s="13">
       <c r="A29" s="15" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" s="16" t="inlineStr">
         <is>
-          <t>Keyword-level ad customizers</t>
+          <t>One vs. two RSAs per ad group under Smart Bidding</t>
         </is>
       </c>
       <c r="C29" s="15" t="inlineStr">
@@ -2991,7 +2983,7 @@
       </c>
       <c r="D29" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E29" s="15" t="inlineStr">
@@ -3001,12 +2993,12 @@
       </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H29" s="15" t="inlineStr">
@@ -3016,17 +3008,17 @@
       </c>
       <c r="I29" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J29" s="16" t="inlineStr">
         <is>
-          <t>Many keywords with distinct prices/variants; want 1:1 copy at scale</t>
+          <t>Deciding ad count per ad group</t>
         </is>
       </c>
       <c r="K29" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner debate</t>
         </is>
       </c>
       <c r="L29" s="15" t="inlineStr">
@@ -3037,7 +3029,7 @@
       <c r="M29" s="15" t="n"/>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t>skills/28-keyword-level-ad-customizers/</t>
+          <t>skills/31-one-vs-two-rsas/</t>
         </is>
       </c>
       <c r="O29" s="15" t="n"/>
@@ -3048,12 +3040,12 @@
       </c>
       <c r="Q29" s="16" t="inlineStr">
         <is>
-          <t>Changes to customizer precedence or the 40-attribute cap; removal of keyword-level customizers; AI Max text customisation overriding advertiser customizer values.</t>
+          <t>A change to the per-ad-group RSA limit; removal of per-ad reporting; a single auto-generated ad per ad group under AI Max.</t>
         </is>
       </c>
       <c r="R29" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S29" s="15" t="inlineStr">
@@ -3064,11 +3056,11 @@
     </row>
     <row r="30" ht="15" customHeight="1" s="13">
       <c r="A30" s="15" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" s="16" t="inlineStr">
         <is>
-          <t>Dynamic ad customizers (countdown, location, business data)</t>
+          <t>Headline count &amp; pinning for compliance-heavy verticals</t>
         </is>
       </c>
       <c r="C30" s="15" t="inlineStr">
@@ -3078,7 +3070,7 @@
       </c>
       <c r="D30" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E30" s="15" t="inlineStr">
@@ -3088,12 +3080,12 @@
       </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G30" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H30" s="15" t="inlineStr">
@@ -3103,17 +3095,17 @@
       </c>
       <c r="I30" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J30" s="16" t="inlineStr">
         <is>
-          <t>Promotions with deadlines, multi-location, or feed-driven copy</t>
+          <t>Finance/health/legal clients needing fixed disclaimers</t>
         </is>
       </c>
       <c r="K30" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L30" s="15" t="inlineStr">
@@ -3124,7 +3116,7 @@
       <c r="M30" s="15" t="n"/>
       <c r="N30" s="17" t="inlineStr">
         <is>
-          <t>skills/29-dynamic-ad-customizers/</t>
+          <t>skills/32-compliance-pinning/</t>
         </is>
       </c>
       <c r="O30" s="15" t="n"/>
@@ -3135,12 +3127,12 @@
       </c>
       <c r="Q30" s="16" t="inlineStr">
         <is>
-          <t>Changes to COUNTDOWN/LOCATION syntax or fallback behaviour; removal of business-data customizers; AI Max text customisation overriding advertiser customizer values.</t>
+          <t>Change to which slots are always shown (H1/H2/D1); a native advertiser-controlled disclaimer field for Search RSAs; AI Max text customisation becoming mandatory or ignoring text guidelines.</t>
         </is>
       </c>
       <c r="R30" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S30" s="15" t="inlineStr">
@@ -3151,21 +3143,21 @@
     </row>
     <row r="31" ht="15" customHeight="1" s="13">
       <c r="A31" s="15" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B31" s="16" t="inlineStr">
         <is>
-          <t>Campaign-name-as-headline diagnostic trick</t>
+          <t>Improve Expected CTR</t>
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D31" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E31" s="15" t="inlineStr">
@@ -3175,7 +3167,7 @@
       </c>
       <c r="F31" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G31" s="15" t="inlineStr">
@@ -3190,35 +3182,31 @@
       </c>
       <c r="I31" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J31" s="16" t="inlineStr">
         <is>
-          <t>Need to know which ad group/campaign a query actually fires from</t>
+          <t>Expected CTR below average on spend-heavy keywords</t>
         </is>
       </c>
       <c r="K31" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L31" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M31" s="15" t="n"/>
       <c r="N31" s="17" t="inlineStr">
         <is>
-          <t>skills/30-campaign-name-headline-diagnostic/</t>
-        </is>
-      </c>
-      <c r="O31" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/34-improve-expected-ctr/</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="n"/>
       <c r="P31" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -3226,37 +3214,37 @@
       </c>
       <c r="Q31" s="16" t="inlineStr">
         <is>
-          <t>Not applicable until a method exists; any method depends on the 15-character path fields and the always-shown H1/H2/D1 slots.</t>
+          <t>Google changing the expected-CTR comparison set (currently exact-same-keyword, trailing 90 days) or folding assets into QS; retirement of keyword-level QS reporting.</t>
         </is>
       </c>
       <c r="R31" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S31" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="32" ht="15" customHeight="1" s="13">
       <c r="A32" s="15" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B32" s="16" t="inlineStr">
         <is>
-          <t>One vs. two RSAs per ad group under Smart Bidding</t>
+          <t>Improve Ad Relevance</t>
         </is>
       </c>
       <c r="C32" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D32" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E32" s="15" t="inlineStr">
@@ -3266,7 +3254,7 @@
       </c>
       <c r="F32" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G32" s="15" t="inlineStr">
@@ -3276,22 +3264,22 @@
       </c>
       <c r="H32" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I32" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J32" s="16" t="inlineStr">
         <is>
-          <t>Deciding ad count per ad group</t>
+          <t>Ad relevance below average; keyword-to-ad mismatch</t>
         </is>
       </c>
       <c r="K32" s="15" t="inlineStr">
         <is>
-          <t>Practitioner debate</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L32" s="15" t="inlineStr">
@@ -3302,7 +3290,7 @@
       <c r="M32" s="15" t="n"/>
       <c r="N32" s="17" t="inlineStr">
         <is>
-          <t>skills/31-one-vs-two-rsas/</t>
+          <t>skills/35-improve-ad-relevance/</t>
         </is>
       </c>
       <c r="O32" s="15" t="n"/>
@@ -3313,12 +3301,12 @@
       </c>
       <c r="Q32" s="16" t="inlineStr">
         <is>
-          <t>A change to the per-ad-group RSA limit; removal of per-ad reporting; a single auto-generated ad per ad group under AI Max.</t>
+          <t>Google merging ad relevance into an asset-level signal, changing the exact-same-keyword comparison set, or removing keyword-level component reporting.</t>
         </is>
       </c>
       <c r="R32" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S32" s="15" t="inlineStr">
@@ -3329,21 +3317,21 @@
     </row>
     <row r="33" ht="15" customHeight="1" s="13">
       <c r="A33" s="15" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="B33" s="16" t="inlineStr">
         <is>
-          <t>Headline count &amp; pinning for compliance-heavy verticals</t>
+          <t>Improve Landing Page Experience</t>
         </is>
       </c>
       <c r="C33" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D33" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E33" s="15" t="inlineStr">
@@ -3353,7 +3341,7 @@
       </c>
       <c r="F33" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G33" s="15" t="inlineStr">
@@ -3363,22 +3351,22 @@
       </c>
       <c r="H33" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I33" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J33" s="16" t="inlineStr">
         <is>
-          <t>Finance/health/legal clients needing fixed disclaimers</t>
+          <t>LPE below average; CPCs high relative to competitors</t>
         </is>
       </c>
       <c r="K33" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L33" s="15" t="inlineStr">
@@ -3389,7 +3377,7 @@
       <c r="M33" s="15" t="n"/>
       <c r="N33" s="17" t="inlineStr">
         <is>
-          <t>skills/32-compliance-pinning/</t>
+          <t>skills/36-improve-landing-page-experience/</t>
         </is>
       </c>
       <c r="O33" s="15" t="n"/>
@@ -3400,12 +3388,12 @@
       </c>
       <c r="Q33" s="16" t="inlineStr">
         <is>
-          <t>Change to which slots are always shown (H1/H2/D1); a native advertiser-controlled disclaimer field for Search RSAs; AI Max text customisation becoming mandatory or ignoring text guidelines.</t>
+          <t>Google replacing crawler-based LPE with a separately reported Core Web Vitals or engagement signal, removing LPE from the keyword report, or changing the exact-same-keyword comparison set.</t>
         </is>
       </c>
       <c r="R33" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S33" s="15" t="inlineStr">
@@ -3416,11 +3404,11 @@
     </row>
     <row r="34" ht="15" customHeight="1" s="13">
       <c r="A34" s="15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B34" s="16" t="inlineStr">
         <is>
-          <t>Improve Expected CTR</t>
+          <t>QS tracker script (daily snapshot)</t>
         </is>
       </c>
       <c r="C34" s="15" t="inlineStr">
@@ -3430,7 +3418,7 @@
       </c>
       <c r="D34" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E34" s="15" t="inlineStr">
@@ -3440,7 +3428,7 @@
       </c>
       <c r="F34" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G34" s="15" t="inlineStr">
@@ -3450,22 +3438,22 @@
       </c>
       <c r="H34" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I34" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J34" s="16" t="inlineStr">
         <is>
-          <t>Expected CTR below average on spend-heavy keywords</t>
+          <t>Need QS history, which Google doesn't keep</t>
         </is>
       </c>
       <c r="K34" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Brainlabs / Optmyzr</t>
         </is>
       </c>
       <c r="L34" s="15" t="inlineStr">
@@ -3476,7 +3464,7 @@
       <c r="M34" s="15" t="n"/>
       <c r="N34" s="17" t="inlineStr">
         <is>
-          <t>skills/34-improve-expected-ctr/</t>
+          <t>skills/37-qs-tracker-script/</t>
         </is>
       </c>
       <c r="O34" s="15" t="n"/>
@@ -3487,7 +3475,7 @@
       </c>
       <c r="Q34" s="16" t="inlineStr">
         <is>
-          <t>Google changing the expected-CTR comparison set (currently exact-same-keyword, trailing 90 days) or folding assets into QS; retirement of keyword-level QS reporting.</t>
+          <t>Removal of quality_info from the Google Ads API/Scripts reports, a change to the Scripts 30-minute execution limit, or Google shipping native impression-weighted QS trend charts.</t>
         </is>
       </c>
       <c r="R34" s="15" t="inlineStr">
@@ -3503,11 +3491,11 @@
     </row>
     <row r="35" ht="15" customHeight="1" s="13">
       <c r="A35" s="15" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B35" s="16" t="inlineStr">
         <is>
-          <t>Improve Ad Relevance</t>
+          <t>Impression-weighted QS as the account metric</t>
         </is>
       </c>
       <c r="C35" s="15" t="inlineStr">
@@ -3527,7 +3515,7 @@
       </c>
       <c r="F35" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G35" s="15" t="inlineStr">
@@ -3537,22 +3525,22 @@
       </c>
       <c r="H35" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I35" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J35" s="16" t="inlineStr">
         <is>
-          <t>Ad relevance below average; keyword-to-ad mismatch</t>
+          <t>Reporting QS; average QS is misleading</t>
         </is>
       </c>
       <c r="K35" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L35" s="15" t="inlineStr">
@@ -3563,7 +3551,7 @@
       <c r="M35" s="15" t="n"/>
       <c r="N35" s="17" t="inlineStr">
         <is>
-          <t>skills/35-improve-ad-relevance/</t>
+          <t>skills/38-impression-weighted-qs/</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -3574,12 +3562,12 @@
       </c>
       <c r="Q35" s="16" t="inlineStr">
         <is>
-          <t>Google merging ad relevance into an asset-level signal, changing the exact-same-keyword comparison set, or removing keyword-level component reporting.</t>
+          <t>Google publishing a native weighted account-level quality metric, removing keyword-level QS, or changing the null-QS rule.</t>
         </is>
       </c>
       <c r="R35" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S35" s="15" t="inlineStr">
@@ -3590,11 +3578,11 @@
     </row>
     <row r="36" ht="15" customHeight="1" s="13">
       <c r="A36" s="15" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B36" s="16" t="inlineStr">
         <is>
-          <t>Improve Landing Page Experience</t>
+          <t>Does QS matter under Smart Bidding — the evidence</t>
         </is>
       </c>
       <c r="C36" s="15" t="inlineStr">
@@ -3604,7 +3592,7 @@
       </c>
       <c r="D36" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E36" s="15" t="inlineStr">
@@ -3624,22 +3612,22 @@
       </c>
       <c r="H36" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I36" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
-          <t>LPE below average; CPCs high relative to competitors</t>
+          <t>Deciding how much effort to put into QS work</t>
         </is>
       </c>
       <c r="K36" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Practitioner debate</t>
         </is>
       </c>
       <c r="L36" s="15" t="inlineStr">
@@ -3650,7 +3638,7 @@
       <c r="M36" s="15" t="n"/>
       <c r="N36" s="17" t="inlineStr">
         <is>
-          <t>skills/36-improve-landing-page-experience/</t>
+          <t>skills/39-qs-under-smart-bidding/</t>
         </is>
       </c>
       <c r="O36" s="15" t="n"/>
@@ -3661,7 +3649,7 @@
       </c>
       <c r="Q36" s="16" t="inlineStr">
         <is>
-          <t>Google replacing crawler-based LPE with a separately reported Core Web Vitals or engagement signal, removing LPE from the keyword report, or changing the exact-same-keyword comparison set.</t>
+          <t>Google publishing how Smart Bidding treats quality components, a canon cross-account study of QS work under Smart Bidding, or removal of keyword-level QS.</t>
         </is>
       </c>
       <c r="R36" s="15" t="inlineStr">
@@ -3677,21 +3665,21 @@
     </row>
     <row r="37" ht="15" customHeight="1" s="13">
       <c r="A37" s="15" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" s="16" t="inlineStr">
         <is>
-          <t>QS tracker script (daily snapshot)</t>
+          <t>Portfolio bid strategies with max CPC caps</t>
         </is>
       </c>
       <c r="C37" s="15" t="inlineStr">
         <is>
-          <t>Quality Score</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D37" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E37" s="15" t="inlineStr">
@@ -3701,12 +3689,12 @@
       </c>
       <c r="F37" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G37" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H37" s="15" t="inlineStr">
@@ -3716,17 +3704,17 @@
       </c>
       <c r="I37" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
-          <t>Need QS history, which Google doesn't keep</t>
+          <t>Smart Bidding overpaying on clicks; need a ceiling</t>
         </is>
       </c>
       <c r="K37" s="15" t="inlineStr">
         <is>
-          <t>Brainlabs / Optmyzr</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L37" s="15" t="inlineStr">
@@ -3737,7 +3725,7 @@
       <c r="M37" s="15" t="n"/>
       <c r="N37" s="17" t="inlineStr">
         <is>
-          <t>skills/37-qs-tracker-script/</t>
+          <t>skills/40-portfolio-max-cpc-caps/</t>
         </is>
       </c>
       <c r="O37" s="15" t="n"/>
@@ -3748,7 +3736,7 @@
       </c>
       <c r="Q37" s="16" t="inlineStr">
         <is>
-          <t>Removal of quality_info from the Google Ads API/Scripts reports, a change to the Scripts 30-minute execution limit, or Google shipping native impression-weighted QS trend charts.</t>
+          <t>Google adding bid limits to standard (non-portfolio) strategies, removing them from portfolios, extending them beyond Search auctions, or reversing the 17 Aug 2026 budget-limited bidding change.</t>
         </is>
       </c>
       <c r="R37" s="15" t="inlineStr">
@@ -3764,16 +3752,16 @@
     </row>
     <row r="38" ht="15" customHeight="1" s="13">
       <c r="A38" s="15" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="16" t="inlineStr">
         <is>
-          <t>Impression-weighted QS as the account metric</t>
+          <t>Conversion value rules</t>
         </is>
       </c>
       <c r="C38" s="15" t="inlineStr">
         <is>
-          <t>Quality Score</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D38" s="15" t="inlineStr">
@@ -3783,22 +3771,22 @@
       </c>
       <c r="E38" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F38" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G38" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H38" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I38" s="15" t="inlineStr">
@@ -3808,12 +3796,12 @@
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
-          <t>Reporting QS; average QS is misleading</t>
+          <t>Want tROAS to favour an audience/location/device without splitting campaigns</t>
         </is>
       </c>
       <c r="K38" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L38" s="15" t="inlineStr">
@@ -3824,7 +3812,7 @@
       <c r="M38" s="15" t="n"/>
       <c r="N38" s="17" t="inlineStr">
         <is>
-          <t>skills/38-impression-weighted-qs/</t>
+          <t>skills/41-conversion-value-rules/</t>
         </is>
       </c>
       <c r="O38" s="15" t="n"/>
@@ -3835,12 +3823,12 @@
       </c>
       <c r="Q38" s="16" t="inlineStr">
         <is>
-          <t>Google publishing a native weighted account-level quality metric, removing keyword-level QS, or changing the null-QS rule.</t>
+          <t>Google changing the multiplier range (0.5–10×), the two-dimension limit, the one-rule-per-conversion precedence, or extending rules to non-value bid strategies.</t>
         </is>
       </c>
       <c r="R38" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S38" s="15" t="inlineStr">
@@ -3851,36 +3839,36 @@
     </row>
     <row r="39" ht="15" customHeight="1" s="13">
       <c r="A39" s="15" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B39" s="16" t="inlineStr">
         <is>
-          <t>Does QS matter under Smart Bidding — the evidence</t>
+          <t>Value-based bidding for lead gen (proxy values)</t>
         </is>
       </c>
       <c r="C39" s="15" t="inlineStr">
         <is>
-          <t>Quality Score</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D39" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E39" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F39" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G39" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H39" s="15" t="inlineStr">
@@ -3890,17 +3878,17 @@
       </c>
       <c r="I39" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
-          <t>Deciding how much effort to put into QS work</t>
+          <t>Lead-gen client; leads differ in quality; moving from tCPA to tROAS</t>
         </is>
       </c>
       <c r="K39" s="15" t="inlineStr">
         <is>
-          <t>Practitioner debate</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L39" s="15" t="inlineStr">
@@ -3911,7 +3899,7 @@
       <c r="M39" s="15" t="n"/>
       <c r="N39" s="17" t="inlineStr">
         <is>
-          <t>skills/39-qs-under-smart-bidding/</t>
+          <t>skills/42-value-based-bidding-lead-gen/</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
@@ -3922,12 +3910,12 @@
       </c>
       <c r="Q39" s="16" t="inlineStr">
         <is>
-          <t>Google publishing how Smart Bidding treats quality components, a canon cross-account study of QS work under Smart Bidding, or removal of keyword-level QS.</t>
+          <t>Google changing conversion value rules, removing Max Conversion Value without a target, changing tROAS eligibility floors, or the Data Manager API changing offline value upload.</t>
         </is>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S39" s="15" t="inlineStr">
@@ -3938,11 +3926,11 @@
     </row>
     <row r="40" ht="15" customHeight="1" s="13">
       <c r="A40" s="15" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B40" s="16" t="inlineStr">
         <is>
-          <t>Portfolio bid strategies with max CPC caps</t>
+          <t>Micro-conversion ladder for new accounts</t>
         </is>
       </c>
       <c r="C40" s="15" t="inlineStr">
@@ -3952,22 +3940,22 @@
       </c>
       <c r="D40" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E40" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F40" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G40" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H40" s="15" t="inlineStr">
@@ -3982,12 +3970,12 @@
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
-          <t>Smart Bidding overpaying on clicks; need a ceiling</t>
+          <t>Too few macro conversions for Smart Bidding to learn</t>
         </is>
       </c>
       <c r="K40" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L40" s="15" t="inlineStr">
@@ -3998,7 +3986,7 @@
       <c r="M40" s="15" t="n"/>
       <c r="N40" s="17" t="inlineStr">
         <is>
-          <t>skills/40-portfolio-max-cpc-caps/</t>
+          <t>skills/43-micro-conversion-ladder/</t>
         </is>
       </c>
       <c r="O40" s="15" t="n"/>
@@ -4009,12 +3997,12 @@
       </c>
       <c r="Q40" s="16" t="inlineStr">
         <is>
-          <t>Google adding bid limits to standard (non-portfolio) strategies, removing them from portfolios, extending them beyond Search auctions, or reversing the 17 Aug 2026 budget-limited bidding change.</t>
+          <t>Google removing the primary/secondary conversion distinction, changing the Smart Bidding data floors, or retiring Maximize Clicks.</t>
         </is>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S40" s="15" t="inlineStr">
@@ -4025,11 +4013,11 @@
     </row>
     <row r="41" ht="15" customHeight="1" s="13">
       <c r="A41" s="15" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B41" s="16" t="inlineStr">
         <is>
-          <t>Conversion value rules</t>
+          <t>Seasonality adjustments vs. data exclusions</t>
         </is>
       </c>
       <c r="C41" s="15" t="inlineStr">
@@ -4059,7 +4047,7 @@
       </c>
       <c r="H41" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I41" s="15" t="inlineStr">
@@ -4069,7 +4057,7 @@
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
-          <t>Want tROAS to favour an audience/location/device without splitting campaigns</t>
+          <t>Short sale coming, or a tracking outage happened</t>
         </is>
       </c>
       <c r="K41" s="15" t="inlineStr">
@@ -4085,7 +4073,7 @@
       <c r="M41" s="15" t="n"/>
       <c r="N41" s="17" t="inlineStr">
         <is>
-          <t>skills/41-conversion-value-rules/</t>
+          <t>skills/44-seasonality-adjustments-vs-data-exclusions/</t>
         </is>
       </c>
       <c r="O41" s="15" t="n"/>
@@ -4096,12 +4084,12 @@
       </c>
       <c r="Q41" s="16" t="inlineStr">
         <is>
-          <t>Google changing the multiplier range (0.5–10×), the two-dimension limit, the one-rule-per-conversion precedence, or extending rules to non-value bid strategies.</t>
+          <t>Google changing seasonality-adjustment duration guidance or the 0.1–10 modifier range, changing data exclusions to conversion-based rather than click-based, or new cross-account evidence that adjustments on mainstream events stopped inflating CPCs.</t>
         </is>
       </c>
       <c r="R41" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S41" s="15" t="inlineStr">
@@ -4112,11 +4100,11 @@
     </row>
     <row r="42" ht="23.25" customHeight="1" s="13">
       <c r="A42" s="15" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B42" s="16" t="inlineStr">
         <is>
-          <t>Value-based bidding for lead gen (proxy values)</t>
+          <t>Target impression share for brand defence</t>
         </is>
       </c>
       <c r="C42" s="15" t="inlineStr">
@@ -4131,17 +4119,17 @@
       </c>
       <c r="E42" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F42" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G42" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H42" s="15" t="inlineStr">
@@ -4151,12 +4139,12 @@
       </c>
       <c r="I42" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
-          <t>Lead-gen client; leads differ in quality; moving from tCPA to tROAS</t>
+          <t>Competitors bidding on brand; deciding how to defend</t>
         </is>
       </c>
       <c r="K42" s="15" t="inlineStr">
@@ -4172,7 +4160,7 @@
       <c r="M42" s="15" t="n"/>
       <c r="N42" s="17" t="inlineStr">
         <is>
-          <t>skills/42-value-based-bidding-lead-gen/</t>
+          <t>skills/45-target-impression-share-brand-defence/</t>
         </is>
       </c>
       <c r="O42" s="15" t="n"/>
@@ -4183,7 +4171,7 @@
       </c>
       <c r="Q42" s="16" t="inlineStr">
         <is>
-          <t>Google changing conversion value rules, removing Max Conversion Value without a target, changing tROAS eligibility floors, or the Data Manager API changing offline value upload.</t>
+          <t>Google removing the bid limit from Target Impression Share, changing Ad Rank reserve pricing on uncontested auctions, or restricting competitor brand bidding by policy.</t>
         </is>
       </c>
       <c r="R42" s="15" t="inlineStr">
@@ -4199,11 +4187,11 @@
     </row>
     <row r="43" ht="15" customHeight="1" s="13">
       <c r="A43" s="15" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B43" s="16" t="inlineStr">
         <is>
-          <t>Micro-conversion ladder for new accounts</t>
+          <t>Bid simulator &amp; 'target too aggressive' diagnosis</t>
         </is>
       </c>
       <c r="C43" s="15" t="inlineStr">
@@ -4213,7 +4201,7 @@
       </c>
       <c r="D43" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E43" s="15" t="inlineStr">
@@ -4223,27 +4211,27 @@
       </c>
       <c r="F43" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G43" s="15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H43" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I43" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>Too few macro conversions for Smart Bidding to learn</t>
+          <t>Spend dropped after a target change; campaign underdelivering</t>
         </is>
       </c>
       <c r="K43" s="15" t="inlineStr">
@@ -4259,7 +4247,7 @@
       <c r="M43" s="15" t="n"/>
       <c r="N43" s="17" t="inlineStr">
         <is>
-          <t>skills/43-micro-conversion-ladder/</t>
+          <t>skills/46-bid-simulator-target-too-aggressive/</t>
         </is>
       </c>
       <c r="O43" s="15" t="n"/>
@@ -4270,12 +4258,12 @@
       </c>
       <c r="Q43" s="16" t="inlineStr">
         <is>
-          <t>Google removing the primary/secondary conversion distinction, changing the Smart Bidding data floors, or retiring Maximize Clicks.</t>
+          <t>Google changing the simulator data window or availability rules, reversing the 17 Aug 2026 budget-limited bidding change, or changing the bid strategy report's average-target reporting.</t>
         </is>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S43" s="15" t="inlineStr">
@@ -4286,11 +4274,11 @@
     </row>
     <row r="44" ht="15" customHeight="1" s="13">
       <c r="A44" s="15" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B44" s="16" t="inlineStr">
         <is>
-          <t>Seasonality adjustments vs. data exclusions</t>
+          <t>Enhanced conversions — measurement uplift &amp; when it pays</t>
         </is>
       </c>
       <c r="C44" s="15" t="inlineStr">
@@ -4300,7 +4288,7 @@
       </c>
       <c r="D44" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E44" s="15" t="inlineStr">
@@ -4310,17 +4298,17 @@
       </c>
       <c r="F44" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G44" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H44" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I44" s="15" t="inlineStr">
@@ -4330,7 +4318,7 @@
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>Short sale coming, or a tracking outage happened</t>
+          <t>Deciding whether the setup effort is worth it for a client</t>
         </is>
       </c>
       <c r="K44" s="15" t="inlineStr">
@@ -4346,7 +4334,7 @@
       <c r="M44" s="15" t="n"/>
       <c r="N44" s="17" t="inlineStr">
         <is>
-          <t>skills/44-seasonality-adjustments-vs-data-exclusions/</t>
+          <t>skills/47-enhanced-conversions-uplift/</t>
         </is>
       </c>
       <c r="O44" s="15" t="n"/>
@@ -4357,12 +4345,12 @@
       </c>
       <c r="Q44" s="16" t="inlineStr">
         <is>
-          <t>Google changing seasonality-adjustment duration guidance or the 0.1–10 modifier range, changing data exclusions to conversion-based rather than click-based, or new cross-account evidence that adjustments on mainstream events stopped inflating CPCs.</t>
+          <t>Google changing the matching mechanism, removing the GCLID requirement/recommendation, changing the single on/off setting introduced April 2026, or publishing per-account uplift reporting that makes the verification protocol redundant.</t>
         </is>
       </c>
       <c r="R44" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S44" s="15" t="inlineStr">
@@ -4373,11 +4361,11 @@
     </row>
     <row r="45" ht="15" customHeight="1" s="13">
       <c r="A45" s="15" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B45" s="16" t="inlineStr">
         <is>
-          <t>Target impression share for brand defence</t>
+          <t>Offline conversion import with lead stages</t>
         </is>
       </c>
       <c r="C45" s="15" t="inlineStr">
@@ -4387,22 +4375,22 @@
       </c>
       <c r="D45" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E45" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F45" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G45" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H45" s="15" t="inlineStr">
@@ -4412,17 +4400,17 @@
       </c>
       <c r="I45" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>Competitors bidding on brand; deciding how to defend</t>
+          <t>B2B/long sales cycle; want Smart Bidding on SQL/closed-won</t>
         </is>
       </c>
       <c r="K45" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L45" s="15" t="inlineStr">
@@ -4433,7 +4421,7 @@
       <c r="M45" s="15" t="n"/>
       <c r="N45" s="17" t="inlineStr">
         <is>
-          <t>skills/45-target-impression-share-brand-defence/</t>
+          <t>skills/48-offline-conversion-import-lead-stages/</t>
         </is>
       </c>
       <c r="O45" s="15" t="n"/>
@@ -4444,7 +4432,7 @@
       </c>
       <c r="Q45" s="16" t="inlineStr">
         <is>
-          <t>Google removing the bid limit from Target Impression Share, changing Ad Rank reserve pricing on uncontested auctions, or restricting competitor brand bidding by policy.</t>
+          <t>Google changing the GCLID upload/restatement windows, the 90-day click window, Data Manager source cadences, or deprecating classic offline conversion import in favour of enhanced conversions for leads only.</t>
         </is>
       </c>
       <c r="R45" s="15" t="inlineStr">
@@ -4460,11 +4448,11 @@
     </row>
     <row r="46" ht="15" customHeight="1" s="13">
       <c r="A46" s="15" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B46" s="16" t="inlineStr">
         <is>
-          <t>Bid simulator &amp; 'target too aggressive' diagnosis</t>
+          <t>Conversion lag modelling</t>
         </is>
       </c>
       <c r="C46" s="15" t="inlineStr">
@@ -4494,7 +4482,7 @@
       </c>
       <c r="H46" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I46" s="15" t="inlineStr">
@@ -4504,7 +4492,7 @@
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
-          <t>Spend dropped after a target change; campaign underdelivering</t>
+          <t>Recent performance looks bad; need to adjust for lag before acting</t>
         </is>
       </c>
       <c r="K46" s="15" t="inlineStr">
@@ -4520,7 +4508,7 @@
       <c r="M46" s="15" t="n"/>
       <c r="N46" s="17" t="inlineStr">
         <is>
-          <t>skills/46-bid-simulator-target-too-aggressive/</t>
+          <t>skills/49-conversion-lag-modelling/</t>
         </is>
       </c>
       <c r="O46" s="15" t="n"/>
@@ -4531,12 +4519,12 @@
       </c>
       <c r="Q46" s="16" t="inlineStr">
         <is>
-          <t>Google changing the simulator data window or availability rules, reversing the 17 Aug 2026 budget-limited bidding change, or changing the bid strategy report's average-target reporting.</t>
+          <t>Google changing conversion-time reporting or the lag-bucket segments, the 90-day click window, or how late conversions are weighted in Smart Bidding.</t>
         </is>
       </c>
       <c r="R46" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S46" s="15" t="inlineStr">
@@ -4547,56 +4535,56 @@
     </row>
     <row r="47" ht="15" customHeight="1" s="13">
       <c r="A47" s="15" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B47" s="16" t="inlineStr">
         <is>
-          <t>Enhanced conversions — measurement uplift &amp; when it pays</t>
+          <t>RLSA layering under Smart Bidding</t>
         </is>
       </c>
       <c r="C47" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Audiences</t>
         </is>
       </c>
       <c r="D47" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E47" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F47" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G47" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H47" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I47" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
-          <t>Deciding whether the setup effort is worth it for a client</t>
+          <t>Have remarketing lists; deciding observation vs. target vs. bid adj</t>
         </is>
       </c>
       <c r="K47" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L47" s="15" t="inlineStr">
@@ -4607,7 +4595,7 @@
       <c r="M47" s="15" t="n"/>
       <c r="N47" s="17" t="inlineStr">
         <is>
-          <t>skills/47-enhanced-conversions-uplift/</t>
+          <t>skills/50-rlsa-layering-smart-bidding/</t>
         </is>
       </c>
       <c r="O47" s="15" t="n"/>
@@ -4618,7 +4606,7 @@
       </c>
       <c r="Q47" s="16" t="inlineStr">
         <is>
-          <t>Google changing the matching mechanism, removing the GCLID requirement/recommendation, changing the single on/off setting introduced April 2026, or publishing per-account uplift reporting that makes the verification protocol redundant.</t>
+          <t>Google documenting that Smart Bidding honours audience bid adjustments other than -100%; removal of observation mode from Search; conversion value rules extended to tCPA/Max Conversions; Google ending automatic use of first-party lists as Search signals.</t>
         </is>
       </c>
       <c r="R47" s="15" t="inlineStr">
@@ -4634,21 +4622,21 @@
     </row>
     <row r="48" ht="15" customHeight="1" s="13">
       <c r="A48" s="15" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B48" s="16" t="inlineStr">
         <is>
-          <t>Offline conversion import with lead stages</t>
+          <t>Customer Match as signal vs. target</t>
         </is>
       </c>
       <c r="C48" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Audiences</t>
         </is>
       </c>
       <c r="D48" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E48" s="15" t="inlineStr">
@@ -4668,17 +4656,17 @@
       </c>
       <c r="H48" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I48" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
-          <t>B2B/long sales cycle; want Smart Bidding on SQL/closed-won</t>
+          <t>Have first-party lists; deciding how to use them and refresh cadence</t>
         </is>
       </c>
       <c r="K48" s="15" t="inlineStr">
@@ -4694,7 +4682,7 @@
       <c r="M48" s="15" t="n"/>
       <c r="N48" s="17" t="inlineStr">
         <is>
-          <t>skills/48-offline-conversion-import-lead-stages/</t>
+          <t>skills/51-customer-match-signal-vs-target/</t>
         </is>
       </c>
       <c r="O48" s="15" t="n"/>
@@ -4705,12 +4693,12 @@
       </c>
       <c r="Q48" s="16" t="inlineStr">
         <is>
-          <t>Google changing the GCLID upload/restatement windows, the 90-day click window, Data Manager source cadences, or deprecating classic offline conversion import in favour of enhanced conversions for leads only.</t>
+          <t>Google removing the account-level "Use all Customer Match lists in Smart Bidding or Optimized Targeting" opt-out; changes to the 540-day membership cap or the 100-active-members eligibility rule; Customer Match becoming usable under manual bidding.</t>
         </is>
       </c>
       <c r="R48" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S48" s="15" t="inlineStr">
@@ -4721,21 +4709,21 @@
     </row>
     <row r="49" ht="15" customHeight="1" s="13">
       <c r="A49" s="15" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B49" s="16" t="inlineStr">
         <is>
-          <t>Conversion lag modelling</t>
+          <t>B2B audience exclusions (demographic, in-market, HHI)</t>
         </is>
       </c>
       <c r="C49" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Audiences</t>
         </is>
       </c>
       <c r="D49" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E49" s="15" t="inlineStr">
@@ -4745,17 +4733,17 @@
       </c>
       <c r="F49" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G49" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H49" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I49" s="15" t="inlineStr">
@@ -4765,7 +4753,7 @@
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
-          <t>Recent performance looks bad; need to adjust for lag before acting</t>
+          <t>B2B client getting consumer traffic</t>
         </is>
       </c>
       <c r="K49" s="15" t="inlineStr">
@@ -4781,7 +4769,7 @@
       <c r="M49" s="15" t="n"/>
       <c r="N49" s="17" t="inlineStr">
         <is>
-          <t>skills/49-conversion-lag-modelling/</t>
+          <t>skills/52-b2b-audience-exclusions/</t>
         </is>
       </c>
       <c r="O49" s="15" t="n"/>
@@ -4792,7 +4780,7 @@
       </c>
       <c r="Q49" s="16" t="inlineStr">
         <is>
-          <t>Google changing conversion-time reporting or the lag-bucket segments, the 90-day click window, or how late conversions are weighted in Smart Bidding.</t>
+          <t>Google adding parental status, life events or custom segments to Search; HHI becoming available in European markets; Smart Bidding honouring non-(-100%) audience bid adjustments; demographics gaining an observation setting.</t>
         </is>
       </c>
       <c r="R49" s="15" t="inlineStr">
@@ -4808,11 +4796,11 @@
     </row>
     <row r="50" ht="15" customHeight="1" s="13">
       <c r="A50" s="15" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B50" s="16" t="inlineStr">
         <is>
-          <t>RLSA layering under Smart Bidding</t>
+          <t>GA4 first-party segments into Google Ads</t>
         </is>
       </c>
       <c r="C50" s="15" t="inlineStr">
@@ -4822,42 +4810,42 @@
       </c>
       <c r="D50" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E50" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F50" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G50" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H50" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I50" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
-          <t>Have remarketing lists; deciding observation vs. target vs. bid adj</t>
+          <t>GA4 linked; want behavioural segments as signals</t>
         </is>
       </c>
       <c r="K50" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L50" s="15" t="inlineStr">
@@ -4868,7 +4856,7 @@
       <c r="M50" s="15" t="n"/>
       <c r="N50" s="17" t="inlineStr">
         <is>
-          <t>skills/50-rlsa-layering-smart-bidding/</t>
+          <t>skills/54-ga4-segments-into-google-ads/</t>
         </is>
       </c>
       <c r="O50" s="15" t="n"/>
@@ -4879,7 +4867,7 @@
       </c>
       <c r="Q50" s="16" t="inlineStr">
         <is>
-          <t>Google documenting that Smart Bidding honours audience bid adjustments other than -100%; removal of observation mode from Search; conversion value rules extended to tCPA/Max Conversions; Google ending automatic use of first-party lists as Search signals.</t>
+          <t>GA4 removing the 30-day backfill or changing the 100-audience cap; GA4 Customer Match leaving beta with different mechanics; Google Ads deprecating tag-based remarketing lists; consent-mode changes to which GA4 users are exportable.</t>
         </is>
       </c>
       <c r="R50" s="15" t="inlineStr">
@@ -4895,51 +4883,51 @@
     </row>
     <row r="51" ht="15" customHeight="1" s="13">
       <c r="A51" s="15" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B51" s="16" t="inlineStr">
         <is>
-          <t>Customer Match as signal vs. target</t>
+          <t>PMax brand exclusions — full method</t>
         </is>
       </c>
       <c r="C51" s="15" t="inlineStr">
         <is>
-          <t>Audiences</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D51" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E51" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F51" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G51" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H51" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I51" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
-          <t>Have first-party lists; deciding how to use them and refresh cadence</t>
+          <t>PMax eating brand traffic and inflating ROAS</t>
         </is>
       </c>
       <c r="K51" s="15" t="inlineStr">
@@ -4955,7 +4943,7 @@
       <c r="M51" s="15" t="n"/>
       <c r="N51" s="17" t="inlineStr">
         <is>
-          <t>skills/51-customer-match-signal-vs-target/</t>
+          <t>skills/55-pmax-brand-exclusions/</t>
         </is>
       </c>
       <c r="O51" s="15" t="n"/>
@@ -4966,12 +4954,12 @@
       </c>
       <c r="Q51" s="16" t="inlineStr">
         <is>
-          <t>Google removing the account-level "Use all Customer Match lists in Smart Bidding or Optimized Targeting" opt-out; changes to the 540-day membership cap or the 100-active-members eligibility rule; Customer Match becoming usable under manual bidding.</t>
+          <t>Google extending brand exclusions beyond Search, Shopping and YouTube-search inventory; a change to broad-match-based brand-list matching; removal of the "Allow Shopping ads on excluded brand searches" option; a change to the exact-match-keyword priority rule between Search and PMax.</t>
         </is>
       </c>
       <c r="R51" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S51" s="15" t="inlineStr">
@@ -4982,31 +4970,31 @@
     </row>
     <row r="52" ht="15" customHeight="1" s="13">
       <c r="A52" s="15" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B52" s="16" t="inlineStr">
         <is>
-          <t>B2B audience exclusions (demographic, in-market, HHI)</t>
+          <t>Feed-only PMax</t>
         </is>
       </c>
       <c r="C52" s="15" t="inlineStr">
         <is>
-          <t>Audiences</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D52" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E52" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F52" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G52" s="15" t="inlineStr">
@@ -5016,7 +5004,7 @@
       </c>
       <c r="H52" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I52" s="15" t="inlineStr">
@@ -5026,7 +5014,7 @@
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
-          <t>B2B client getting consumer traffic</t>
+          <t>E-com client; want Shopping-like control without creative spend</t>
         </is>
       </c>
       <c r="K52" s="15" t="inlineStr">
@@ -5042,7 +5030,7 @@
       <c r="M52" s="15" t="n"/>
       <c r="N52" s="17" t="inlineStr">
         <is>
-          <t>skills/52-b2b-audience-exclusions/</t>
+          <t>skills/56-feed-only-pmax/</t>
         </is>
       </c>
       <c r="O52" s="15" t="n"/>
@@ -5053,7 +5041,7 @@
       </c>
       <c r="Q52" s="16" t="inlineStr">
         <is>
-          <t>Google adding parental status, life events or custom segments to Search; HHI becoming available in European markets; Smart Bidding honouring non-(-100%) audience bid adjustments; demographics gaining an observation setting.</t>
+          <t>Google removing the opt-out from auto-generated assets; a change to the channel report's "ads using product data" segmentation; deprecation of Standard Shopping as the comparison campaign.</t>
         </is>
       </c>
       <c r="R52" s="15" t="inlineStr">
@@ -5069,26 +5057,26 @@
     </row>
     <row r="53" ht="15" customHeight="1" s="13">
       <c r="A53" s="15" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B53" s="16" t="inlineStr">
         <is>
-          <t>Combined segments for intent stacking</t>
+          <t>PMax search terms insights — what you can see and mine</t>
         </is>
       </c>
       <c r="C53" s="15" t="inlineStr">
         <is>
-          <t>Audiences</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D53" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E53" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F53" s="15" t="inlineStr">
@@ -5098,22 +5086,22 @@
       </c>
       <c r="G53" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H53" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I53" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>Want AND/OR/NOT audience logic for tighter targeting</t>
+          <t>Need query-level visibility in PMax</t>
         </is>
       </c>
       <c r="K53" s="15" t="inlineStr">
@@ -5123,20 +5111,16 @@
       </c>
       <c r="L53" s="15" t="inlineStr">
         <is>
-          <t>Drafting</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="M53" s="15" t="n"/>
       <c r="N53" s="17" t="inlineStr">
         <is>
-          <t>skills/53-combined-segments-intent-stacking/</t>
-        </is>
-      </c>
-      <c r="O53" s="15" t="inlineStr">
-        <is>
-          <t>THIN CANON stub — see SKILL.md question for Elias</t>
-        </is>
-      </c>
+          <t>skills/57-pmax-search-terms-insights/</t>
+        </is>
+      </c>
+      <c r="O53" s="15" t="n"/>
       <c r="P53" s="15" t="inlineStr">
         <is>
           <t>2026-10-13</t>
@@ -5144,42 +5128,42 @@
       </c>
       <c r="Q53" s="16" t="inlineStr">
         <is>
-          <t>Any change to combined-segment availability by campaign type or to the AND/OR/NOT rules; Search gaining custom segments.</t>
+          <t>Google adding cost to term-level PMax reporting; removal of the PMax search terms report or the campaign_search_term_insight API resource; asset-group-level negatives; a change to the privacy threshold that withholds low-volume terms.</t>
         </is>
       </c>
       <c r="R53" s="15" t="inlineStr">
         <is>
-          <t>Thin</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S53" s="15" t="inlineStr">
         <is>
-          <t>NEEDS ELIAS</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="13">
       <c r="A54" s="15" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B54" s="16" t="inlineStr">
         <is>
-          <t>GA4 first-party segments into Google Ads</t>
+          <t>Asset groups by product vs. by audience</t>
         </is>
       </c>
       <c r="C54" s="15" t="inlineStr">
         <is>
-          <t>Audiences</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D54" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E54" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F54" s="15" t="inlineStr">
@@ -5204,12 +5188,12 @@
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>GA4 linked; want behavioural segments as signals</t>
+          <t>Structuring a new PMax campaign</t>
         </is>
       </c>
       <c r="K54" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner debate</t>
         </is>
       </c>
       <c r="L54" s="15" t="inlineStr">
@@ -5220,7 +5204,7 @@
       <c r="M54" s="15" t="n"/>
       <c r="N54" s="17" t="inlineStr">
         <is>
-          <t>skills/54-ga4-segments-into-google-ads/</t>
+          <t>skills/58-pmax-asset-group-structure/</t>
         </is>
       </c>
       <c r="O54" s="15" t="n"/>
@@ -5231,7 +5215,7 @@
       </c>
       <c r="Q54" s="16" t="inlineStr">
         <is>
-          <t>GA4 removing the 30-day backfill or changing the 100-audience cap; GA4 Customer Match leaving beta with different mechanics; Google Ads deprecating tag-based remarketing lists; consent-mode changes to which GA4 users are exportable.</t>
+          <t>Google making audience signals hard targets; asset-group-level bidding targets; changes to listing-group mechanics.</t>
         </is>
       </c>
       <c r="R54" s="15" t="inlineStr">
@@ -5247,11 +5231,11 @@
     </row>
     <row r="55" ht="15" customHeight="1" s="13">
       <c r="A55" s="15" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B55" s="16" t="inlineStr">
         <is>
-          <t>PMax brand exclusions — full method</t>
+          <t>PMax cannibalising brand/Search — diagnosis</t>
         </is>
       </c>
       <c r="C55" s="15" t="inlineStr">
@@ -5261,7 +5245,7 @@
       </c>
       <c r="D55" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E55" s="15" t="inlineStr">
@@ -5271,17 +5255,17 @@
       </c>
       <c r="F55" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G55" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H55" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I55" s="15" t="inlineStr">
@@ -5291,12 +5275,12 @@
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
-          <t>PMax eating brand traffic and inflating ROAS</t>
+          <t>Search performance fell after PMax launch</t>
         </is>
       </c>
       <c r="K55" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Mike Rhodes script + practitioner</t>
         </is>
       </c>
       <c r="L55" s="15" t="inlineStr">
@@ -5307,7 +5291,7 @@
       <c r="M55" s="15" t="n"/>
       <c r="N55" s="17" t="inlineStr">
         <is>
-          <t>skills/55-pmax-brand-exclusions/</t>
+          <t>skills/59-pmax-cannibalisation-diagnosis/</t>
         </is>
       </c>
       <c r="O55" s="15" t="n"/>
@@ -5318,7 +5302,7 @@
       </c>
       <c r="Q55" s="16" t="inlineStr">
         <is>
-          <t>Google extending brand exclusions beyond Search, Shopping and YouTube-search inventory; a change to broad-match-based brand-list matching; removal of the "Allow Shopping ads on excluded brand searches" option; a change to the exact-match-keyword priority rule between Search and PMax.</t>
+          <t>A change to the rule that an identical Search keyword takes precedence over PMax; cost appearing in the PMax search terms report; Google shipping Search-vs-PMax or channel-level controls; removal of the PMax search terms report.</t>
         </is>
       </c>
       <c r="R55" s="15" t="inlineStr">
@@ -5334,11 +5318,11 @@
     </row>
     <row r="56" ht="15" customHeight="1" s="13">
       <c r="A56" s="15" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B56" s="16" t="inlineStr">
         <is>
-          <t>Feed-only PMax</t>
+          <t>PMax placement exclusions &amp; display/video spend</t>
         </is>
       </c>
       <c r="C56" s="15" t="inlineStr">
@@ -5348,7 +5332,7 @@
       </c>
       <c r="D56" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E56" s="15" t="inlineStr">
@@ -5358,7 +5342,7 @@
       </c>
       <c r="F56" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G56" s="15" t="inlineStr">
@@ -5368,7 +5352,7 @@
       </c>
       <c r="H56" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I56" s="15" t="inlineStr">
@@ -5378,7 +5362,7 @@
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>E-com client; want Shopping-like control without creative spend</t>
+          <t>Too much PMax spend going to low-quality placements</t>
         </is>
       </c>
       <c r="K56" s="15" t="inlineStr">
@@ -5394,7 +5378,7 @@
       <c r="M56" s="15" t="n"/>
       <c r="N56" s="17" t="inlineStr">
         <is>
-          <t>skills/56-feed-only-pmax/</t>
+          <t>skills/60-pmax-placement-exclusions/</t>
         </is>
       </c>
       <c r="O56" s="15" t="n"/>
@@ -5405,12 +5389,12 @@
       </c>
       <c r="Q56" s="16" t="inlineStr">
         <is>
-          <t>Google removing the opt-out from auto-generated assets; a change to the channel report's "ads using product data" segmentation; deprecation of Standard Shopping as the comparison campaign.</t>
+          <t>Campaign-level placement exclusions or channel-level budget/bid controls in PMax; cost appearing in the PMax placement report; a change to the account-level exclusion scope.</t>
         </is>
       </c>
       <c r="R56" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S56" s="15" t="inlineStr">
@@ -5421,11 +5405,11 @@
     </row>
     <row r="57" ht="15" customHeight="1" s="13">
       <c r="A57" s="15" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="B57" s="16" t="inlineStr">
         <is>
-          <t>PMax search terms insights — what you can see and mine</t>
+          <t>URL expansion off + final URL control</t>
         </is>
       </c>
       <c r="C57" s="15" t="inlineStr">
@@ -5435,7 +5419,7 @@
       </c>
       <c r="D57" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E57" s="15" t="inlineStr">
@@ -5445,7 +5429,7 @@
       </c>
       <c r="F57" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G57" s="15" t="inlineStr">
@@ -5455,17 +5439,17 @@
       </c>
       <c r="H57" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I57" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>Need query-level visibility in PMax</t>
+          <t>PMax sending traffic to unintended pages</t>
         </is>
       </c>
       <c r="K57" s="15" t="inlineStr">
@@ -5481,7 +5465,7 @@
       <c r="M57" s="15" t="n"/>
       <c r="N57" s="17" t="inlineStr">
         <is>
-          <t>skills/57-pmax-search-terms-insights/</t>
+          <t>skills/61-pmax-url-expansion/</t>
         </is>
       </c>
       <c r="O57" s="15" t="n"/>
@@ -5492,12 +5476,12 @@
       </c>
       <c r="Q57" s="16" t="inlineStr">
         <is>
-          <t>Google adding cost to term-level PMax reporting; removal of the PMax search terms report or the campaign_search_term_insight API resource; asset-group-level negatives; a change to the privacy threshold that withholds low-volume terms.</t>
+          <t>A change to the default-on setting; the ability to exclude the campaign's own final URL or homepage; expansion folding into AI Max page controls; removal of page feeds from PMax.</t>
         </is>
       </c>
       <c r="R57" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S57" s="15" t="inlineStr">
@@ -5508,11 +5492,11 @@
     </row>
     <row r="58" ht="15" customHeight="1" s="13">
       <c r="A58" s="15" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B58" s="16" t="inlineStr">
         <is>
-          <t>Asset groups by product vs. by audience</t>
+          <t>PMax campaign-level negatives</t>
         </is>
       </c>
       <c r="C58" s="15" t="inlineStr">
@@ -5522,7 +5506,7 @@
       </c>
       <c r="D58" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E58" s="15" t="inlineStr">
@@ -5532,7 +5516,7 @@
       </c>
       <c r="F58" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G58" s="15" t="inlineStr">
@@ -5542,22 +5526,22 @@
       </c>
       <c r="H58" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I58" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
-          <t>Structuring a new PMax campaign</t>
+          <t>Irrelevant queries visible in PMax insights</t>
         </is>
       </c>
       <c r="K58" s="15" t="inlineStr">
         <is>
-          <t>Practitioner debate</t>
+          <t>Google docs (recent feature)</t>
         </is>
       </c>
       <c r="L58" s="15" t="inlineStr">
@@ -5568,7 +5552,7 @@
       <c r="M58" s="15" t="n"/>
       <c r="N58" s="17" t="inlineStr">
         <is>
-          <t>skills/58-pmax-asset-group-structure/</t>
+          <t>skills/62-pmax-campaign-negatives/</t>
         </is>
       </c>
       <c r="O58" s="15" t="n"/>
@@ -5579,12 +5563,12 @@
       </c>
       <c r="Q58" s="16" t="inlineStr">
         <is>
-          <t>Google making audience signals hard targets; asset-group-level bidding targets; changes to listing-group mechanics.</t>
+          <t>PMax negatives extending to Display, Video or Discover inventory; asset-group-level negatives; a change to the 10,000-per-campaign or 1,000-per-account limits; removal of the PMax search terms report.</t>
         </is>
       </c>
       <c r="R58" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S58" s="15" t="inlineStr">
@@ -5595,11 +5579,11 @@
     </row>
     <row r="59" ht="15" customHeight="1" s="13">
       <c r="A59" s="15" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B59" s="16" t="inlineStr">
         <is>
-          <t>PMax cannibalising brand/Search — diagnosis</t>
+          <t>New customer acquisition goal — definition problem</t>
         </is>
       </c>
       <c r="C59" s="15" t="inlineStr">
@@ -5609,7 +5593,7 @@
       </c>
       <c r="D59" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E59" s="15" t="inlineStr">
@@ -5619,7 +5603,7 @@
       </c>
       <c r="F59" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G59" s="15" t="inlineStr">
@@ -5629,22 +5613,22 @@
       </c>
       <c r="H59" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I59" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J59" s="16" t="inlineStr">
         <is>
-          <t>Search performance fell after PMax launch</t>
+          <t>Client wants to bid higher for new customers</t>
         </is>
       </c>
       <c r="K59" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes script + practitioner</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L59" s="15" t="inlineStr">
@@ -5655,7 +5639,7 @@
       <c r="M59" s="15" t="n"/>
       <c r="N59" s="17" t="inlineStr">
         <is>
-          <t>skills/59-pmax-cannibalisation-diagnosis/</t>
+          <t>skills/63-pmax-new-customer-acquisition/</t>
         </is>
       </c>
       <c r="O59" s="15" t="n"/>
@@ -5666,12 +5650,12 @@
       </c>
       <c r="Q59" s="16" t="inlineStr">
         <is>
-          <t>A change to the rule that an identical Search keyword takes precedence over PMax; cost appearing in the PMax search terms report; Google shipping Search-vs-PMax or channel-level controls; removal of the PMax search terms report.</t>
+          <t>A change to the 540-day auto-detection window; removal of the Original conv. value column; the premium becoming bidding-only (non-reporting); in-platform incrementality testing for lifecycle goals; removal of New Customer Only mode.</t>
         </is>
       </c>
       <c r="R59" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S59" s="15" t="inlineStr">
@@ -5682,16 +5666,16 @@
     </row>
     <row r="60" ht="15" customHeight="1" s="13">
       <c r="A60" s="15" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B60" s="16" t="inlineStr">
         <is>
-          <t>PMax placement exclusions &amp; display/video spend</t>
+          <t>Custom labels by margin / stock / seasonality</t>
         </is>
       </c>
       <c r="C60" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D60" s="15" t="inlineStr">
@@ -5701,7 +5685,7 @@
       </c>
       <c r="E60" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F60" s="15" t="inlineStr">
@@ -5711,22 +5695,22 @@
       </c>
       <c r="G60" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H60" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I60" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J60" s="16" t="inlineStr">
         <is>
-          <t>Too much PMax spend going to low-quality placements</t>
+          <t>Want bidding tiers by profitability or availability</t>
         </is>
       </c>
       <c r="K60" s="15" t="inlineStr">
@@ -5742,7 +5726,7 @@
       <c r="M60" s="15" t="n"/>
       <c r="N60" s="17" t="inlineStr">
         <is>
-          <t>skills/60-pmax-placement-exclusions/</t>
+          <t>skills/64-custom-labels-margin-stock-season/</t>
         </is>
       </c>
       <c r="O60" s="15" t="n"/>
@@ -5753,7 +5737,7 @@
       </c>
       <c r="Q60" s="16" t="inlineStr">
         <is>
-          <t>Campaign-level placement exclusions or channel-level budget/bid controls in PMax; cost appearing in the PMax placement report; a change to the account-level exclusion scope.</t>
+          <t>Google changing the 5-label or 1,000-value caps, removing custom labels from PMax/AI Max listing groups, or dropping supplemental data sources from Merchant Center Next.</t>
         </is>
       </c>
       <c r="R60" s="15" t="inlineStr">
@@ -5769,31 +5753,31 @@
     </row>
     <row r="61" ht="15" customHeight="1" s="13">
       <c r="A61" s="15" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B61" s="16" t="inlineStr">
         <is>
-          <t>URL expansion off + final URL control</t>
+          <t>Feed rules &amp; supplemental feeds</t>
         </is>
       </c>
       <c r="C61" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D61" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E61" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F61" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G61" s="15" t="inlineStr">
@@ -5803,7 +5787,7 @@
       </c>
       <c r="H61" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I61" s="15" t="inlineStr">
@@ -5813,7 +5797,7 @@
       </c>
       <c r="J61" s="16" t="inlineStr">
         <is>
-          <t>PMax sending traffic to unintended pages</t>
+          <t>Need to change titles/attributes without touching the source feed</t>
         </is>
       </c>
       <c r="K61" s="15" t="inlineStr">
@@ -5829,7 +5813,7 @@
       <c r="M61" s="15" t="n"/>
       <c r="N61" s="17" t="inlineStr">
         <is>
-          <t>skills/61-pmax-url-expansion/</t>
+          <t>skills/65-feed-rules-supplemental-feeds/</t>
         </is>
       </c>
       <c r="O61" s="15" t="n"/>
@@ -5840,7 +5824,7 @@
       </c>
       <c r="Q61" s="16" t="inlineStr">
         <is>
-          <t>A change to the default-on setting; the ability to exclude the campaign's own final URL or homepage; expansion folding into AI Max page controls; removal of page feeds from PMax.</t>
+          <t>Google removing supplemental sources or attribute rules from Merchant Center Next, dropping the Advanced data source management add-on, making id matching case-insensitive, or lifting the once-a-day scheduled-fetch limit.</t>
         </is>
       </c>
       <c r="R61" s="15" t="inlineStr">
@@ -5856,26 +5840,26 @@
     </row>
     <row r="62" ht="15" customHeight="1" s="13">
       <c r="A62" s="15" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B62" s="16" t="inlineStr">
         <is>
-          <t>PMax campaign-level negatives</t>
+          <t>Title structure research — what moves CTR</t>
         </is>
       </c>
       <c r="C62" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D62" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E62" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F62" s="15" t="inlineStr">
@@ -5890,22 +5874,22 @@
       </c>
       <c r="H62" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I62" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J62" s="16" t="inlineStr">
         <is>
-          <t>Irrelevant queries visible in PMax insights</t>
+          <t>Shopping CTR low; titles are generic</t>
         </is>
       </c>
       <c r="K62" s="15" t="inlineStr">
         <is>
-          <t>Google docs (recent feature)</t>
+          <t>Industry studies</t>
         </is>
       </c>
       <c r="L62" s="15" t="inlineStr">
@@ -5916,7 +5900,7 @@
       <c r="M62" s="15" t="n"/>
       <c r="N62" s="17" t="inlineStr">
         <is>
-          <t>skills/62-pmax-campaign-negatives/</t>
+          <t>skills/66-title-structure-research/</t>
         </is>
       </c>
       <c r="O62" s="15" t="n"/>
@@ -5927,12 +5911,12 @@
       </c>
       <c r="Q62" s="16" t="inlineStr">
         <is>
-          <t>PMax negatives extending to Display, Video or Discover inventory; asset-group-level negatives; a change to the 10,000-per-campaign or 1,000-per-account limits; removal of the PMax search terms report.</t>
+          <t>Google changing the ~70-character displayed cut-off or the 150-character title limit, AI Max / dynamic titles overriding merchant titles by default, or Merchant Center removing attribute rules and supplemental sources (the test mechanism).</t>
         </is>
       </c>
       <c r="R62" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S62" s="15" t="inlineStr">
@@ -5943,51 +5927,51 @@
     </row>
     <row r="63" ht="15" customHeight="1" s="13">
       <c r="A63" s="15" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B63" s="16" t="inlineStr">
         <is>
-          <t>New customer acquisition goal — definition problem</t>
+          <t>Merchant Center diagnostics &amp; disapproval patterns</t>
         </is>
       </c>
       <c r="C63" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D63" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E63" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F63" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G63" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H63" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="I63" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
-          <t>Client wants to bid higher for new customers</t>
+          <t>Products disapproved or limited</t>
         </is>
       </c>
       <c r="K63" s="15" t="inlineStr">
@@ -6003,7 +5987,7 @@
       <c r="M63" s="15" t="n"/>
       <c r="N63" s="17" t="inlineStr">
         <is>
-          <t>skills/63-pmax-new-customer-acquisition/</t>
+          <t>skills/67-merchant-center-diagnostics/</t>
         </is>
       </c>
       <c r="O63" s="15" t="n"/>
@@ -6014,7 +5998,7 @@
       </c>
       <c r="Q63" s="16" t="inlineStr">
         <is>
-          <t>A change to the 540-day auto-detection window; removal of the Original conv. value column; the premium becoming bidding-only (non-reporting); in-platform incrementality testing for lifecycle goals; removal of New Customer Only mode.</t>
+          <t>Google changing the misrepresentation warning windows (7/28 days) or 7-business-day review, removing the Content API product-status endpoint, or moving diagnostics wholly into Google Ads with a different issue taxonomy.</t>
         </is>
       </c>
       <c r="R63" s="15" t="inlineStr">
@@ -6030,11 +6014,11 @@
     </row>
     <row r="64" ht="15" customHeight="1" s="13">
       <c r="A64" s="15" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B64" s="16" t="inlineStr">
         <is>
-          <t>Custom labels by margin / stock / seasonality</t>
+          <t>Shopping query sculpting via priority + negatives</t>
         </is>
       </c>
       <c r="C64" s="15" t="inlineStr">
@@ -6064,17 +6048,17 @@
       </c>
       <c r="H64" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I64" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
-          <t>Want bidding tiers by profitability or availability</t>
+          <t>Want generic vs. brand vs. product queries in separate campaigns</t>
         </is>
       </c>
       <c r="K64" s="15" t="inlineStr">
@@ -6090,7 +6074,7 @@
       <c r="M64" s="15" t="n"/>
       <c r="N64" s="17" t="inlineStr">
         <is>
-          <t>skills/64-custom-labels-margin-stock-season/</t>
+          <t>skills/68-shopping-query-sculpting/</t>
         </is>
       </c>
       <c r="O64" s="15" t="n"/>
@@ -6101,7 +6085,7 @@
       </c>
       <c r="Q64" s="16" t="inlineStr">
         <is>
-          <t>Google changing the 5-label or 1,000-value caps, removing custom labels from PMax/AI Max listing groups, or dropping supplemental data sources from Merchant Center Next.</t>
+          <t>Google removing campaign priority from Standard Shopping, forcing PMax precedence without brand exclusions, removing shared budgets, or AI Max for Shopping replacing keyword-free matching with its own query rules.</t>
         </is>
       </c>
       <c r="R64" s="15" t="inlineStr">
@@ -6117,31 +6101,31 @@
     </row>
     <row r="65" ht="15" customHeight="1" s="13">
       <c r="A65" s="15" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B65" s="16" t="inlineStr">
         <is>
-          <t>Feed rules &amp; supplemental feeds</t>
+          <t>PMax insights script</t>
         </is>
       </c>
       <c r="C65" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D65" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E65" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F65" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G65" s="15" t="inlineStr">
@@ -6151,22 +6135,22 @@
       </c>
       <c r="H65" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I65" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
-          <t>Need to change titles/attributes without touching the source feed</t>
+          <t>Running PMax; need channel/placement/query breakdown</t>
         </is>
       </c>
       <c r="K65" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Mike Rhodes</t>
         </is>
       </c>
       <c r="L65" s="15" t="inlineStr">
@@ -6177,7 +6161,7 @@
       <c r="M65" s="15" t="n"/>
       <c r="N65" s="17" t="inlineStr">
         <is>
-          <t>skills/65-feed-rules-supplemental-feeds/</t>
+          <t>skills/69-pmax-insights-script/</t>
         </is>
       </c>
       <c r="O65" s="15" t="n"/>
@@ -6188,12 +6172,12 @@
       </c>
       <c r="Q65" s="16" t="inlineStr">
         <is>
-          <t>Google removing supplemental sources or attribute rules from Merchant Center Next, dropping the Advanced data source management add-on, making id matching case-insensitive, or lifting the once-a-day scheduled-fetch limit.</t>
+          <t>Google exposing channel-level spend, cost-bearing search terms and placement cost natively in the PMax UI/API; deprecation of campaign_search_term_insight or performance_max_placement_view; Google Ads Scripts API-version sunsets breaking the queries.</t>
         </is>
       </c>
       <c r="R65" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S65" s="15" t="inlineStr">
@@ -6204,31 +6188,31 @@
     </row>
     <row r="66" ht="15" customHeight="1" s="13">
       <c r="A66" s="15" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B66" s="16" t="inlineStr">
         <is>
-          <t>Title structure research — what moves CTR</t>
+          <t>N-gram script</t>
         </is>
       </c>
       <c r="C66" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D66" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E66" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F66" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G66" s="15" t="inlineStr">
@@ -6243,17 +6227,17 @@
       </c>
       <c r="I66" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J66" s="16" t="inlineStr">
         <is>
-          <t>Shopping CTR low; titles are generic</t>
+          <t>Want automated n-gram output for search terms</t>
         </is>
       </c>
       <c r="K66" s="15" t="inlineStr">
         <is>
-          <t>Industry studies</t>
+          <t>Nils Rooijmans / Brainlabs</t>
         </is>
       </c>
       <c r="L66" s="15" t="inlineStr">
@@ -6264,7 +6248,7 @@
       <c r="M66" s="15" t="n"/>
       <c r="N66" s="17" t="inlineStr">
         <is>
-          <t>skills/66-title-structure-research/</t>
+          <t>skills/70-n-gram-script/</t>
         </is>
       </c>
       <c r="O66" s="15" t="n"/>
@@ -6275,12 +6259,12 @@
       </c>
       <c r="Q66" s="16" t="inlineStr">
         <is>
-          <t>Google changing the ~70-character displayed cut-off or the 150-character title limit, AI Max / dynamic titles overriding merchant titles by default, or Merchant Center removing attribute rules and supplemental sources (the test mechanism).</t>
+          <t>Further privacy-thresholding of the search terms report; removal of search_term_view or campaign_search_term_insight from the Scripts runtime; API-version sunsets breaking the GAQL.</t>
         </is>
       </c>
       <c r="R66" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S66" s="15" t="inlineStr">
@@ -6291,31 +6275,31 @@
     </row>
     <row r="67" ht="15" customHeight="1" s="13">
       <c r="A67" s="15" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="B67" s="16" t="inlineStr">
         <is>
-          <t>Merchant Center diagnostics &amp; disapproval patterns</t>
+          <t>Budget pacing script</t>
         </is>
       </c>
       <c r="C67" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D67" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E67" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F67" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G67" s="15" t="inlineStr">
@@ -6325,7 +6309,7 @@
       </c>
       <c r="H67" s="15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I67" s="15" t="inlineStr">
@@ -6335,12 +6319,12 @@
       </c>
       <c r="J67" s="16" t="inlineStr">
         <is>
-          <t>Products disapproved or limited</t>
+          <t>Monthly budgets; need over/under-pacing alerts</t>
         </is>
       </c>
       <c r="K67" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L67" s="15" t="inlineStr">
@@ -6351,7 +6335,7 @@
       <c r="M67" s="15" t="n"/>
       <c r="N67" s="17" t="inlineStr">
         <is>
-          <t>skills/67-merchant-center-diagnostics/</t>
+          <t>skills/71-budget-pacing-script/</t>
         </is>
       </c>
       <c r="O67" s="15" t="n"/>
@@ -6362,7 +6346,7 @@
       </c>
       <c r="Q67" s="16" t="inlineStr">
         <is>
-          <t>Google changing the misrepresentation warning windows (7/28 days) or 7-business-day review, removing the Content API product-status endpoint, or moving diagnostics wholly into Google Ads with a different issue taxonomy.</t>
+          <t>Google changing the 2x-daily / 30.4x-monthly overdelivery rules or adding true monthly budgets to all campaign types; Scripts exposing cost for PMax/Demand Gen in the campaign iterator; GAQL version sunsets.</t>
         </is>
       </c>
       <c r="R67" s="15" t="inlineStr">
@@ -6378,41 +6362,41 @@
     </row>
     <row r="68" ht="15" customHeight="1" s="13">
       <c r="A68" s="15" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B68" s="16" t="inlineStr">
         <is>
-          <t>Shopping query sculpting via priority + negatives</t>
+          <t>Anomaly detector script</t>
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D68" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F68" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G68" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H68" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I68" s="15" t="inlineStr">
@@ -6422,12 +6406,12 @@
       </c>
       <c r="J68" s="16" t="inlineStr">
         <is>
-          <t>Want generic vs. brand vs. product queries in separate campaigns</t>
+          <t>Want alerts on sudden spend/CPA/conv changes</t>
         </is>
       </c>
       <c r="K68" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L68" s="15" t="inlineStr">
@@ -6438,7 +6422,7 @@
       <c r="M68" s="15" t="n"/>
       <c r="N68" s="17" t="inlineStr">
         <is>
-          <t>skills/68-shopping-query-sculpting/</t>
+          <t>skills/72-anomaly-detector-script/</t>
         </is>
       </c>
       <c r="O68" s="15" t="n"/>
@@ -6449,12 +6433,12 @@
       </c>
       <c r="Q68" s="16" t="inlineStr">
         <is>
-          <t>Google removing campaign priority from Standard Shopping, forcing PMax precedence without brand exclusions, removing shared budgets, or AI Max for Shopping replacing keyword-free matching with its own query rules.</t>
+          <t>Deprecation of search_term_view or change_event in Scripts; Scripts frequency or runtime limits changing; Google removing or re-pinning the Account Anomaly Detector solution.</t>
         </is>
       </c>
       <c r="R68" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S68" s="15" t="inlineStr">
@@ -6465,11 +6449,11 @@
     </row>
     <row r="69" ht="15" customHeight="1" s="13">
       <c r="A69" s="15" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B69" s="16" t="inlineStr">
         <is>
-          <t>PMax insights script</t>
+          <t>404 / broken URL checker</t>
         </is>
       </c>
       <c r="C69" s="15" t="inlineStr">
@@ -6484,7 +6468,7 @@
       </c>
       <c r="E69" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F69" s="15" t="inlineStr">
@@ -6504,17 +6488,17 @@
       </c>
       <c r="I69" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J69" s="16" t="inlineStr">
         <is>
-          <t>Running PMax; need channel/placement/query breakdown</t>
+          <t>Large site or frequent page changes</t>
         </is>
       </c>
       <c r="K69" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L69" s="15" t="inlineStr">
@@ -6525,7 +6509,7 @@
       <c r="M69" s="15" t="n"/>
       <c r="N69" s="17" t="inlineStr">
         <is>
-          <t>skills/69-pmax-insights-script/</t>
+          <t>skills/73-broken-url-checker-script/</t>
         </is>
       </c>
       <c r="O69" s="15" t="n"/>
@@ -6536,12 +6520,12 @@
       </c>
       <c r="Q69" s="16" t="inlineStr">
         <is>
-          <t>Google exposing channel-level spend, cost-bearing search terms and placement cost natively in the PMax UI/API; deprecation of campaign_search_term_insight or performance_max_placement_view; Google Ads Scripts API-version sunsets breaking the queries.</t>
+          <t>Removal or quota reduction of UrlFetchApp in Scripts; Google making "Destination not working" disapprovals immediate and complete; removal of PMax final URL expansion.</t>
         </is>
       </c>
       <c r="R69" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S69" s="15" t="inlineStr">
@@ -6552,11 +6536,11 @@
     </row>
     <row r="70" ht="15" customHeight="1" s="13">
       <c r="A70" s="15" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B70" s="16" t="inlineStr">
         <is>
-          <t>N-gram script</t>
+          <t>Negative keyword conflict script</t>
         </is>
       </c>
       <c r="C70" s="15" t="inlineStr">
@@ -6591,17 +6575,17 @@
       </c>
       <c r="I70" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J70" s="16" t="inlineStr">
         <is>
-          <t>Want automated n-gram output for search terms</t>
+          <t>Many negative lists; want automated conflict checks</t>
         </is>
       </c>
       <c r="K70" s="15" t="inlineStr">
         <is>
-          <t>Nils Rooijmans / Brainlabs</t>
+          <t>Scripts community</t>
         </is>
       </c>
       <c r="L70" s="15" t="inlineStr">
@@ -6612,7 +6596,7 @@
       <c r="M70" s="15" t="n"/>
       <c r="N70" s="17" t="inlineStr">
         <is>
-          <t>skills/70-n-gram-script/</t>
+          <t>skills/74-negative-keyword-conflict-script/</t>
         </is>
       </c>
       <c r="O70" s="15" t="n"/>
@@ -6623,12 +6607,12 @@
       </c>
       <c r="Q70" s="16" t="inlineStr">
         <is>
-          <t>Further privacy-thresholding of the search terms report; removal of search_term_view or campaign_search_term_insight from the Scripts runtime; API-version sunsets breaking the GAQL.</t>
+          <t>Google applying close variants to negative keywords; removal of shared negative lists or keyword_view; GAQL paging changes that push the script's 250k/50k limits.</t>
         </is>
       </c>
       <c r="R70" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S70" s="15" t="inlineStr">
@@ -6639,11 +6623,11 @@
     </row>
     <row r="71" ht="15" customHeight="1" s="13">
       <c r="A71" s="15" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B71" s="16" t="inlineStr">
         <is>
-          <t>Budget pacing script</t>
+          <t>Ad disapproval alert script</t>
         </is>
       </c>
       <c r="C71" s="15" t="inlineStr">
@@ -6678,12 +6662,12 @@
       </c>
       <c r="I71" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J71" s="16" t="inlineStr">
         <is>
-          <t>Monthly budgets; need over/under-pacing alerts</t>
+          <t>Compliance-sensitive vertical; disapprovals go unnoticed</t>
         </is>
       </c>
       <c r="K71" s="15" t="inlineStr">
@@ -6699,7 +6683,7 @@
       <c r="M71" s="15" t="n"/>
       <c r="N71" s="17" t="inlineStr">
         <is>
-          <t>skills/71-budget-pacing-script/</t>
+          <t>skills/75-ad-disapproval-alert-script/</t>
         </is>
       </c>
       <c r="O71" s="15" t="n"/>
@@ -6710,7 +6694,7 @@
       </c>
       <c r="Q71" s="16" t="inlineStr">
         <is>
-          <t>Google changing the 2x-daily / 30.4x-monthly overdelivery rules or adding true monthly budgets to all campaign types; Scripts exposing cost for PMax/Demand Gen in the campaign iterator; GAQL version sunsets.</t>
+          <t>Changes to ad_group_ad.policy_summary fields or policy topic naming; Shopping Content API deprecation in favour of the Merchant API; Google adding reliable notifications for past-violation and limited statuses.</t>
         </is>
       </c>
       <c r="R71" s="15" t="inlineStr">
@@ -6726,11 +6710,11 @@
     </row>
     <row r="72" ht="15" customHeight="1" s="13">
       <c r="A72" s="15" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B72" s="16" t="inlineStr">
         <is>
-          <t>Anomaly detector script</t>
+          <t>Search term wasted-spend script</t>
         </is>
       </c>
       <c r="C72" s="15" t="inlineStr">
@@ -6745,7 +6729,7 @@
       </c>
       <c r="E72" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F72" s="15" t="inlineStr">
@@ -6770,7 +6754,7 @@
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>Want alerts on sudden spend/CPA/conv changes</t>
+          <t>Want a weekly list of zero-conversion spend by query</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
@@ -6786,7 +6770,7 @@
       <c r="M72" s="15" t="n"/>
       <c r="N72" s="17" t="inlineStr">
         <is>
-          <t>skills/72-anomaly-detector-script/</t>
+          <t>skills/76-search-term-wasted-spend-script/</t>
         </is>
       </c>
       <c r="O72" s="15" t="n"/>
@@ -6797,12 +6781,12 @@
       </c>
       <c r="Q72" s="16" t="inlineStr">
         <is>
-          <t>Deprecation of search_term_view or change_event in Scripts; Scripts frequency or runtime limits changing; Google removing or re-pinning the Account Anomaly Detector solution.</t>
+          <t>Further privacy-thresholding of search_term_view; Google applying close variants to negatives; removal of campaign-level PMax negatives; API-version sunsets.</t>
         </is>
       </c>
       <c r="R72" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S72" s="15" t="inlineStr">
@@ -6813,11 +6797,11 @@
     </row>
     <row r="73" ht="15" customHeight="1" s="13">
       <c r="A73" s="15" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B73" s="16" t="inlineStr">
         <is>
-          <t>404 / broken URL checker</t>
+          <t>Automated rules vs. scripts — when each</t>
         </is>
       </c>
       <c r="C73" s="15" t="inlineStr">
@@ -6827,7 +6811,7 @@
       </c>
       <c r="D73" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E73" s="15" t="inlineStr">
@@ -6852,17 +6836,17 @@
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>Large site or frequent page changes</t>
+          <t>Deciding how to automate a recurring action</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -6873,7 +6857,7 @@
       <c r="M73" s="15" t="n"/>
       <c r="N73" s="17" t="inlineStr">
         <is>
-          <t>skills/73-broken-url-checker-script/</t>
+          <t>skills/77-automated-rules-vs-scripts/</t>
         </is>
       </c>
       <c r="O73" s="15" t="n"/>
@@ -6884,12 +6868,12 @@
       </c>
       <c r="Q73" s="16" t="inlineStr">
         <is>
-          <t>Removal or quota reduction of UrlFetchApp in Scripts; Google making "Destination not working" disapprovals immediate and complete; removal of PMax final URL expansion.</t>
+          <t>Google removing Automated Rules or folding them into agentic features; Scripts limits changing (30 min, hourly, 250/account); the Ads API gaining native agent tooling that collapses the scripts-as-data layer.</t>
         </is>
       </c>
       <c r="R73" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S73" s="15" t="inlineStr">
@@ -6900,11 +6884,11 @@
     </row>
     <row r="74" ht="15" customHeight="1" s="13">
       <c r="A74" s="15" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B74" s="16" t="inlineStr">
         <is>
-          <t>Negative keyword conflict script</t>
+          <t>Recommendations tab — auto-apply opt-out &amp; dismiss list</t>
         </is>
       </c>
       <c r="C74" s="15" t="inlineStr">
@@ -6914,17 +6898,17 @@
       </c>
       <c r="D74" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E74" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F74" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G74" s="15" t="inlineStr">
@@ -6939,17 +6923,17 @@
       </c>
       <c r="I74" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>Many negative lists; want automated conflict checks</t>
+          <t>New or inherited account; prevent Google auto-applying changes</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
@@ -6960,7 +6944,7 @@
       <c r="M74" s="15" t="n"/>
       <c r="N74" s="17" t="inlineStr">
         <is>
-          <t>skills/74-negative-keyword-conflict-script/</t>
+          <t>skills/78-recommendations-auto-apply-opt-out/</t>
         </is>
       </c>
       <c r="O74" s="15" t="n"/>
@@ -6971,12 +6955,12 @@
       </c>
       <c r="Q74" s="16" t="inlineStr">
         <is>
-          <t>Google applying close variants to negative keywords; removal of shared negative lists or keyword_view; GAQL paging changes that push the script's 250k/50k limits.</t>
+          <t>Google removing auto-apply as a per-account setting; Google extending system bulk changes beyond low-activity keywords and ad groups; changes to change_event retention or the 10k-row cap that break the monitoring script.</t>
         </is>
       </c>
       <c r="R74" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S74" s="15" t="inlineStr">
@@ -6987,56 +6971,56 @@
     </row>
     <row r="75" ht="15" customHeight="1" s="13">
       <c r="A75" s="15" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B75" s="16" t="inlineStr">
         <is>
-          <t>Ad disapproval alert script</t>
+          <t>Custom experiments — split, duration, valid win</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E75" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F75" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G75" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H75" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I75" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>Compliance-sensitive vertical; disapprovals go unnoticed</t>
+          <t>Want to test a bid strategy, structure or landing page properly</t>
         </is>
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
@@ -7047,7 +7031,7 @@
       <c r="M75" s="15" t="n"/>
       <c r="N75" s="17" t="inlineStr">
         <is>
-          <t>skills/75-ad-disapproval-alert-script/</t>
+          <t>skills/79-custom-experiments/</t>
         </is>
       </c>
       <c r="O75" s="15" t="n"/>
@@ -7058,7 +7042,7 @@
       </c>
       <c r="Q75" s="16" t="inlineStr">
         <is>
-          <t>Changes to ad_group_ad.policy_summary fields or policy topic naming; Shopping Content API deprecation in favour of the Merchant API; Google adding reliable notifications for past-violation and limited statuses.</t>
+          <t>Changes to the 7-day ramp-up exclusion, the 80% default confidence display, budget-vs-traffic split rules per campaign type, or replacement of custom experiments by Google-recommended / multi-campaign experiments only.</t>
         </is>
       </c>
       <c r="R75" s="15" t="inlineStr">
@@ -7074,41 +7058,41 @@
     </row>
     <row r="76" ht="15" customHeight="1" s="13">
       <c r="A76" s="15" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B76" s="16" t="inlineStr">
         <is>
-          <t>Search term wasted-spend script</t>
+          <t>Geo experiments / conversion lift</t>
         </is>
       </c>
       <c r="C76" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
         <is>
-          <t>Script</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E76" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F76" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G76" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H76" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
@@ -7118,12 +7102,12 @@
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>Want a weekly list of zero-conversion spend by query</t>
+          <t>Need incrementality evidence for a channel or campaign</t>
         </is>
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>Scripts community</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
@@ -7134,7 +7118,7 @@
       <c r="M76" s="15" t="n"/>
       <c r="N76" s="17" t="inlineStr">
         <is>
-          <t>skills/76-search-term-wasted-spend-script/</t>
+          <t>skills/80-geo-experiments-conversion-lift/</t>
         </is>
       </c>
       <c r="O76" s="15" t="n"/>
@@ -7145,12 +7129,12 @@
       </c>
       <c r="Q76" s="16" t="inlineStr">
         <is>
-          <t>Further privacy-thresholding of search_term_view; Google applying close variants to negatives; removal of campaign-level PMax negatives; API-version sunsets.</t>
+          <t>Changes to Conversion Lift minimums ($5k budget, 1,000 conversions, 14 days), the certainty selector, geo-based study availability, how projected cooldown conversions are included, or Google exposing/removing the priors behind its Bayesian lift estimates.</t>
         </is>
       </c>
       <c r="R76" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S76" s="15" t="inlineStr">
@@ -7161,51 +7145,51 @@
     </row>
     <row r="77" ht="15" customHeight="1" s="13">
       <c r="A77" s="15" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B77" s="16" t="inlineStr">
         <is>
-          <t>Automated rules vs. scripts — when each</t>
+          <t>Brand incrementality test</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E77" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F77" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G77" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H77" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>Deciding how to automate a recurring action</t>
+          <t>Question whether brand spend is incremental</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
@@ -7221,7 +7205,7 @@
       <c r="M77" s="15" t="n"/>
       <c r="N77" s="17" t="inlineStr">
         <is>
-          <t>skills/77-automated-rules-vs-scripts/</t>
+          <t>skills/81-brand-incrementality-test/</t>
         </is>
       </c>
       <c r="O77" s="15" t="n"/>
@@ -7232,12 +7216,12 @@
       </c>
       <c r="Q77" s="16" t="inlineStr">
         <is>
-          <t>Google removing Automated Rules or folding them into agentic features; Scripts limits changing (30 min, hourly, 250/account); the Ads API gaining native agent tooling that collapses the scripts-as-data layer.</t>
+          <t>Removal or change of PMax brand exclusions / Search brand lists; changes to Conversion Lift minimums; Google altering serving preference between exact-match keywords and PMax for brand queries.</t>
         </is>
       </c>
       <c r="R77" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S77" s="15" t="inlineStr">
@@ -7248,21 +7232,21 @@
     </row>
     <row r="78" ht="15" customHeight="1" s="13">
       <c r="A78" s="15" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B78" s="16" t="inlineStr">
         <is>
-          <t>Recommendations tab — auto-apply opt-out &amp; dismiss list</t>
+          <t>Statistical significance for ad tests</t>
         </is>
       </c>
       <c r="C78" s="15" t="inlineStr">
         <is>
-          <t>Scripts &amp; automation</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Research</t>
         </is>
       </c>
       <c r="E78" s="15" t="inlineStr">
@@ -7272,7 +7256,7 @@
       </c>
       <c r="F78" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G78" s="15" t="inlineStr">
@@ -7282,17 +7266,17 @@
       </c>
       <c r="H78" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
-          <t>New or inherited account; prevent Google auto-applying changes</t>
+          <t>Calling winners in RSA/landing page tests</t>
         </is>
       </c>
       <c r="K78" s="15" t="inlineStr">
@@ -7308,7 +7292,7 @@
       <c r="M78" s="15" t="n"/>
       <c r="N78" s="17" t="inlineStr">
         <is>
-          <t>skills/78-recommendations-auto-apply-opt-out/</t>
+          <t>skills/82-statistical-significance-ad-tests/</t>
         </is>
       </c>
       <c r="O78" s="15" t="n"/>
@@ -7319,7 +7303,7 @@
       </c>
       <c r="Q78" s="16" t="inlineStr">
         <is>
-          <t>Google removing auto-apply as a per-account setting; Google extending system bulk changes beyond low-activity keywords and ad groups; changes to change_event retention or the 10k-row cap that break the monitoring script.</t>
+          <t>Google removing "Do not optimize" rotation entirely; changes to RSA asset limits (15/4) or pinning rules; a documented significance method in ad variations; mandatory final URL expansion or AI Max text customisation breaking ad-vs-ad comparability.</t>
         </is>
       </c>
       <c r="R78" s="15" t="inlineStr">
@@ -7335,11 +7319,11 @@
     </row>
     <row r="79" ht="15" customHeight="1" s="13">
       <c r="A79" s="15" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B79" s="16" t="inlineStr">
         <is>
-          <t>Custom experiments — split, duration, valid win</t>
+          <t>Auction insights trend reading</t>
         </is>
       </c>
       <c r="C79" s="15" t="inlineStr">
@@ -7349,7 +7333,7 @@
       </c>
       <c r="D79" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E79" s="15" t="inlineStr">
@@ -7359,32 +7343,32 @@
       </c>
       <c r="F79" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G79" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H79" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J79" s="16" t="inlineStr">
         <is>
-          <t>Want to test a bid strategy, structure or landing page properly</t>
+          <t>Performance shift with no internal change; suspect competitors</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
@@ -7395,7 +7379,7 @@
       <c r="M79" s="15" t="n"/>
       <c r="N79" s="17" t="inlineStr">
         <is>
-          <t>skills/79-custom-experiments/</t>
+          <t>skills/83-auction-insights-trend-reading/</t>
         </is>
       </c>
       <c r="O79" s="15" t="n"/>
@@ -7406,7 +7390,7 @@
       </c>
       <c r="Q79" s="16" t="inlineStr">
         <is>
-          <t>Changes to the 7-day ramp-up exclusion, the 80% default confidence display, budget-vs-traffic split rules per campaign type, or replacement of custom experiments by Google-recommended / multi-campaign experiments only.</t>
+          <t>Google changing auction-insights metric definitions, the 10% IS display floor, or time segmentation; removal of keyword-level auction insights under keywordless Search.</t>
         </is>
       </c>
       <c r="R79" s="15" t="inlineStr">
@@ -7422,11 +7406,11 @@
     </row>
     <row r="80" ht="15" customHeight="1" s="13">
       <c r="A80" s="15" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B80" s="16" t="inlineStr">
         <is>
-          <t>Geo experiments / conversion lift</t>
+          <t>Impression share decomposition decision rule</t>
         </is>
       </c>
       <c r="C80" s="15" t="inlineStr">
@@ -7436,7 +7420,7 @@
       </c>
       <c r="D80" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E80" s="15" t="inlineStr">
@@ -7451,27 +7435,27 @@
       </c>
       <c r="G80" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H80" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J80" s="16" t="inlineStr">
         <is>
-          <t>Need incrementality evidence for a channel or campaign</t>
+          <t>Lost IS; deciding budget vs. bid vs. QS action</t>
         </is>
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
@@ -7482,7 +7466,7 @@
       <c r="M80" s="15" t="n"/>
       <c r="N80" s="17" t="inlineStr">
         <is>
-          <t>skills/80-geo-experiments-conversion-lift/</t>
+          <t>skills/84-impression-share-decomposition/</t>
         </is>
       </c>
       <c r="O80" s="15" t="n"/>
@@ -7493,12 +7477,12 @@
       </c>
       <c r="Q80" s="16" t="inlineStr">
         <is>
-          <t>Changes to Conversion Lift minimums ($5k budget, 1,000 conversions, 14 days), the certainty selector, geo-based study availability, how projected cooldown conversions are included, or Google exposing/removing the priors behind its Bayesian lift estimates.</t>
+          <t>Google reinstating bid suppression on budget-limited tCPA/tROAS campaigns; changes to eligible-impression estimation; removal of the budget/rank split in lost-IS columns.</t>
         </is>
       </c>
       <c r="R80" s="15" t="inlineStr">
         <is>
-          <t>Adequate</t>
+          <t>Strong</t>
         </is>
       </c>
       <c r="S80" s="15" t="inlineStr">
@@ -7509,11 +7493,11 @@
     </row>
     <row r="81" ht="15" customHeight="1" s="13">
       <c r="A81" s="15" t="n">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B81" s="16" t="inlineStr">
         <is>
-          <t>Brand incrementality test</t>
+          <t>Hour-of-day / day-of-week heatmap analysis</t>
         </is>
       </c>
       <c r="C81" s="15" t="inlineStr">
@@ -7528,12 +7512,12 @@
       </c>
       <c r="E81" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F81" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G81" s="15" t="inlineStr">
@@ -7543,17 +7527,17 @@
       </c>
       <c r="H81" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J81" s="16" t="inlineStr">
         <is>
-          <t>Question whether brand spend is incremental</t>
+          <t>Suspect performance varies by time; deciding schedules</t>
         </is>
       </c>
       <c r="K81" s="15" t="inlineStr">
@@ -7569,7 +7553,7 @@
       <c r="M81" s="15" t="n"/>
       <c r="N81" s="17" t="inlineStr">
         <is>
-          <t>skills/81-brand-incrementality-test/</t>
+          <t>skills/85-hour-day-heatmap-analysis/</t>
         </is>
       </c>
       <c r="O81" s="15" t="n"/>
@@ -7580,7 +7564,7 @@
       </c>
       <c r="Q81" s="16" t="inlineStr">
         <is>
-          <t>Removal or change of PMax brand exclusions / Search brand lists; changes to Conversion Lift minimums; Google altering serving preference between exact-match keywords and PMax for brand queries.</t>
+          <t>Google re-enabling ad-schedule bid adjustments under Smart Bidding, changing the 30.4× pacing rule for scheduled campaigns, or removing ad schedules / −100% device adjustments.</t>
         </is>
       </c>
       <c r="R81" s="15" t="inlineStr">
@@ -7596,11 +7580,11 @@
     </row>
     <row r="82" ht="15" customHeight="1" s="13">
       <c r="A82" s="15" t="n">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B82" s="16" t="inlineStr">
         <is>
-          <t>Statistical significance for ad tests</t>
+          <t>Attribution model comparison (DDA vs last click)</t>
         </is>
       </c>
       <c r="C82" s="15" t="inlineStr">
@@ -7610,7 +7594,7 @@
       </c>
       <c r="D82" s="15" t="inlineStr">
         <is>
-          <t>Research</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E82" s="15" t="inlineStr">
@@ -7620,12 +7604,12 @@
       </c>
       <c r="F82" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G82" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H82" s="15" t="inlineStr">
@@ -7640,12 +7624,12 @@
       </c>
       <c r="J82" s="16" t="inlineStr">
         <is>
-          <t>Calling winners in RSA/landing page tests</t>
+          <t>Reporting delta vs. client's analytics; upper-funnel credit</t>
         </is>
       </c>
       <c r="K82" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L82" s="15" t="inlineStr">
@@ -7656,7 +7640,7 @@
       <c r="M82" s="15" t="n"/>
       <c r="N82" s="17" t="inlineStr">
         <is>
-          <t>skills/82-statistical-significance-ad-tests/</t>
+          <t>skills/86-attribution-model-comparison/</t>
         </is>
       </c>
       <c r="O82" s="15" t="n"/>
@@ -7667,12 +7651,12 @@
       </c>
       <c r="Q82" s="16" t="inlineStr">
         <is>
-          <t>Google removing "Do not optimize" rotation entirely; changes to RSA asset limits (15/4) or pinning rules; a documented significance method in ad variations; mandatory final URL expansion or AI Max text customisation breaking ad-vs-ad comparability.</t>
+          <t>Google changing the DDA default or its 200-conversion / 2,000-interaction recommendation, the 90-day GCLID import window, the new-customer value adjustment columns, or by-conversion-time reporting.</t>
         </is>
       </c>
       <c r="R82" s="15" t="inlineStr">
         <is>
-          <t>Strong</t>
+          <t>Adequate</t>
         </is>
       </c>
       <c r="S82" s="15" t="inlineStr">
@@ -7683,31 +7667,31 @@
     </row>
     <row r="83" ht="15" customHeight="1" s="13">
       <c r="A83" s="15" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B83" s="16" t="inlineStr">
         <is>
-          <t>Auction insights trend reading</t>
+          <t>Location options: presence vs. presence-or-interest</t>
         </is>
       </c>
       <c r="C83" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Defaults to override</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E83" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F83" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G83" s="15" t="inlineStr">
@@ -7717,17 +7701,17 @@
       </c>
       <c r="H83" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J83" s="16" t="inlineStr">
         <is>
-          <t>Performance shift with no internal change; suspect competitors</t>
+          <t>Every new campaign; auditing inherited accounts</t>
         </is>
       </c>
       <c r="K83" s="15" t="inlineStr">
@@ -7743,7 +7727,7 @@
       <c r="M83" s="15" t="n"/>
       <c r="N83" s="17" t="inlineStr">
         <is>
-          <t>skills/83-auction-insights-trend-reading/</t>
+          <t>skills/87-location-options-presence/</t>
         </is>
       </c>
       <c r="O83" s="15" t="n"/>
@@ -7754,7 +7738,7 @@
       </c>
       <c r="Q83" s="16" t="inlineStr">
         <is>
-          <t>Google changing auction-insights metric definitions, the 10% IS display floor, or time segmentation; removal of keyword-level auction insights under keywordless Search.</t>
+          <t>Google removing the "Presence" targeting option (as it removed "Search interest" in April 2023); a native User-location report returning to the UI; location bid modifiers becoming available under tCPA/tROAS.</t>
         </is>
       </c>
       <c r="R83" s="15" t="inlineStr">
@@ -7770,21 +7754,21 @@
     </row>
     <row r="84" ht="15" customHeight="1" s="13">
       <c r="A84" s="15" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B84" s="16" t="inlineStr">
         <is>
-          <t>Impression share decomposition decision rule</t>
+          <t>Standard off-list (partners, display expansion, URL expansion, auto-apply)</t>
         </is>
       </c>
       <c r="C84" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Defaults to override</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E84" s="15" t="inlineStr">
@@ -7794,7 +7778,7 @@
       </c>
       <c r="F84" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G84" s="15" t="inlineStr">
@@ -7804,7 +7788,7 @@
       </c>
       <c r="H84" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -7814,12 +7798,12 @@
       </c>
       <c r="J84" s="16" t="inlineStr">
         <is>
-          <t>Lost IS; deciding budget vs. bid vs. QS action</t>
+          <t>Every new campaign; auditing inherited accounts</t>
         </is>
       </c>
       <c r="K84" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Epiminds method</t>
         </is>
       </c>
       <c r="L84" s="15" t="inlineStr">
@@ -7830,7 +7814,7 @@
       <c r="M84" s="15" t="n"/>
       <c r="N84" s="17" t="inlineStr">
         <is>
-          <t>skills/84-impression-share-decomposition/</t>
+          <t>skills/88-standard-off-list/</t>
         </is>
       </c>
       <c r="O84" s="15" t="n"/>
@@ -7841,7 +7825,7 @@
       </c>
       <c r="Q84" s="16" t="inlineStr">
         <is>
-          <t>Google reinstating bid suppression on budget-limited tCPA/tROAS campaigns; changes to eligible-impression estimation; removal of the budget/rank split in lost-IS columns.</t>
+          <t>Google defaulting search partners or Display Expansion to off; partner-site reporting or exclusions arriving for Search; Final URL expansion defaulting to off or gaining keyword-level control; auto-apply recommendations being removed or moved to MCC level.</t>
         </is>
       </c>
       <c r="R84" s="15" t="inlineStr">
@@ -7857,41 +7841,41 @@
     </row>
     <row r="85" ht="15" customHeight="1" s="13">
       <c r="A85" s="15" t="n">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B85" s="16" t="inlineStr">
         <is>
-          <t>Hour-of-day / day-of-week heatmap analysis</t>
+          <t>Ad rotation settings under Smart Bidding</t>
         </is>
       </c>
       <c r="C85" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Defaults to override</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E85" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F85" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G85" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H85" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I85" s="15" t="inlineStr">
@@ -7901,12 +7885,12 @@
       </c>
       <c r="J85" s="16" t="inlineStr">
         <is>
-          <t>Suspect performance varies by time; deciding schedules</t>
+          <t>Setting up or auditing ad rotation</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Google docs + practitioner</t>
         </is>
       </c>
       <c r="L85" s="15" t="inlineStr">
@@ -7917,7 +7901,7 @@
       <c r="M85" s="15" t="n"/>
       <c r="N85" s="17" t="inlineStr">
         <is>
-          <t>skills/85-hour-day-heatmap-analysis/</t>
+          <t>skills/89-ad-rotation-smart-bidding/</t>
         </is>
       </c>
       <c r="O85" s="15" t="n"/>
@@ -7928,7 +7912,7 @@
       </c>
       <c r="Q85" s="16" t="inlineStr">
         <is>
-          <t>Google re-enabling ad-schedule bid adjustments under Smart Bidding, changing the 30.4× pacing rule for scheduled campaigns, or removing ad schedules / −100% device adjustments.</t>
+          <t>Google honouring "Do not optimize" under Smart Bidding; Optimize being re-tuned to conversions rather than clicks; the rotation setting being removed; Ad variations experiments being withdrawn.</t>
         </is>
       </c>
       <c r="R85" s="15" t="inlineStr">
@@ -7944,21 +7928,21 @@
     </row>
     <row r="86" ht="15" customHeight="1" s="13">
       <c r="A86" s="15" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B86" s="16" t="inlineStr">
         <is>
-          <t>Attribution model comparison (DDA vs last click)</t>
+          <t>Account-level negatives &amp; brand restrictions</t>
         </is>
       </c>
       <c r="C86" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Defaults to override</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E86" s="15" t="inlineStr">
@@ -7968,32 +7952,32 @@
       </c>
       <c r="F86" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G86" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H86" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J86" s="16" t="inlineStr">
         <is>
-          <t>Reporting delta vs. client's analytics; upper-funnel credit</t>
+          <t>Account-wide exclusions needed across many campaigns</t>
         </is>
       </c>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Google docs (recent feature)</t>
         </is>
       </c>
       <c r="L86" s="15" t="inlineStr">
@@ -8004,7 +7988,7 @@
       <c r="M86" s="15" t="n"/>
       <c r="N86" s="17" t="inlineStr">
         <is>
-          <t>skills/86-attribution-model-comparison/</t>
+          <t>skills/90-account-level-negatives-brand-restrictions/</t>
         </is>
       </c>
       <c r="O86" s="15" t="n"/>
@@ -8015,7 +7999,7 @@
       </c>
       <c r="Q86" s="16" t="inlineStr">
         <is>
-          <t>Google changing the DDA default or its 200-conversion / 2,000-interaction recommendation, the 90-day GCLID import window, the new-customer value adjustment columns, or by-conversion-time reporting.</t>
+          <t>The 1,000-keyword account-level cap changing; account-level negatives gaining per-campaign-type scoping; brand exclusions reliably covering close variants (new cross-account evidence); PMax negatives at asset-group level.</t>
         </is>
       </c>
       <c r="R86" s="15" t="inlineStr">
@@ -8031,21 +8015,21 @@
     </row>
     <row r="87" ht="15" customHeight="1" s="13">
       <c r="A87" s="15" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B87" s="16" t="inlineStr">
         <is>
-          <t>Location options: presence vs. presence-or-interest</t>
+          <t>Full account audit — multi-module diagnostic</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">
         <is>
-          <t>Defaults to override</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E87" s="15" t="inlineStr">
@@ -8055,7 +8039,7 @@
       </c>
       <c r="F87" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G87" s="15" t="inlineStr">
@@ -8065,7 +8049,7 @@
       </c>
       <c r="H87" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
@@ -8075,7 +8059,7 @@
       </c>
       <c r="J87" s="16" t="inlineStr">
         <is>
-          <t>Every new campaign; auditing inherited accounts</t>
+          <t>Taking over an account, quarterly review, or pre-pitch; need a ranked list of critical issues across tracking, structure, settings, keywords/search terms, bids/budgets, ads, landing pages</t>
         </is>
       </c>
       <c r="K87" s="15" t="inlineStr">
@@ -8085,54 +8069,42 @@
       </c>
       <c r="L87" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="M87" s="15" t="n"/>
-      <c r="N87" s="17" t="inlineStr">
-        <is>
-          <t>skills/87-location-options-presence/</t>
-        </is>
-      </c>
-      <c r="O87" s="15" t="n"/>
-      <c r="P87" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Q87" s="16" t="inlineStr">
-        <is>
-          <t>Google removing the "Presence" targeting option (as it removed "Search interest" in April 2023); a native User-location report returning to the UI; location bid modifiers becoming available under tCPA/tROAS.</t>
-        </is>
-      </c>
-      <c r="R87" s="15" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
+      <c r="N87" s="17" t="n"/>
+      <c r="O87" s="15" t="inlineStr">
+        <is>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+        </is>
+      </c>
+      <c r="P87" s="15" t="n"/>
+      <c r="Q87" s="16" t="n"/>
+      <c r="R87" s="15" t="n"/>
       <c r="S87" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="88" ht="15" customHeight="1" s="13">
       <c r="A88" s="15" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B88" s="16" t="inlineStr">
         <is>
-          <t>Standard off-list (partners, display expansion, URL expansion, auto-apply)</t>
+          <t>Conversion tracking audit</t>
         </is>
       </c>
       <c r="C88" s="15" t="inlineStr">
         <is>
-          <t>Defaults to override</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E88" s="15" t="inlineStr">
@@ -8162,74 +8134,62 @@
       </c>
       <c r="J88" s="16" t="inlineStr">
         <is>
-          <t>Every new campaign; auditing inherited accounts</t>
+          <t>Before trusting Smart Bidding on any account: verify tags, primary/secondary actions, duplicates, attribution, Enhanced Conversions, Consent Mode v2, OCI, counting method</t>
         </is>
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>Epiminds method</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="M88" s="15" t="n"/>
-      <c r="N88" s="17" t="inlineStr">
-        <is>
-          <t>skills/88-standard-off-list/</t>
-        </is>
-      </c>
-      <c r="O88" s="15" t="n"/>
-      <c r="P88" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Q88" s="16" t="inlineStr">
-        <is>
-          <t>Google defaulting search partners or Display Expansion to off; partner-site reporting or exclusions arriving for Search; Final URL expansion defaulting to off or gaining keyword-level control; auto-apply recommendations being removed or moved to MCC level.</t>
-        </is>
-      </c>
-      <c r="R88" s="15" t="inlineStr">
-        <is>
-          <t>Strong</t>
-        </is>
-      </c>
+      <c r="N88" s="17" t="n"/>
+      <c r="O88" s="15" t="inlineStr">
+        <is>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
+        </is>
+      </c>
+      <c r="P88" s="15" t="n"/>
+      <c r="Q88" s="16" t="n"/>
+      <c r="R88" s="15" t="n"/>
       <c r="S88" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="89" ht="23.25" customHeight="1" s="13">
       <c r="A89" s="15" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B89" s="16" t="inlineStr">
         <is>
-          <t>Ad rotation settings under Smart Bidding</t>
+          <t>Weekly account review routine</t>
         </is>
       </c>
       <c r="C89" s="15" t="inlineStr">
         <is>
-          <t>Defaults to override</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E89" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F89" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G89" s="15" t="inlineStr">
@@ -8239,74 +8199,62 @@
       </c>
       <c r="H89" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Weekly</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>Setting up or auditing ad rotation</t>
+          <t>Running the standing weekly check: what to look at, in what order, over which lookbacks, and what triggers an action vs a watch</t>
         </is>
       </c>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>Google docs + practitioner</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L89" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="M89" s="15" t="n"/>
-      <c r="N89" s="17" t="inlineStr">
-        <is>
-          <t>skills/89-ad-rotation-smart-bidding/</t>
-        </is>
-      </c>
-      <c r="O89" s="15" t="n"/>
-      <c r="P89" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Q89" s="16" t="inlineStr">
-        <is>
-          <t>Google honouring "Do not optimize" under Smart Bidding; Optimize being re-tuned to conversions rather than clicks; the rotation setting being removed; Ad variations experiments being withdrawn.</t>
-        </is>
-      </c>
-      <c r="R89" s="15" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
+      <c r="N89" s="17" t="n"/>
+      <c r="O89" s="15" t="inlineStr">
+        <is>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
+        </is>
+      </c>
+      <c r="P89" s="15" t="n"/>
+      <c r="Q89" s="16" t="n"/>
+      <c r="R89" s="15" t="n"/>
       <c r="S89" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="90" ht="15" customHeight="1" s="13">
       <c r="A90" s="15" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="B90" s="16" t="inlineStr">
         <is>
-          <t>Account-level negatives &amp; brand restrictions</t>
+          <t>Performance change root-cause diagnosis</t>
         </is>
       </c>
       <c r="C90" s="15" t="inlineStr">
         <is>
-          <t>Defaults to override</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E90" s="15" t="inlineStr">
@@ -8316,7 +8264,7 @@
       </c>
       <c r="F90" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G90" s="15" t="inlineStr">
@@ -8326,7 +8274,7 @@
       </c>
       <c r="H90" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
@@ -8336,64 +8284,52 @@
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
-          <t>Account-wide exclusions needed across many campaigns</t>
+          <t>CPC, CTR, clicks, conversions or CPA moved and nobody knows why; need a decomposition tree before touching anything</t>
         </is>
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>Google docs (recent feature)</t>
+          <t>Adalysis KPI monitoring series</t>
         </is>
       </c>
       <c r="L90" s="15" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Proposed</t>
         </is>
       </c>
       <c r="M90" s="15" t="n"/>
-      <c r="N90" s="17" t="inlineStr">
-        <is>
-          <t>skills/90-account-level-negatives-brand-restrictions/</t>
-        </is>
-      </c>
-      <c r="O90" s="15" t="n"/>
-      <c r="P90" s="15" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="Q90" s="16" t="inlineStr">
-        <is>
-          <t>The 1,000-keyword account-level cap changing; account-level negatives gaining per-campaign-type scoping; brand exclusions reliably covering close variants (new cross-account evidence); PMax negatives at asset-group level.</t>
-        </is>
-      </c>
-      <c r="R90" s="15" t="inlineStr">
-        <is>
-          <t>Adequate</t>
-        </is>
-      </c>
+      <c r="N90" s="17" t="n"/>
+      <c r="O90" s="15" t="inlineStr">
+        <is>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
+        </is>
+      </c>
+      <c r="P90" s="15" t="n"/>
+      <c r="Q90" s="16" t="n"/>
+      <c r="R90" s="15" t="n"/>
       <c r="S90" s="15" t="inlineStr">
         <is>
-          <t>PASS</t>
+          <t>NEEDS ELIAS</t>
         </is>
       </c>
     </row>
     <row r="91" ht="15" customHeight="1" s="13">
       <c r="A91" s="15" t="n">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="B91" s="16" t="inlineStr">
         <is>
-          <t>Full account audit — multi-module diagnostic</t>
+          <t>Bid strategy selection — Smart Bidding vs manual, target vs maximise</t>
         </is>
       </c>
       <c r="C91" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E91" s="15" t="inlineStr">
@@ -8403,7 +8339,7 @@
       </c>
       <c r="F91" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G91" s="15" t="inlineStr">
@@ -8413,7 +8349,7 @@
       </c>
       <c r="H91" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
@@ -8423,12 +8359,12 @@
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
-          <t>Taking over an account, quarterly review, or pre-pitch; need a ranked list of critical issues across tracking, structure, settings, keywords/search terms, bids/budgets, ads, landing pages</t>
+          <t>Choosing or changing a bid strategy per campaign; deciding whether volume, signal quality and spend-control needs justify Smart Bidding at all</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Optmyzr / Adalysis / PPC Mastery</t>
         </is>
       </c>
       <c r="L91" s="15" t="inlineStr">
@@ -8440,7 +8376,7 @@
       <c r="N91" s="17" t="n"/>
       <c r="O91" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub exposes 'Account Audit — 24 diagnostics across 5 modules' and an Account Health Report (Tracking, Campaign Structure, Landing Pages, QS, Ad Quality); TPE #149 lists 13 stacked audits; Hopkins (SEJ 2025) on regular audits; Optmyzr 9-section audit. Library has per-topic diagnostics but no library-level audit row.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
         </is>
       </c>
       <c r="P91" s="15" t="n"/>
@@ -8454,11 +8390,11 @@
     </row>
     <row r="92">
       <c r="A92" s="15" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B92" s="16" t="inlineStr">
         <is>
-          <t>Conversion tracking audit</t>
+          <t>Targets from unit economics — break-even ROAS, profit curve, growth vs efficiency</t>
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr">
@@ -8468,7 +8404,7 @@
       </c>
       <c r="D92" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E92" s="15" t="inlineStr">
@@ -8488,7 +8424,7 @@
       </c>
       <c r="H92" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -8498,12 +8434,12 @@
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
-          <t>Before trusting Smart Bidding on any account: verify tags, primary/secondary actions, duplicates, attribution, Enhanced Conversions, Consent Mode v2, OCI, counting method</t>
+          <t>Setting or renegotiating tCPA/tROAS with a client; need margin, LTV, payback and a primary-goal/guardrail pair before touching the target</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Mike Rhodes / PPC Mastery</t>
         </is>
       </c>
       <c r="L92" s="15" t="inlineStr">
@@ -8515,7 +8451,7 @@
       <c r="N92" s="17" t="n"/>
       <c r="O92" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS public hub 'Tracking Audit — 50-point check' naming Enhanced Conversions, Consent Mode v2, OCI, attribution model, duplicate actions, primary/secondary; ZATO 'Conversion tracking: why clean data is everything'; Hopkins SEJ 2024 enterprise tracking pitfalls. Rows 47/48 cover two pieces only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
         </is>
       </c>
       <c r="P92" s="15" t="n"/>
@@ -8529,16 +8465,16 @@
     </row>
     <row r="93">
       <c r="A93" s="15" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B93" s="16" t="inlineStr">
         <is>
-          <t>Weekly account review routine</t>
+          <t>Smart Bidding learning period — what resets it and change-size rules</t>
         </is>
       </c>
       <c r="C93" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
@@ -8563,17 +8499,17 @@
       </c>
       <c r="H93" s="15" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
-          <t>Running the standing weekly check: what to look at, in what order, over which lookbacks, and what triggers an action vs a watch</t>
+          <t>Planning any target, budget, structure or conversion-action change on a Smart Bidding campaign; deciding step size and spacing to avoid relearning</t>
         </is>
       </c>
       <c r="K93" s="15" t="inlineStr">
@@ -8590,7 +8526,7 @@
       <c r="N93" s="17" t="n"/>
       <c r="O93" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Performance Analysis' with sample output 'Weekly Review' and 7/30/90/365-day trend windows (TPE #149); Optmyzr audit cadence (weekly health / monthly / quarterly); Adalysis 'how to automate your Google Ads KPI monitoring'.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
         </is>
       </c>
       <c r="P93" s="15" t="n"/>
@@ -8604,41 +8540,41 @@
     </row>
     <row r="94">
       <c r="A94" s="15" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B94" s="16" t="inlineStr">
         <is>
-          <t>Performance change root-cause diagnosis</t>
+          <t>AI Max for Search — test design and evaluation</t>
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Keyword &amp; query</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F94" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G94" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H94" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -8648,12 +8584,12 @@
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>CPC, CTR, clicks, conversions or CPA moved and nobody knows why; need a decomposition tree before touching anything</t>
+          <t>Google is pushing AI Max; need prerequisites, a limited test, and how to read search terms, asset source and URL expansion before keeping it on</t>
         </is>
       </c>
       <c r="K94" s="15" t="inlineStr">
         <is>
-          <t>Adalysis KPI monitoring series</t>
+          <t>Adalysis / ZATO</t>
         </is>
       </c>
       <c r="L94" s="15" t="inlineStr">
@@ -8665,7 +8601,7 @@
       <c r="N94" s="17" t="n"/>
       <c r="O94" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'KPI monitoring diagnosis' series (why does CPC/cost, CTR, clicks, conversions/CVR, impression volume change) plus 'analyze the correct time periods'; PPC OS 'Performance Analysis — the why behind metric shifts'. Rows 84/83/49 cover single causes only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
         </is>
       </c>
       <c r="P94" s="15" t="n"/>
@@ -8679,41 +8615,41 @@
     </row>
     <row r="95">
       <c r="A95" s="15" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B95" s="16" t="inlineStr">
         <is>
-          <t>Bid strategy selection — Smart Bidding vs manual, target vs maximise</t>
+          <t>Product performance bucketing for Shopping and PMax</t>
         </is>
       </c>
       <c r="C95" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E95" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F95" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G95" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H95" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
@@ -8723,12 +8659,12 @@
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>Choosing or changing a bid strategy per campaign; deciding whether volume, signal quality and spend-control needs justify Smart Bidding at all</t>
+          <t>Spend concentrated on a few SKUs while most products get no impressions; want zombies/heroes/sidekicks split into campaigns or asset groups</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>Optmyzr / Adalysis / PPC Mastery</t>
+          <t>Mike Rhodes / Optmyzr</t>
         </is>
       </c>
       <c r="L95" s="15" t="inlineStr">
@@ -8740,7 +8676,7 @@
       <c r="N95" s="17" t="n"/>
       <c r="O95" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'When to stop using Smart Bidding' (Optmyzr, May 2026; ~50 conv/30d rule, manual CPC + rules alternative); Adalysis 'when to use target vs max CPA/ROAS'; PPC Mastery lists bid strategy choice as a core topic; Hopkins SEJ budget-by-stage. No existing row covers the choice itself.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
         </is>
       </c>
       <c r="P95" s="15" t="n"/>
@@ -8754,11 +8690,11 @@
     </row>
     <row r="96">
       <c r="A96" s="15" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B96" s="16" t="inlineStr">
         <is>
-          <t>Targets from unit economics — break-even ROAS, profit curve, growth vs efficiency</t>
+          <t>Bid adjustments under Smart Bidding — what still applies</t>
         </is>
       </c>
       <c r="C96" s="15" t="inlineStr">
@@ -8768,7 +8704,7 @@
       </c>
       <c r="D96" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Setting</t>
         </is>
       </c>
       <c r="E96" s="15" t="inlineStr">
@@ -8788,22 +8724,22 @@
       </c>
       <c r="H96" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>Setting or renegotiating tCPA/tROAS with a client; need margin, LTV, payback and a primary-goal/guardrail pair before touching the target</t>
+          <t>Inherited account full of device/location/schedule/audience adjustments on tCPA/tROAS; deciding what to strip, what -100% exclusions remain valid</t>
         </is>
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes / PPC Mastery</t>
+          <t>PPC Mastery / Adalysis</t>
         </is>
       </c>
       <c r="L96" s="15" t="inlineStr">
@@ -8815,7 +8751,7 @@
       <c r="N96" s="17" t="n"/>
       <c r="O96" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 8020agent (profit curve, budget optimisation, break-even ROAS); PPC OS course 'Goal Setting Mastery' + vault 'target calculators'; TPE #144 growth vs efficiency (primary focus + guardrail), TPE #148 LTV flywheel, TPE #149 Phase 1 context questions; Optmyzr ROAS-by-vertical benchmarks (Sep 2026).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
         </is>
       </c>
       <c r="P96" s="15" t="n"/>
@@ -8829,11 +8765,11 @@
     </row>
     <row r="97">
       <c r="A97" s="15" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B97" s="16" t="inlineStr">
         <is>
-          <t>Smart Bidding learning period — what resets it and change-size rules</t>
+          <t>Budget reallocation across campaigns by marginal return</t>
         </is>
       </c>
       <c r="C97" s="15" t="inlineStr">
@@ -8853,27 +8789,27 @@
       </c>
       <c r="F97" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Scale</t>
         </is>
       </c>
       <c r="G97" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H97" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>Planning any target, budget, structure or conversion-action change on a Smart Bidding campaign; deciding step size and spacing to avoid relearning</t>
+          <t>Fixed account budget; some campaigns limited by budget, others underspending; deciding where the next euro goes and whether shared budgets help</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
@@ -8890,7 +8826,7 @@
       <c r="N97" s="17" t="n"/>
       <c r="O97" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'What are learning periods' (SEJ, Dec 2025) and 'Why do budgets overspend with tROAS' (Feb 2026); Adalysis 'what happens when you change your PPC budgets'; PPC Mastery structure-under-Smart-Bidding material. Row 9 only covers campaigns stuck in learning from low volume.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
         </is>
       </c>
       <c r="P97" s="15" t="n"/>
@@ -8904,26 +8840,26 @@
     </row>
     <row r="98">
       <c r="A98" s="15" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B98" s="16" t="inlineStr">
         <is>
-          <t>AI Max for Search — test design and evaluation</t>
+          <t>Scaling without breaking efficiency — budget and target step rules</t>
         </is>
       </c>
       <c r="C98" s="15" t="inlineStr">
         <is>
-          <t>Keyword &amp; query</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E98" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F98" s="15" t="inlineStr">
@@ -8938,22 +8874,22 @@
       </c>
       <c r="H98" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>Google is pushing AI Max; need prerequisites, a limited test, and how to read search terms, asset source and URL expansion before keeping it on</t>
+          <t>Client wants 2x volume; deciding the order of levers (budget, target, match type, campaign type) and step sizes without CPA blowing up</t>
         </is>
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>Adalysis / ZATO</t>
+          <t>ZATO / PPC Mastery</t>
         </is>
       </c>
       <c r="L98" s="15" t="inlineStr">
@@ -8965,7 +8901,7 @@
       <c r="N98" s="17" t="n"/>
       <c r="O98" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'How to evaluate your AI Max performance' (Adalysis, Aug 2026; broad-match prerequisite, 30 conv/mo, n-gram + asset-source + URL analysis); ZATO has a whole 'AI Max for Search' topic; Cruz 'What are you optimizing for when keywords matter less' (SEL, Apr 2026). No row mentions AI Max.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
         </is>
       </c>
       <c r="P98" s="15" t="n"/>
@@ -8979,56 +8915,56 @@
     </row>
     <row r="99">
       <c r="A99" s="15" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B99" s="16" t="inlineStr">
         <is>
-          <t>Product performance bucketing for Shopping and PMax</t>
+          <t>Campaign not serving / zero impressions troubleshooting</t>
         </is>
       </c>
       <c r="C99" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Testing &amp; measurement</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E99" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F99" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G99" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H99" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>P1</t>
+          <t>P2</t>
         </is>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>Spend concentrated on a few SKUs while most products get no impressions; want zombies/heroes/sidekicks split into campaigns or asset groups</t>
+          <t>Live campaign with no or near-zero impressions; need the ordered checklist (billing, policy, status, targeting, bids/targets, negatives, eligibility) before escalating</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes / Optmyzr</t>
+          <t>ZATO / Navah Hopkins</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
@@ -9040,7 +8976,7 @@
       <c r="N99" s="17" t="n"/>
       <c r="O99" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'products' and 'check-product-data' scripts (GitHub mikerhodesideas/free); Optmyzr 'segment products in Google Shopping ads'; PPC OS 'shopping feed and product optimization'. Row 64 tiers by margin/stock, not by performance.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
         </is>
       </c>
       <c r="P99" s="15" t="n"/>
@@ -9054,26 +8990,26 @@
     </row>
     <row r="100">
       <c r="A100" s="15" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B100" s="16" t="inlineStr">
         <is>
-          <t>Bid adjustments under Smart Bidding — what still applies</t>
+          <t>New Search campaign launch checklist and first-30-days watch</t>
         </is>
       </c>
       <c r="C100" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Account structure</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
         <is>
-          <t>Setting</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E100" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F100" s="15" t="inlineStr">
@@ -9083,7 +9019,7 @@
       </c>
       <c r="G100" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>New</t>
         </is>
       </c>
       <c r="H100" s="15" t="inlineStr">
@@ -9098,12 +9034,12 @@
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>Inherited account full of device/location/schedule/audience adjustments on tCPA/tROAS; deciding what to strip, what -100% exclusions remain valid</t>
+          <t>Launching a new Search campaign; pre-launch settings check and what to review in weeks 1–2 (relevance, net-new impressions, IS) vs weeks 3–4 (conversion quality, serving, match type, bid method switch)</t>
         </is>
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
-          <t>PPC Mastery / Adalysis</t>
+          <t>Adalysis / PPC Mastery</t>
         </is>
       </c>
       <c r="L100" s="15" t="inlineStr">
@@ -9115,7 +9051,7 @@
       <c r="N100" s="17" t="n"/>
       <c r="O100" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: TPE #145 'Why bid adjustments are dead' (public cheat-sheet by strategy); Adalysis 'how bid adjustments are used by bidding method' and 'how audience bid adjustments work with tCPA/tROAS'. Row 41 covers value rules only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
         </is>
       </c>
       <c r="P100" s="15" t="n"/>
@@ -9129,16 +9065,16 @@
     </row>
     <row r="101">
       <c r="A101" s="15" t="n">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B101" s="16" t="inlineStr">
         <is>
-          <t>Budget reallocation across campaigns by marginal return</t>
+          <t>Ad assets (sitelinks, callouts, snippets, images) — build and evaluate</t>
         </is>
       </c>
       <c r="C101" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>RSA &amp; ad copy</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
@@ -9148,22 +9084,22 @@
       </c>
       <c r="E101" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F101" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G101" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H101" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I101" s="15" t="inlineStr">
@@ -9173,12 +9109,12 @@
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>Fixed account budget; some campaigns limited by budget, others underspending; deciding where the next euro goes and whether shared budgets help</t>
+          <t>Setting up or auditing assets; reading asset-level performance and the asset-vs-ad report; which assets to pin to campaign vs account level</t>
         </is>
       </c>
       <c r="K101" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Adalysis</t>
         </is>
       </c>
       <c r="L101" s="15" t="inlineStr">
@@ -9190,7 +9126,7 @@
       <c r="N101" s="17" t="n"/>
       <c r="O101" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Bids &amp; Budgets — reallocates budgets, validates targets'; Optmyzr 'manage PPC budgets' and 'smart bidding budget caps guide'; Adalysis 'why your campaigns are underspending' and 'IS loss due to budget'; Rhodes 8020agent budget optimiser. Row 71 is only the pacing alert.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
         </is>
       </c>
       <c r="P101" s="15" t="n"/>
@@ -9204,41 +9140,41 @@
     </row>
     <row r="102">
       <c r="A102" s="15" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="B102" s="16" t="inlineStr">
         <is>
-          <t>Scaling without breaking efficiency — budget and target step rules</t>
+          <t>Feed attribute optimisation beyond titles (product_type, google_product_category, id, description)</t>
         </is>
       </c>
       <c r="C102" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Technique</t>
         </is>
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F102" s="15" t="inlineStr">
         <is>
-          <t>Scale</t>
+          <t>Setup</t>
         </is>
       </c>
       <c r="G102" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H102" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -9248,12 +9184,12 @@
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
-          <t>Client wants 2x volume; deciding the order of levers (budget, target, match type, campaign type) and step sizes without CPA blowing up</t>
+          <t>Titles done; want the secondary attributes that drive matching and segmentation right, and stable product IDs before any feed-provider change</t>
         </is>
       </c>
       <c r="K102" s="15" t="inlineStr">
         <is>
-          <t>ZATO / PPC Mastery</t>
+          <t>ZATO Merchant Center Mastery</t>
         </is>
       </c>
       <c r="L102" s="15" t="inlineStr">
@@ -9265,7 +9201,7 @@
       <c r="N102" s="17" t="n"/>
       <c r="O102" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to scale Google Ads' and 'The physics of PPC'; TPE #147 bottom-up funnel, #144 growth vs efficiency; Hopkins 'From launch to scale: budget strategies for all campaign stages' (SEJ 2024).</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
         </is>
       </c>
       <c r="P102" s="15" t="n"/>
@@ -9279,16 +9215,16 @@
     </row>
     <row r="103">
       <c r="A103" s="15" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="B103" s="16" t="inlineStr">
         <is>
-          <t>Campaign not serving / zero impressions troubleshooting</t>
+          <t>Merchant Center account suspension recovery</t>
         </is>
       </c>
       <c r="C103" s="15" t="inlineStr">
         <is>
-          <t>Testing &amp; measurement</t>
+          <t>Shopping &amp; feeds</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
@@ -9298,12 +9234,12 @@
       </c>
       <c r="E103" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="F103" s="15" t="inlineStr">
         <is>
-          <t>Diagnose</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G103" s="15" t="inlineStr">
@@ -9323,12 +9259,12 @@
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
-          <t>Live campaign with no or near-zero impressions; need the ordered checklist (billing, policy, status, targeting, bids/targets, negatives, eligibility) before escalating</t>
+          <t>Account-level suspension (misrepresentation, unacceptable business practices, tax/shipping) rather than item disapprovals; need the compliance checklist and appeal sequence</t>
         </is>
       </c>
       <c r="K103" s="15" t="inlineStr">
         <is>
-          <t>ZATO / Navah Hopkins</t>
+          <t>ZATO</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
@@ -9340,7 +9276,7 @@
       <c r="N103" s="17" t="n"/>
       <c r="O103" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'Why isn't my campaign serving — the most asked question in the support forum'; Hopkins 'Why have my ads not got any impressions' (SEJ 2024). Rows 46 and 19 cover under-delivery and low-volume keywords, not non-serving.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
         </is>
       </c>
       <c r="P103" s="15" t="n"/>
@@ -9354,41 +9290,41 @@
     </row>
     <row r="104">
       <c r="A104" s="15" t="n">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B104" s="16" t="inlineStr">
         <is>
-          <t>New Search campaign launch checklist and first-30-days watch</t>
+          <t>PMax asset group and asset performance review</t>
         </is>
       </c>
       <c r="C104" s="15" t="inlineStr">
         <is>
-          <t>Account structure</t>
+          <t>Performance Max</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E104" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>PMax</t>
         </is>
       </c>
       <c r="F104" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G104" s="15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H104" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -9398,12 +9334,12 @@
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
-          <t>Launching a new Search campaign; pre-launch settings check and what to review in weeks 1–2 (relevance, net-new impressions, IS) vs weeks 3–4 (conversion quality, serving, match type, bid method switch)</t>
+          <t>Deciding which assets and asset groups to replace; reading asset ratings, asset-group spend and conversion split, and auto-generated vs supplied assets</t>
         </is>
       </c>
       <c r="K104" s="15" t="inlineStr">
         <is>
-          <t>Adalysis / PPC Mastery</t>
+          <t>Mike Rhodes</t>
         </is>
       </c>
       <c r="L104" s="15" t="inlineStr">
@@ -9415,7 +9351,7 @@
       <c r="N104" s="17" t="n"/>
       <c r="O104" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Geddes 'Launching a new Search campaign: what to watch in the first month' (Adalysis, 2025); PPC OS 'Search Mastery' public course lists a launch checklist. Rows 87/88 are settings only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
         </is>
       </c>
       <c r="P104" s="15" t="n"/>
@@ -9429,31 +9365,31 @@
     </row>
     <row r="105">
       <c r="A105" s="15" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="B105" s="16" t="inlineStr">
         <is>
-          <t>Ad assets (sitelinks, callouts, snippets, images) — build and evaluate</t>
+          <t>Spam conversions and invalid traffic polluting Smart Bidding</t>
         </is>
       </c>
       <c r="C105" s="15" t="inlineStr">
         <is>
-          <t>RSA &amp; ad copy</t>
+          <t>Bidding</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
         <is>
-          <t>Technique</t>
+          <t>Diagnostic</t>
         </is>
       </c>
       <c r="E105" s="15" t="inlineStr">
         <is>
-          <t>Search</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F105" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G105" s="15" t="inlineStr">
@@ -9473,12 +9409,12 @@
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>Setting up or auditing assets; reading asset-level performance and the asset-vs-ad report; which assets to pin to campaign vs account level</t>
+          <t>Sudden conversion spike with no revenue, bot form fills, or suspected click fraud; detect, confirm, negate/exclude, and clean the bidding signal</t>
         </is>
       </c>
       <c r="K105" s="15" t="inlineStr">
         <is>
-          <t>Adalysis</t>
+          <t>Practitioner method</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
@@ -9490,7 +9426,7 @@
       <c r="N105" s="17" t="n"/>
       <c r="O105" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Adalysis 'understanding and analyzing extension data', 'easily analyze ad extension usage', 'importance of ad extensions', '20 more sitelink ideas'; PPC OS 'Ad Quality (RSAs)' health sub-score. The library has no row on assets/extensions.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
         </is>
       </c>
       <c r="P105" s="15" t="n"/>
@@ -9504,16 +9440,16 @@
     </row>
     <row r="106">
       <c r="A106" s="15" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B106" s="16" t="inlineStr">
         <is>
-          <t>Feed attribute optimisation beyond titles (product_type, google_product_category, id, description)</t>
+          <t>Landing page audit for paid search</t>
         </is>
       </c>
       <c r="C106" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Quality Score</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
@@ -9523,12 +9459,12 @@
       </c>
       <c r="E106" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F106" s="15" t="inlineStr">
         <is>
-          <t>Setup</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G106" s="15" t="inlineStr">
@@ -9538,7 +9474,7 @@
       </c>
       <c r="H106" s="15" t="inlineStr">
         <is>
-          <t>One-off</t>
+          <t>As needed</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
@@ -9548,12 +9484,12 @@
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>Titles done; want the secondary attributes that drive matching and segmentation right, and stable product IDs before any feed-provider change</t>
+          <t>CVR low despite relevant traffic; structured LP audit (message match, hero, proof, speed, form/CTA, guarantee) and how to test LP with ad together</t>
         </is>
       </c>
       <c r="K106" s="15" t="inlineStr">
         <is>
-          <t>ZATO Merchant Center Mastery</t>
+          <t>PPC Mastery / Adalysis</t>
         </is>
       </c>
       <c r="L106" s="15" t="inlineStr">
@@ -9565,7 +9501,7 @@
       <c r="N106" s="17" t="n"/>
       <c r="O106" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'optimize product_type', 'optimize google_product_category', 'why the id attribute matters', 'optimize product descriptions (2026)', 'changing feed providers: roadmap'; PPC OS 'Feeds — titles and secondary attributes'. Rows 65/66 cover rules mechanics and titles only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
         </is>
       </c>
       <c r="P106" s="15" t="n"/>
@@ -9579,41 +9515,41 @@
     </row>
     <row r="107">
       <c r="A107" s="15" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B107" s="16" t="inlineStr">
         <is>
-          <t>Merchant Center account suspension recovery</t>
+          <t>Automation layering — guardrail automations over Google's automation</t>
         </is>
       </c>
       <c r="C107" s="15" t="inlineStr">
         <is>
-          <t>Shopping &amp; feeds</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E107" s="15" t="inlineStr">
         <is>
-          <t>Shopping</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F107" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Optimise</t>
         </is>
       </c>
       <c r="G107" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H107" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I107" s="15" t="inlineStr">
@@ -9623,12 +9559,12 @@
       </c>
       <c r="J107" s="16" t="inlineStr">
         <is>
-          <t>Account-level suspension (misrepresentation, unacceptable business practices, tax/shipping) rather than item disapprovals; need the compliance checklist and appeal sequence</t>
+          <t>Deciding which Google automations to adopt and which monitors (alerts, rules, scripts) must sit on top of each before go-live</t>
         </is>
       </c>
       <c r="K107" s="15" t="inlineStr">
         <is>
-          <t>ZATO</t>
+          <t>Fred Vallaeys</t>
         </is>
       </c>
       <c r="L107" s="15" t="inlineStr">
@@ -9640,7 +9576,7 @@
       <c r="N107" s="17" t="n"/>
       <c r="O107" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: ZATO 'How to fix a Merchant Center suspension for misrepresentation', 'tax suspension fix', 'preventing disapprovals and suspensions by mastering compliance'. Row 67 is item-level disapprovals.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
         </is>
       </c>
       <c r="P107" s="15" t="n"/>
@@ -9654,56 +9590,56 @@
     </row>
     <row r="108">
       <c r="A108" s="15" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B108" s="16" t="inlineStr">
         <is>
-          <t>PMax asset group and asset performance review</t>
+          <t>Change history monitoring</t>
         </is>
       </c>
       <c r="C108" s="15" t="inlineStr">
         <is>
-          <t>Performance Max</t>
+          <t>Scripts &amp; automation</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Diagnostic</t>
+          <t>Script</t>
         </is>
       </c>
       <c r="E108" s="15" t="inlineStr">
         <is>
-          <t>PMax</t>
+          <t>All</t>
         </is>
       </c>
       <c r="F108" s="15" t="inlineStr">
         <is>
-          <t>Optimise</t>
+          <t>Protect</t>
         </is>
       </c>
       <c r="G108" s="15" t="inlineStr">
         <is>
-          <t>Established</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="H108" s="15" t="inlineStr">
         <is>
-          <t>Monthly</t>
+          <t>One-off</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J108" s="16" t="inlineStr">
         <is>
-          <t>Deciding which assets and asset groups to replace; reading asset ratings, asset-group spend and conversion split, and auto-generated vs supplied assets</t>
+          <t>Multiple users, Google reps or auto-apply touching the account; want daily alerts on unexpected changes with who/what</t>
         </is>
       </c>
       <c r="K108" s="15" t="inlineStr">
         <is>
-          <t>Mike Rhodes</t>
+          <t>Nils Rooijmans</t>
         </is>
       </c>
       <c r="L108" s="15" t="inlineStr">
@@ -9715,7 +9651,7 @@
       <c r="N108" s="17" t="n"/>
       <c r="O108" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Rhodes 'pmax-assets' script (GitHub); PPC OS 'pMax' skill and 'Performance Max Mastery' course; Hopkins 'Should you use auto-generated creative' (SEJ 2026). Row 58 is structure only.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
         </is>
       </c>
       <c r="P108" s="15" t="n"/>
@@ -9729,16 +9665,16 @@
     </row>
     <row r="109">
       <c r="A109" s="15" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B109" s="16" t="inlineStr">
         <is>
-          <t>Spam conversions and invalid traffic polluting Smart Bidding</t>
+          <t>Lin-Rodnitzky ratio as a search-term health metric</t>
         </is>
       </c>
       <c r="C109" s="15" t="inlineStr">
         <is>
-          <t>Bidding</t>
+          <t>Keyword &amp; query</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -9748,37 +9684,37 @@
       </c>
       <c r="E109" s="15" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Search</t>
         </is>
       </c>
       <c r="F109" s="15" t="inlineStr">
         <is>
-          <t>Protect</t>
+          <t>Diagnose</t>
         </is>
       </c>
       <c r="G109" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Established</t>
         </is>
       </c>
       <c r="H109" s="15" t="inlineStr">
         <is>
-          <t>As needed</t>
+          <t>Monthly</t>
         </is>
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
-          <t>P2</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="J109" s="16" t="inlineStr">
         <is>
-          <t>Sudden conversion spike with no revenue, bot form fills, or suspected click fraud; detect, confirm, negate/exclude, and clean the bidding signal</t>
+          <t>Need one account-level number for whether query mining is too conservative or too loose (all-query CPA ÷ converting-query CPA, bands 1.0–1.5 / 1.5–2.0 / 2.0–2.5 / 2.5+)</t>
         </is>
       </c>
       <c r="K109" s="15" t="inlineStr">
         <is>
-          <t>Practitioner method</t>
+          <t>Nils Rooijmans script</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
@@ -9790,7 +9726,7 @@
       <c r="N109" s="17" t="n"/>
       <c r="O109" s="15" t="inlineStr">
         <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Hopkins 'How to identify and solve click fraud' (SEJ, Apr 2026); Optmyzr 'Protect Smart Bidding from spam conversions' (Jul 2026, method only, vendor byline); ZATO clean-data post. Row 44 covers data exclusions after the fact, not detection.</t>
+          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
         </is>
       </c>
       <c r="P109" s="15" t="n"/>
@@ -9802,342 +9738,42 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="B110" s="16" t="inlineStr">
-        <is>
-          <t>Landing page audit for paid search</t>
-        </is>
-      </c>
-      <c r="C110" s="15" t="inlineStr">
-        <is>
-          <t>Quality Score</t>
-        </is>
-      </c>
-      <c r="D110" s="15" t="inlineStr">
-        <is>
-          <t>Technique</t>
-        </is>
-      </c>
-      <c r="E110" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F110" s="15" t="inlineStr">
-        <is>
-          <t>Optimise</t>
-        </is>
-      </c>
-      <c r="G110" s="15" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H110" s="15" t="inlineStr">
-        <is>
-          <t>As needed</t>
-        </is>
-      </c>
-      <c r="I110" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J110" s="16" t="inlineStr">
-        <is>
-          <t>CVR low despite relevant traffic; structured LP audit (message match, hero, proof, speed, form/CTA, guarantee) and how to test LP with ad together</t>
-        </is>
-      </c>
-      <c r="K110" s="15" t="inlineStr">
-        <is>
-          <t>PPC Mastery / Adalysis</t>
-        </is>
-      </c>
-      <c r="L110" s="15" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M110" s="15" t="n"/>
-      <c r="N110" s="17" t="n"/>
-      <c r="O110" s="15" t="inlineStr">
-        <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: PPC OS 'Landing Pages — 6-pillar structural audit' and 'Landing Page Mastery' course; Adalysis 'test landing pages and ads together', 'customer journey testing'; Rhodes 'landing-page' script; Optmyzr 'PPC landing page AI signal problem'. Row 36 is the QS LPE component only.</t>
-        </is>
-      </c>
-      <c r="P110" s="15" t="n"/>
-      <c r="Q110" s="16" t="n"/>
-      <c r="R110" s="15" t="n"/>
-      <c r="S110" s="15" t="inlineStr">
-        <is>
-          <t>NEEDS ELIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="15" t="n">
-        <v>111</v>
-      </c>
-      <c r="B111" s="16" t="inlineStr">
-        <is>
-          <t>Automation layering — guardrail automations over Google's automation</t>
-        </is>
-      </c>
-      <c r="C111" s="15" t="inlineStr">
-        <is>
-          <t>Scripts &amp; automation</t>
-        </is>
-      </c>
-      <c r="D111" s="15" t="inlineStr">
-        <is>
-          <t>Strategy</t>
-        </is>
-      </c>
-      <c r="E111" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F111" s="15" t="inlineStr">
-        <is>
-          <t>Optimise</t>
-        </is>
-      </c>
-      <c r="G111" s="15" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="H111" s="15" t="inlineStr">
-        <is>
-          <t>One-off</t>
-        </is>
-      </c>
-      <c r="I111" s="15" t="inlineStr">
-        <is>
-          <t>P2</t>
-        </is>
-      </c>
-      <c r="J111" s="16" t="inlineStr">
-        <is>
-          <t>Deciding which Google automations to adopt and which monitors (alerts, rules, scripts) must sit on top of each before go-live</t>
-        </is>
-      </c>
-      <c r="K111" s="15" t="inlineStr">
-        <is>
-          <t>Fred Vallaeys</t>
-        </is>
-      </c>
-      <c r="L111" s="15" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M111" s="15" t="n"/>
-      <c r="N111" s="17" t="n"/>
-      <c r="O111" s="15" t="inlineStr">
-        <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Vallaeys 'Automation layering is driving PPC' (SEL) and canon lists it among his strongest topics; Hopkins 'How do I keep control as platforms automate my account' (SEJ, Sep 2026); Optmyzr 72,358-account manual-work study (Sep 2026). Row 77 is rules-vs-scripts tool choice, not the layering strategy.</t>
-        </is>
-      </c>
-      <c r="P111" s="15" t="n"/>
-      <c r="Q111" s="16" t="n"/>
-      <c r="R111" s="15" t="n"/>
-      <c r="S111" s="15" t="inlineStr">
-        <is>
-          <t>NEEDS ELIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="15" t="n">
-        <v>112</v>
-      </c>
-      <c r="B112" s="16" t="inlineStr">
-        <is>
-          <t>Change history monitoring</t>
-        </is>
-      </c>
-      <c r="C112" s="15" t="inlineStr">
-        <is>
-          <t>Scripts &amp; automation</t>
-        </is>
-      </c>
-      <c r="D112" s="15" t="inlineStr">
-        <is>
-          <t>Script</t>
-        </is>
-      </c>
-      <c r="E112" s="15" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="F112" s="15" t="inlineStr">
-        <is>
-          <t>Protect</t>
-        </is>
-      </c>
-      <c r="G112" s="15" t="inlineStr">
-        <is>
-          <t>Any</t>
-        </is>
-      </c>
-      <c r="H112" s="15" t="inlineStr">
-        <is>
-          <t>One-off</t>
-        </is>
-      </c>
-      <c r="I112" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J112" s="16" t="inlineStr">
-        <is>
-          <t>Multiple users, Google reps or auto-apply touching the account; want daily alerts on unexpected changes with who/what</t>
-        </is>
-      </c>
-      <c r="K112" s="15" t="inlineStr">
-        <is>
-          <t>Nils Rooijmans</t>
-        </is>
-      </c>
-      <c r="L112" s="15" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M112" s="15" t="n"/>
-      <c r="N112" s="17" t="n"/>
-      <c r="O112" s="15" t="inlineStr">
-        <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Change history alerts' script (public catalogue); Hopkins Sep 2026 on keeping control under automation. Row 78 only opts out of auto-apply; it does not monitor what changed.</t>
-        </is>
-      </c>
-      <c r="P112" s="15" t="n"/>
-      <c r="Q112" s="16" t="n"/>
-      <c r="R112" s="15" t="n"/>
-      <c r="S112" s="15" t="inlineStr">
-        <is>
-          <t>NEEDS ELIAS</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" s="15" t="n">
-        <v>113</v>
-      </c>
-      <c r="B113" s="16" t="inlineStr">
-        <is>
-          <t>Lin-Rodnitzky ratio as a search-term health metric</t>
-        </is>
-      </c>
-      <c r="C113" s="15" t="inlineStr">
-        <is>
-          <t>Keyword &amp; query</t>
-        </is>
-      </c>
-      <c r="D113" s="15" t="inlineStr">
-        <is>
-          <t>Diagnostic</t>
-        </is>
-      </c>
-      <c r="E113" s="15" t="inlineStr">
-        <is>
-          <t>Search</t>
-        </is>
-      </c>
-      <c r="F113" s="15" t="inlineStr">
-        <is>
-          <t>Diagnose</t>
-        </is>
-      </c>
-      <c r="G113" s="15" t="inlineStr">
-        <is>
-          <t>Established</t>
-        </is>
-      </c>
-      <c r="H113" s="15" t="inlineStr">
-        <is>
-          <t>Monthly</t>
-        </is>
-      </c>
-      <c r="I113" s="15" t="inlineStr">
-        <is>
-          <t>P3</t>
-        </is>
-      </c>
-      <c r="J113" s="16" t="inlineStr">
-        <is>
-          <t>Need one account-level number for whether query mining is too conservative or too loose (all-query CPA ÷ converting-query CPA, bands 1.0–1.5 / 1.5–2.0 / 2.0–2.5 / 2.5+)</t>
-        </is>
-      </c>
-      <c r="K113" s="15" t="inlineStr">
-        <is>
-          <t>Nils Rooijmans script</t>
-        </is>
-      </c>
-      <c r="L113" s="15" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="M113" s="15" t="n"/>
-      <c r="N113" s="17" t="n"/>
-      <c r="O113" s="15" t="inlineStr">
-        <is>
-          <t>Proposed in the Phase 2 coverage pass — needs Elias go/no-go before building. why core: Nils 'Lin Rodnitzky Ratio' script (Nov 2024, updated 2025) in his public catalogue; complements 10/76 which find individual waste but give no account-level verdict.</t>
-        </is>
-      </c>
-      <c r="P113" s="15" t="n"/>
-      <c r="Q113" s="16" t="n"/>
-      <c r="R113" s="15" t="n"/>
-      <c r="S113" s="15" t="inlineStr">
-        <is>
-          <t>NEEDS ELIAS</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:S91"/>
   <dataValidations count="9">
-    <dataValidation sqref="D2:D113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D2:D109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Structure,Strategy,Technique,Script,Research,Diagnostic,Setting"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="E2:E113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="E2:E109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Search,Shopping,PMax,All"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="F2:F113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="F2:F109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Setup,Scale,Optimise,Diagnose,Protect"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G2:G113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G2:G109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"New,Established,Any"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="H2:H109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"One-off,Weekly,Monthly,As needed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="I2:I113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="I2:I109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"P1,P2,P3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="L2:L113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="L2:L109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Not started,Drafting,Review,Done,Proposed,Re-check"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="R2:R113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="R2:R109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"Strong,Adequate,Thin"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="S2:S113" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="S2:S109" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
       <formula1>"PASS,FAIL,NEEDS ELIAS"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10228,10 +9864,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId84"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N87" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N88" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N90" r:id="rId89"/>
   </hyperlinks>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10745,11 +10377,11 @@
         </is>
       </c>
       <c r="B2" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A2)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A2)</f>
         <v/>
       </c>
       <c r="C2" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A2,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A2,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D2" s="22" t="n"/>
@@ -10759,7 +10391,7 @@
         </is>
       </c>
       <c r="F2" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$113,E2)</f>
+        <f>COUNTIF(Skills!$I$2:$I$109,E2)</f>
         <v/>
       </c>
       <c r="G2" s="22" t="n"/>
@@ -10769,7 +10401,7 @@
         </is>
       </c>
       <c r="I2" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$113,H2)</f>
+        <f>COUNTIF(Skills!$F$2:$F$109,H2)</f>
         <v/>
       </c>
     </row>
@@ -10780,11 +10412,11 @@
         </is>
       </c>
       <c r="B3" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A3)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A3)</f>
         <v/>
       </c>
       <c r="C3" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A3,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A3,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D3" s="22" t="n"/>
@@ -10794,7 +10426,7 @@
         </is>
       </c>
       <c r="F3" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$113,E3)</f>
+        <f>COUNTIF(Skills!$I$2:$I$109,E3)</f>
         <v/>
       </c>
       <c r="G3" s="22" t="n"/>
@@ -10804,7 +10436,7 @@
         </is>
       </c>
       <c r="I3" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$113,H3)</f>
+        <f>COUNTIF(Skills!$F$2:$F$109,H3)</f>
         <v/>
       </c>
     </row>
@@ -10815,11 +10447,11 @@
         </is>
       </c>
       <c r="B4" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A4)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A4)</f>
         <v/>
       </c>
       <c r="C4" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A4,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A4,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D4" s="22" t="n"/>
@@ -10829,7 +10461,7 @@
         </is>
       </c>
       <c r="F4" s="22">
-        <f>COUNTIF(Skills!$I$2:$I$113,E4)</f>
+        <f>COUNTIF(Skills!$I$2:$I$109,E4)</f>
         <v/>
       </c>
       <c r="G4" s="22" t="n"/>
@@ -10839,7 +10471,7 @@
         </is>
       </c>
       <c r="I4" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$113,H4)</f>
+        <f>COUNTIF(Skills!$F$2:$F$109,H4)</f>
         <v/>
       </c>
     </row>
@@ -10850,11 +10482,11 @@
         </is>
       </c>
       <c r="B5" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A5)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A5)</f>
         <v/>
       </c>
       <c r="C5" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A5,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A5,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D5" s="22" t="n"/>
@@ -10867,7 +10499,7 @@
         </is>
       </c>
       <c r="I5" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$113,H5)</f>
+        <f>COUNTIF(Skills!$F$2:$F$109,H5)</f>
         <v/>
       </c>
     </row>
@@ -10878,11 +10510,11 @@
         </is>
       </c>
       <c r="B6" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A6)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A6)</f>
         <v/>
       </c>
       <c r="C6" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A6,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A6,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D6" s="22" t="n"/>
@@ -10895,7 +10527,7 @@
         </is>
       </c>
       <c r="I6" s="22">
-        <f>COUNTIF(Skills!$F$2:$F$113,H6)</f>
+        <f>COUNTIF(Skills!$F$2:$F$109,H6)</f>
         <v/>
       </c>
     </row>
@@ -10906,11 +10538,11 @@
         </is>
       </c>
       <c r="B7" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A7)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A7)</f>
         <v/>
       </c>
       <c r="C7" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A7,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A7,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D7" s="22" t="n"/>
@@ -10927,11 +10559,11 @@
         </is>
       </c>
       <c r="B8" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A8)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A8)</f>
         <v/>
       </c>
       <c r="C8" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A8,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A8,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D8" s="22" t="n"/>
@@ -10948,11 +10580,11 @@
         </is>
       </c>
       <c r="B9" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A9)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A9)</f>
         <v/>
       </c>
       <c r="C9" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A9,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A9,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D9" s="22" t="n"/>
@@ -10969,11 +10601,11 @@
         </is>
       </c>
       <c r="B10" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A10)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A10)</f>
         <v/>
       </c>
       <c r="C10" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A10,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A10,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D10" s="22" t="n"/>
@@ -10990,11 +10622,11 @@
         </is>
       </c>
       <c r="B11" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A11)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A11)</f>
         <v/>
       </c>
       <c r="C11" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A11,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A11,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D11" s="22" t="n"/>
@@ -11011,11 +10643,11 @@
         </is>
       </c>
       <c r="B12" s="22">
-        <f>COUNTIF(Skills!$C$2:$C$113,A12)</f>
+        <f>COUNTIF(Skills!$C$2:$C$109,A12)</f>
         <v/>
       </c>
       <c r="C12" s="22">
-        <f>COUNTIFS(Skills!$C$2:$C$113,A12,Skills!$L$2:$L$113,"Done")</f>
+        <f>COUNTIFS(Skills!$C$2:$C$109,A12,Skills!$L$2:$L$109,"Done")</f>
         <v/>
       </c>
       <c r="D12" s="22" t="n"/>
